--- a/extraction/mac-gray.xlsx
+++ b/extraction/mac-gray.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Deal facts" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Deal ledger'!$A$1:$V$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Deal ledger'!$A$1:$V$53</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Rounds'!$A$1:$J$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Questions'!$A$1:$G$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Deal facts'!$A$1:$B$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Questions'!$A$1:$G$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Deal facts'!$A$1:$B$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -24,9 +24,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="MM/DD/YYYY"/>
+    <numFmt numFmtId="166" formatCode="$0.00"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -71,7 +72,7 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -439,28 +440,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V50"/>
+  <dimension ref="A1:V53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="7" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
     <col width="9" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
     <col width="7" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
     <col width="8" customWidth="1" min="15" max="15"/>
-    <col width="50" customWidth="1" min="16" max="16"/>
+    <col width="60" customWidth="1" min="16" max="16"/>
     <col width="55" customWidth="1" min="17" max="17"/>
-    <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="9" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
     <col width="12" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
@@ -584,7 +585,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>10/23/2012</t>
+          <t>04/05/2013</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -614,24 +615,24 @@
       <c r="O2" s="2" t="n"/>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Target's financial adviser, hired for Mac-Gray's possible purchase of CSC (2011-2012 Discussions), not for a sale. On 04/05/2013 the board had it explore opportunities, including with Party A.</t>
+          <t>Mac-Gray's financial adviser, first seen acting in the sale context: Board authorized management to work with it to explore transactions, incl. with Party A. Engaged 10/23/2012 for the 2011–2012 Discussions (Mac-Gray's possible purchase of CSC).</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>“In connection with Mac-Gray's consideration of a possible acquisition of CSC, which we refer to as the 2011-2012 Discussions, Mac-Gray engaged BofA Merrill Lynch on October 23, 2012.” (p. 27)</t>
+          <t>“authorized Mac-Gray management to work with BofA Merrill Lynch to explore transactional opportunities that might be available to Mac-Gray” (p. 27)</t>
         </is>
       </c>
       <c r="R2" s="2" t="n"/>
       <c r="S2" s="2" t="n"/>
       <c r="T2" s="3" t="n">
-        <v>41205</v>
+        <v>41369</v>
       </c>
       <c r="U2" s="3" t="n">
-        <v>41205</v>
+        <v>41369</v>
       </c>
       <c r="V2" s="3" t="n">
-        <v>41205</v>
+        <v>41369</v>
       </c>
     </row>
     <row r="3">
@@ -676,12 +677,12 @@
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>Board authorized this on 04/05 as part of exploring opportunities. Party A said it might consider a combination. Party A is a laundry facilities management company.</t>
+          <t>BofA, as instructed by the Board, called Party A (a laundry facilities management company) about a possible combination; Party A said it might consider one. First contact with Party A.</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>“representatives of BofA Merrill Lynch, as instructed by the Board, telephoned a representative of Party A to discuss generally a possible business combination between Party A and Mac-Gray.” (p. 27)</t>
+          <t>“the representative of Party A indicated that Party A might consider a business combination with Mac-Gray” (p. 27)</t>
         </is>
       </c>
       <c r="R3" s="2" t="n"/>
@@ -732,12 +733,12 @@
       <c r="O4" s="2" t="n"/>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Target's outside legal counsel, first seen acting here. Later also advised the Special Committee.</t>
+          <t>Mac-Gray's outside legal counsel; first seen acting at the 05/09 Board meeting. Later also advised the Special Committee.</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>“representatives from BofA Merrill Lynch and Goodwin Procter LLP, outside legal counsel to Mac-Gray, were also in attendance” (p. 27)</t>
+          <t>“Goodwin Procter LLP, outside legal counsel to Mac-Gray” (p. 27)</t>
         </is>
       </c>
       <c r="R4" s="2" t="n"/>
@@ -758,18 +759,18 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>05/15/2013</t>
+          <t>05/09/2013</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>BofA Merrill Lynch</t>
+          <t>Mac-Gray</t>
         </is>
       </c>
       <c r="D5" s="2" t="n"/>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Adviser ended</t>
+          <t>Target sale decision</t>
         </is>
       </c>
       <c r="F5" s="2" t="n">
@@ -788,24 +789,24 @@
       <c r="O5" s="2" t="n"/>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>The Transaction Committee decided on 05/14 to end the 2011-2012 mandate, since BofA was being invited to pitch for the sale-review role.</t>
+          <t>Board discussed a possible sale process and its risks (leaks, disclosure to competitors); formed a Transaction Committee (Bullock, Daoust) to recommend a financial adviser for a strategic-alternatives review incl. a sale. Qualification: sale-process decision deferred.</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>“Mac-Gray sent a letter to BofA Merrill Lynch terminating their engagement in connection with the 2011-2012 Discussions.” (p. 29)</t>
+          <t>“The Board concluded that it would discuss the review of strategic alternatives, including engaging in a potential sale process, at its next meeting” (p. 28)</t>
         </is>
       </c>
       <c r="R5" s="2" t="n"/>
       <c r="S5" s="2" t="n"/>
       <c r="T5" s="3" t="n">
-        <v>41409</v>
+        <v>41403</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>41409</v>
+        <v>41403</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>41409</v>
+        <v>41403</v>
       </c>
     </row>
     <row r="6">
@@ -814,7 +815,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>05/30/2013</t>
+          <t>05/15/2013</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -825,7 +826,7 @@
       <c r="D6" s="2" t="n"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Adviser</t>
+          <t>Adviser ended</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
@@ -844,24 +845,24 @@
       <c r="O6" s="2" t="n"/>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>Re-engaged as the target's sole financial adviser for the strategic review and possible sale, chosen from three banks. Engagement letter 05/31; no buyer financing without consent.</t>
+          <t>Mac-Gray terminated BofA's 2011–2012 Discussions engagement letter (Transaction Committee decision 05/14), because BofA was to pitch for the new sale mandate and the CSC sale had ended.</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>“the Board unanimously approved the engagement of BofA Merrill Lynch on the terms discussed at this meeting.” (p. 29)</t>
+          <t>“Mac-Gray sent a letter to BofA Merrill Lynch terminating their engagement in connection with the 2011-2012 Discussions” (p. 29)</t>
         </is>
       </c>
       <c r="R6" s="2" t="n"/>
       <c r="S6" s="2" t="n"/>
       <c r="T6" s="3" t="n">
-        <v>41424</v>
+        <v>41409</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>41424</v>
+        <v>41409</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>41424</v>
+        <v>41409</v>
       </c>
     </row>
     <row r="7">
@@ -875,13 +876,13 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Moab Partners, L.P.</t>
+          <t>BofA Merrill Lynch</t>
         </is>
       </c>
       <c r="D7" s="2" t="n"/>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Activist</t>
+          <t>Adviser</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
@@ -900,12 +901,12 @@
       <c r="O7" s="2" t="n"/>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>Moab (about 9% holder) won a proxy contest; Rothenberg and Hyman replaced incumbents. The filing does not say Moab pressed for a sale. Rothenberg was later excluded over Moab's rollover interest.</t>
+          <t>Re-engaged as Mac-Gray's (sole) financial adviser for the strategic-alternatives review incl. a sale, chosen over two other banks (pitches 05/22, 05/29). Letter signed 05/31 bars it from financing buyers without consent. Fee about $8.1m (p. 51).</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>“the Mac-Gray stockholders elected as directors Michael M. Rothenberg and James E. Hyman, candidates nominated by Mac-Gray's stockholder, Moab Partners, L.P.” (p. 29)</t>
+          <t>“the Board unanimously approved the engagement of BofA Merrill Lynch on the terms discussed at this meeting” (p. 29)</t>
         </is>
       </c>
       <c r="R7" s="2" t="n"/>
@@ -926,22 +927,18 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>06/21/2013</t>
+          <t>05/30/2013</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Party A</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Moab Partners, L.P. (Moab)</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n"/>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Activist</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
@@ -950,52 +947,34 @@
       <c r="G8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="I8" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>Heavy</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="H8" s="2" t="n"/>
+      <c r="I8" s="2" t="n"/>
+      <c r="J8" s="2" t="n"/>
+      <c r="K8" s="2" t="n"/>
+      <c r="L8" s="2" t="n"/>
+      <c r="M8" s="2" t="n"/>
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="2" t="n"/>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>Unsolicited proposal to the board, made before any NDA or diligence (Heavy by context). It was still standing when round 1 was evaluated on 07/25.</t>
+          <t>Moab (about 9% holder, per 06/12) won a proxy contest: its nominees Rothenberg (Moab general partner) and Hyman joined the Board. Moab later sought a possible equity rollover (#18, #49); Rothenberg excluded from sale deliberations.</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>“Party A submitted an unsolicited proposal to the Mac-Gray Board of Directors offering to purchase Mac-Gray for an all-cash purchase price of $17.00 to $19.00 per share” (p. 30)</t>
+          <t>“the Mac-Gray stockholders elected as directors Michael M. Rothenberg and James E. Hyman, candidates nominated by Mac-Gray's stockholder, Moab Partners, L.P.” (p. 29)</t>
         </is>
       </c>
       <c r="R8" s="2" t="n"/>
       <c r="S8" s="2" t="n"/>
       <c r="T8" s="3" t="n">
-        <v>41446</v>
+        <v>41424</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>41446</v>
+        <v>41424</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>41446</v>
+        <v>41424</v>
       </c>
     </row>
     <row r="9">
@@ -1004,18 +983,22 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>06/24/2013</t>
+          <t>06/21/2013</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Mac-Gray (Special Committee)</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n"/>
+          <t>Party A</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Target sale decision</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
@@ -1024,34 +1007,56 @@
       <c r="G9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="2" t="n"/>
-      <c r="I9" s="2" t="n"/>
-      <c r="J9" s="2" t="n"/>
-      <c r="K9" s="2" t="n"/>
-      <c r="L9" s="2" t="n"/>
-      <c r="M9" s="2" t="n"/>
+      <c r="H9" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N9" s="2" t="n"/>
       <c r="O9" s="2" t="n"/>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>Board forms a Special Committee of six independent directors, excluding CEO MacDonald and Moab's Rothenberg. The committee will weigh a sale against staying stand-alone and approach 50 parties.</t>
+          <t>Diligence open per narrative: no confidentiality agreement or diligence until 08/05 (#27). Unsolicited written proposal to the Board; Party A enters the process. Financing not stated.</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>“the Special Committee concluded that it would be in the best interests of stockholders to consider a potential sale of Mac-Gray” (p. 31)</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="n"/>
+          <t>“Party A submitted an unsolicited proposal to the Mac-Gray Board of Directors offering to purchase Mac-Gray for an all-cash purchase price of $17.00 to $19.00 per share” (p. 30)</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
       <c r="S9" s="2" t="n"/>
       <c r="T9" s="3" t="n">
-        <v>41449</v>
+        <v>41446</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>41449</v>
+        <v>41446</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>41449</v>
+        <v>41446</v>
       </c>
     </row>
     <row r="10">
@@ -1060,25 +1065,25 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>06/24/2013 to 06/28/2013</t>
+          <t>06/24/2013</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Mac-Gray (BofA Merrill Lynch)</t>
+          <t>Mac-Gray</t>
         </is>
       </c>
       <c r="D10" s="2" t="n"/>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Round opened</t>
+          <t>Target sale decision</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" s="2" t="n"/>
       <c r="I10" s="2" t="n"/>
@@ -1090,28 +1095,24 @@
       <c r="O10" s="2" t="n"/>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>BofA's outreach carries out the 06/24 decision; contacts reported by 06/28. NDA signers get an informational package, with preliminary IOIs due 07/23/2013 (no separate Deadline set row).</t>
+          <t>Board excluded CEO MacDonald and Rothenberg (possible rollover partners) and formed a six-member independent Special Committee. Committee decided to consider a sale against the stand-alone plan and to approach 50 parties (15 strategic, 35 financial). Projections presented.</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>“BofA Merrill Lynch contacted the strategic and financial parties identified at the June 24th Special Committee meeting” (p. 32)</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
+          <t>“the Special Committee concluded that it would be in the best interests of stockholders to consider a potential sale of Mac-Gray” (p. 31)</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="n"/>
       <c r="S10" s="2" t="n"/>
       <c r="T10" s="3" t="n">
-        <v>41451</v>
+        <v>41449</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>41449</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>41453</v>
+        <v>41449</v>
       </c>
     </row>
     <row r="11">
@@ -1120,22 +1121,18 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>by 06/28/2013</t>
+          <t>06/24/2013–06/28/2013 (outreach begins)</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>CSC/Pamplona</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Mac-Gray</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n"/>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Round opened</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
@@ -1149,25 +1146,27 @@
       <c r="J11" s="2" t="n"/>
       <c r="K11" s="2" t="n"/>
       <c r="L11" s="2" t="n"/>
-      <c r="M11" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M11" s="2" t="n"/>
       <c r="N11" s="2" t="n"/>
       <c r="O11" s="2" t="n"/>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>Target-initiated. Pamplona is interested, including an acquisition by its portfolio company CSC (acquired May 2013), and says diligence would be minimal.</t>
+          <t>BofA began contacting the 50 parties chosen on 06/24 over the following weeks; calls with Party A and Pamplona reported by 06/28. Confidentiality signers received an information package and a request for preliminary indications (#16).</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>“BofA Merrill Lynch also reported that they had spoken with representatives of Pamplona, as instructed by the Special Committee, who expressed interest in a transaction” (p. 32)</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="n"/>
+          <t>“BofA Merrill Lynch contacted the strategic and financial parties identified at the June 24th Special Committee meeting” (p. 32)</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
       <c r="S11" s="2" t="n"/>
       <c r="T11" s="3" t="n">
-        <v>41451</v>
+        <v>41449</v>
       </c>
       <c r="U11" s="3" t="n">
         <v>41449</v>
@@ -1182,7 +1181,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>during the next several weeks after 06/24/2013</t>
+          <t>during the several weeks after 06/24/2013</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1218,18 +1217,18 @@
       <c r="O12" s="2" t="n"/>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>Target outreach. Of 50 contacted (15 strategic, 35 financial), Party A (#2) and CSC/Pamplona (#10) are recorded separately, leaving 13 strategic parties.</t>
+          <t>Target outreach. Total 50 = 15 strategic + 35 financial, incl. Party A (first contacted 04/08, #2; spoke again 06/28, citing synergies and financing sources) and CSC/Pamplona (#14): 15 − 2 = 13. Responses not reported.</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>“to solicit potential interest in a transaction with Mac-Gray, 15 of which were potential strategic buyers and 35 of which were potential financial buyers” (p. 32)</t>
+          <t>“50 parties, including CSC and Pamplona, who together we refer to as CSC/Pamplona, and Party A, to solicit potential interest in a transaction with Mac-Gray” (p. 32)</t>
         </is>
       </c>
       <c r="R12" s="2" t="n"/>
       <c r="S12" s="2" t="n"/>
       <c r="T12" s="3" t="n">
-        <v>41451</v>
+        <v>41449</v>
       </c>
       <c r="U12" s="3" t="n">
         <v>41449</v>
@@ -1242,12 +1241,12 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>during the next several weeks after 06/24/2013</t>
+          <t>during the several weeks after 06/24/2013</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>35 financial parties</t>
+          <t>35 financial parties (incl. Party B, Party C)</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1278,18 +1277,22 @@
       <c r="O13" s="2" t="n"/>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Target outreach to all 35 financial parties (including private equity), among them Party B and Party C. 50 contacted in total.</t>
+          <t>Target outreach to 35 financial buyers, incl. private equity firms. Party B and Party C assumed to be among them (filing does not say so expressly; Q4). Rows reconcile to 50: 35 + 13 (#11) + CSC/Pamplona + Party A.</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>“to solicit potential interest in a transaction with Mac-Gray, 15 of which were potential strategic buyers and 35 of which were potential financial buyers” (p. 32)</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="n"/>
+          <t>“15 of which were potential strategic buyers and 35 of which were potential financial buyers, including private equity firms” (p. 32)</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
       <c r="S13" s="2" t="n"/>
       <c r="T13" s="3" t="n">
-        <v>41451</v>
+        <v>41449</v>
       </c>
       <c r="U13" s="3" t="n">
         <v>41449</v>
@@ -1302,7 +1305,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>over the two months after late June 2013</t>
+          <t>06/24/2013–08/24/2013 (over the next two months)</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1338,7 +1341,7 @@
       <c r="O14" s="2" t="n"/>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20 NDAs in total (2 strategic, 18 financial). Party A, CSC/Pamplona, Party B and Party C have their own rows, leaving 16 financial. Signing dates not given; each got an informational package.</t>
+          <t>Filing total: 20 signers over two months = 2 strategic (Party A #27, CSC/Pamplona #19) + 18 financial incl. Party B (#15), Party C (#17); residual 18 − 2 = 16. Dates not reported. Standstills had sunset provisions. Each received the information package.</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1348,17 +1351,19 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="S14" s="2" t="n"/>
       <c r="T14" s="3" t="n">
-        <v>41451</v>
+        <v>41449</v>
       </c>
       <c r="U14" s="3" t="n">
         <v>41449</v>
       </c>
-      <c r="V14" s="2" t="n"/>
+      <c r="V14" s="3" t="n">
+        <v>41510</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -1366,22 +1371,22 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>06/28/2013</t>
+          <t>by 06/28/2013</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Party B</t>
+          <t>CSC/Pamplona</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>NDA signed</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="F15" s="2" t="n">
@@ -1402,21 +1407,21 @@
       <c r="O15" s="2" t="n"/>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>Confidentiality and standstill agreement; received the informational package.</t>
+          <t>BofA, as instructed, called Pamplona, which was interested incl. in an acquisition by its portfolio company CSC; said diligence would be minimal given its familiarity. One bidder unit; filing classes it strategic.</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>“Party B, entered into a confidentiality and standstill agreement with Mac-Gray” (p. 32)</t>
+          <t>“Pamplona emphasized that business and legal due diligence would be minimal given its familiarity with Mac-Gray and the industry generally” (p. 32)</t>
         </is>
       </c>
       <c r="R15" s="2" t="n"/>
       <c r="S15" s="2" t="n"/>
       <c r="T15" s="3" t="n">
-        <v>41453</v>
+        <v>41451</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>41453</v>
+        <v>41449</v>
       </c>
       <c r="V15" s="3" t="n">
         <v>41453</v>
@@ -1428,12 +1433,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>06/30/2013</t>
+          <t>06/28/2013</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Party C</t>
+          <t>Party B</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1464,24 +1469,24 @@
       <c r="O16" s="2" t="n"/>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Confidentiality and standstill agreement; received the informational package.</t>
+          <t>Enters: confidentiality and standstill agreement; received the information package for a preliminary indication. Financial bidder (p. 32).</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>“Party C entered into a confidentiality and standstill agreement with Mac-Gray” (p. 32)</t>
+          <t>“Party B, entered into a confidentiality and standstill agreement with Mac-Gray and was provided with an informational package” (p. 32)</t>
         </is>
       </c>
       <c r="R16" s="2" t="n"/>
       <c r="S16" s="2" t="n"/>
       <c r="T16" s="3" t="n">
-        <v>41455</v>
+        <v>41453</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>41455</v>
+        <v>41453</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>41455</v>
+        <v>41453</v>
       </c>
     </row>
     <row r="17">
@@ -1490,18 +1495,18 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>07/06/2013</t>
+          <t>06/28/2013 (with information packages)</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Mac-Gray (Special Committee)</t>
+          <t>Mac-Gray</t>
         </is>
       </c>
       <c r="D17" s="2" t="n"/>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Deadline set</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
@@ -1517,27 +1522,35 @@
       <c r="L17" s="2" t="n"/>
       <c r="M17" s="2" t="n"/>
       <c r="N17" s="2" t="n"/>
-      <c r="O17" s="2" t="n"/>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>Refuses rollover partnership: denies the request (relayed by Rothenberg 07/03) for Moab to partner exclusively with CSC/Pamplona on a rollover. Such talks allowed only later.</t>
+          <t>Preliminary indications due 07/23/2013, to address valuation, financing, conditions and diligence focus. The instruction came with each signer's information package; dated at the first reported package (Party B, #15).</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>“the Special Committee decided to deny the exclusivity request at this stage of the process” (p. 33)</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="n"/>
+          <t>“which they were instructed to submit by July 23, 2013” (p. 32)</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
       <c r="S17" s="2" t="n"/>
       <c r="T17" s="3" t="n">
-        <v>41461</v>
+        <v>41453</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>41461</v>
+        <v>41453</v>
       </c>
       <c r="V17" s="3" t="n">
-        <v>41461</v>
+        <v>41453</v>
       </c>
     </row>
     <row r="18">
@@ -1546,17 +1559,17 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>07/11/2013</t>
+          <t>06/30/2013</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>CSC/Pamplona</t>
+          <t>Party C</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1582,24 +1595,24 @@
       <c r="O18" s="2" t="n"/>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>Agreement with Pamplona Capital Management LLC, reused in the merger agreement (s. 6.17). Received the informational package. Party A's NDA talks stalled on non-solicit terms 07/11-07/23.</t>
+          <t>Enters: confidentiality and standstill agreement; received the information package. Financial bidder (p. 32).</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>“CSC/Pamplona entered into a confidentiality and standstill agreement with Mac-Gray” (p. 33)</t>
+          <t>“Party C entered into a confidentiality and standstill agreement with Mac-Gray and was provided with an informational package” (p. 32)</t>
         </is>
       </c>
       <c r="R18" s="2" t="n"/>
       <c r="S18" s="2" t="n"/>
       <c r="T18" s="3" t="n">
-        <v>41466</v>
+        <v>41455</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>41466</v>
+        <v>41455</v>
       </c>
       <c r="V18" s="3" t="n">
-        <v>41466</v>
+        <v>41455</v>
       </c>
     </row>
     <row r="19">
@@ -1608,22 +1621,18 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>07/23/2013</t>
+          <t>07/06/2013</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>CSC/Pamplona</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Mac-Gray</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n"/>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F19" s="2" t="n">
@@ -1632,52 +1641,34 @@
       <c r="G19" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H19" s="4" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="I19" s="4" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>Heavy</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="H19" s="2" t="n"/>
+      <c r="I19" s="2" t="n"/>
+      <c r="J19" s="2" t="n"/>
+      <c r="K19" s="2" t="n"/>
+      <c r="L19" s="2" t="n"/>
+      <c r="M19" s="2" t="n"/>
       <c r="N19" s="2" t="n"/>
       <c r="O19" s="2" t="n"/>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>Preliminary IOI based only on the informational package, with no data room or management access (Heavy by context).</t>
+          <t>Refused rollover partnership: on 07/03 Rothenberg said Pamplona would seek confidentiality terms letting CSC/Pamplona share its bid and data with Moab, Moab dealing exclusively with them. Special Committee refused; rollover talks premature with anyone, allowed later.</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>“CSC/Pamplona submitted a preliminary indication of interest at an all-cash purchase price of $18.50 per share.” (p. 33)</t>
+          <t>“the Special Committee decided to deny the exclusivity request at this stage of the process” (p. 33)</t>
         </is>
       </c>
       <c r="R19" s="2" t="n"/>
       <c r="S19" s="2" t="n"/>
       <c r="T19" s="3" t="n">
-        <v>41478</v>
+        <v>41461</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>41478</v>
+        <v>41461</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>41478</v>
+        <v>41461</v>
       </c>
     </row>
     <row r="20">
@@ -1686,18 +1677,22 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>07/23/2013</t>
+          <t>07/11/2013</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Mac-Gray</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="n"/>
+          <t>CSC/Pamplona</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Deadline</t>
+          <t>NDA signed</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
@@ -1711,33 +1706,31 @@
       <c r="J20" s="2" t="n"/>
       <c r="K20" s="2" t="n"/>
       <c r="L20" s="2" t="n"/>
-      <c r="M20" s="2" t="n"/>
+      <c r="M20" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N20" s="2" t="n"/>
       <c r="O20" s="2" t="n"/>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Due date for preliminary IOIs. CSC/Pamplona bid on time; Party B and Party C bid on 07/24 and were considered on 07/25 (late bids accepted).</t>
+          <t>Enters: confidentiality and standstill agreement signed by CSC/Pamplona; received the information package. CSC is a laundry operator owned by Pamplona (private equity fund).</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>“a preliminary indication of interest, which they were instructed to submit by July 23, 2013” (p. 32)</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
+          <t>“CSC/Pamplona entered into a confidentiality and standstill agreement with Mac-Gray and were provided with an informational package” (p. 33)</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="n"/>
       <c r="S20" s="2" t="n"/>
       <c r="T20" s="3" t="n">
-        <v>41478</v>
+        <v>41466</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>41478</v>
+        <v>41466</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>41478</v>
+        <v>41466</v>
       </c>
     </row>
     <row r="21">
@@ -1751,17 +1744,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>16 other financial NDA signers</t>
+          <t>CSC/Pamplona</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Did not submit</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F21" s="2" t="n">
@@ -1770,39 +1763,43 @@
       <c r="G21" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H21" s="2" t="n"/>
-      <c r="I21" s="2" t="n"/>
-      <c r="J21" s="2" t="n"/>
-      <c r="K21" s="2" t="n"/>
-      <c r="L21" s="2" t="n"/>
+      <c r="H21" s="4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
       <c r="M21" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N21" s="2" t="n"/>
+      <c r="O21" s="2" t="n"/>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>Inferred. 20 signers − Party A (no NDA until 08/05) − 3 submitters = 16. On 07/25 the target named only four interested bidders. Some may have signed after 07/23.</t>
+          <t>Diligence open per narrative: management presentation 08/12; limited data-room access, customer data reserved (#28). Preliminary indication; financing and conditions not stated.</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>“reach out to each of the four interested bidders and arrange management meetings” (p. 34)</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>Q3</t>
-        </is>
-      </c>
+          <t>“CSC/Pamplona submitted a preliminary indication of interest at an all-cash purchase price of $18.50 per share” (p. 33)</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="n"/>
       <c r="S21" s="2" t="n"/>
       <c r="T21" s="3" t="n">
         <v>41478</v>
@@ -1820,22 +1817,18 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>07/24/2013</t>
+          <t>07/23/2013</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Party B</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
+          <t>Mac-Gray</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n"/>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Deadline</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
@@ -1844,52 +1837,38 @@
       <c r="G22" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H22" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="I22" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>Heavy</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="H22" s="2" t="n"/>
+      <c r="I22" s="2" t="n"/>
+      <c r="J22" s="2" t="n"/>
+      <c r="K22" s="2" t="n"/>
+      <c r="L22" s="2" t="n"/>
+      <c r="M22" s="2" t="n"/>
       <c r="N22" s="2" t="n"/>
       <c r="O22" s="2" t="n"/>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>Written preliminary IOI, one day after the due date. Based on the informational package only (Heavy by context).</t>
+          <t>Preliminary indications due. CSC/Pamplona on time (#20); late: Party B and Party C on 07/24 (#22, #23), Party C written revision 07/25 (#26); all reviewed 07/25. No bids reported from the other 16 signers.</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>“Party B submitted a preliminary indication of interest at an all-cash purchase price of $17.00 to $18.00 per share.” (p. 33)</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="n"/>
+          <t>“which they were instructed to submit by July 23, 2013” (p. 32)</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
       <c r="S22" s="2" t="n"/>
       <c r="T22" s="3" t="n">
-        <v>41479</v>
+        <v>41478</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>41479</v>
+        <v>41478</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>41479</v>
+        <v>41478</v>
       </c>
     </row>
     <row r="23">
@@ -1903,7 +1882,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Party C</t>
+          <t>Party B</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1923,10 +1902,10 @@
         <v>1</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
@@ -1940,7 +1919,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>Heavy</t>
+          <t>Unclear</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
@@ -1950,15 +1929,19 @@
       <c r="O23" s="2" t="n"/>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>Oral preliminary IOI to BofA, one day after the due date. Based on the informational package only (Heavy by context).</t>
+          <t>Diligence open per narrative: management presentation 08/06; data-room diligence 08/06–08/27. Preliminary indication, one day after the 07/23 due date. Financing not stated.</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>“presented an oral preliminary indication of interest at an all-cash purchase price of $15.00 to $17.00 per share” (p. 33)</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="n"/>
+          <t>“Party B submitted a preliminary indication of interest at an all-cash purchase price of $17.00 to $18.00 per share” (p. 33)</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
       <c r="S23" s="2" t="n"/>
       <c r="T23" s="3" t="n">
         <v>41479</v>
@@ -1976,58 +1959,80 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>07/25/2013</t>
+          <t>07/24/2013</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Mac-Gray (Special Committee)</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="n"/>
+          <t>Party C</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Round opened</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H24" s="2" t="n"/>
-      <c r="I24" s="2" t="n"/>
-      <c r="J24" s="2" t="n"/>
-      <c r="K24" s="2" t="n"/>
-      <c r="L24" s="2" t="n"/>
-      <c r="M24" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N24" s="2" t="n"/>
       <c r="O24" s="2" t="n"/>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>Committee finds IOIs lower than expected. Advances four: Party A (subject to NDA), Party B, Party C, CSC/Pamplona. Staged disclosure; management meetings for all, synergy information for strategics; revised IOIs to follow.</t>
+          <t>Diligence open per narrative: management presentation 08/08. Oral preliminary indication by phone to BofA, one day after the due date.</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>“authorized and instructed BofA Merrill Lynch to proceed with the staged disclosure as discussed at this meeting and to reach out to each of the four interested bidders” (p. 34)</t>
+          <t>“representatives from Party C called BofA Merrill Lynch and presented an oral preliminary indication of interest at an all-cash purchase price of $15.00 to $17.00 per share” (p. 33)</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="S24" s="2" t="n"/>
       <c r="T24" s="3" t="n">
-        <v>41480</v>
+        <v>41479</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>41480</v>
+        <v>41479</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>41480</v>
+        <v>41479</v>
       </c>
     </row>
     <row r="25">
@@ -2036,12 +2041,12 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>07/25/2013</t>
+          <t>by 07/25/2013</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Party C</t>
+          <t>16 other financial NDA signers</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -2051,7 +2056,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Dropped by target</t>
         </is>
       </c>
       <c r="F25" s="2" t="n">
@@ -2060,50 +2065,44 @@
       <c r="G25" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H25" s="4" t="n">
+      <c r="H25" s="2" t="n"/>
+      <c r="I25" s="2" t="n"/>
+      <c r="J25" s="2" t="n"/>
+      <c r="K25" s="2" t="n"/>
+      <c r="L25" s="2" t="n"/>
+      <c r="M25" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="I25" s="4" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>Heavy</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N25" s="2" t="n"/>
-      <c r="O25" s="2" t="n"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>Written IOI after the 07/25 meeting; revises #22 (oral $15.00-$17.00). Answers the round-1 request. Based on the informational package only (Heavy by context).</t>
+          <t>Not among the four bidders advanced on 07/25 (#25); no bids from them reported. 20 signers − 4 advanced = 16. Signing dates unknown: any later signer was outside the four-bidder stage (08/27 letters to four only). Q4.</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>“Party C submitted a written indication of interest at an all-cash purchase price of $16.00 to $16.50 per share.” (p. 34)</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="n"/>
+          <t>“reach out to each of the four interested bidders and arrange management meetings” (p. 34)</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
       <c r="S25" s="2" t="n"/>
       <c r="T25" s="3" t="n">
         <v>41480</v>
       </c>
-      <c r="U25" s="3" t="n">
-        <v>41480</v>
-      </c>
+      <c r="U25" s="2" t="n"/>
       <c r="V25" s="3" t="n">
         <v>41480</v>
       </c>
@@ -2114,22 +2113,18 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>08/05/2013</t>
+          <t>07/25/2013</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Party A</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Mac-Gray</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n"/>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>NDA signed</t>
+          <t>Round opened</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
@@ -2143,31 +2138,33 @@
       <c r="J26" s="2" t="n"/>
       <c r="K26" s="2" t="n"/>
       <c r="L26" s="2" t="n"/>
-      <c r="M26" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M26" s="2" t="n"/>
       <c r="N26" s="2" t="n"/>
       <c r="O26" s="2" t="n"/>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>Talks resumed 07/27 and non-solicit terms agreed. Received the informational package so it could improve its 06/21 proposal (#7).</t>
+          <t>Committee found indications low; chose staged disclosure and advanced four: Party A (if it signed a confidentiality agreement), Party B, Party C, CSC/Pamplona, for management meetings (held 08/06–08/14 for all four), then revised indications.</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>“Party A entered into a confidentiality and standstill agreement with Mac-Gray and was provided with an informational package” (p. 34)</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="n"/>
+          <t>“authorized and instructed BofA Merrill Lynch to proceed with the staged disclosure as discussed at this meeting and to reach out to each of the four interested bidders” (p. 34)</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
       <c r="S26" s="2" t="n"/>
       <c r="T26" s="3" t="n">
-        <v>41491</v>
+        <v>41480</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>41491</v>
+        <v>41480</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>41491</v>
+        <v>41480</v>
       </c>
     </row>
     <row r="27">
@@ -2176,54 +2173,80 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>08/06/2013 to 08/27/2013</t>
+          <t>07/25/2013</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Mac-Gray</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="n"/>
+          <t>Party C</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F27" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H27" s="2" t="n"/>
-      <c r="I27" s="2" t="n"/>
-      <c r="J27" s="2" t="n"/>
-      <c r="K27" s="2" t="n"/>
-      <c r="L27" s="2" t="n"/>
-      <c r="M27" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N27" s="2" t="n"/>
       <c r="O27" s="2" t="n"/>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>Information access differs by bidder type: B and C (financial) get broad data-room access; A and CSC/Pamplona (strategic) get limited access, customer data withheld, plus synergy talks. All four had management presentations 08/06-08/14.</t>
+          <t>Diligence open per narrative: management presentation 08/08. Written indication after the committee meeting, replacing the oral range (#23): top cut from $17.00 to $16.50.</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>“Party A and CSC/Pamplona, in light of the fact that they were strategic bidders, were given somewhat limited access to this electronic data site” (p. 34)</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="n"/>
+          <t>“Party C submitted a written indication of interest at an all-cash purchase price of $16.00 to $16.50 per share” (p. 34)</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
       <c r="S27" s="2" t="n"/>
       <c r="T27" s="3" t="n">
-        <v>41492</v>
+        <v>41480</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>41492</v>
+        <v>41480</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>41513</v>
+        <v>41480</v>
       </c>
     </row>
     <row r="28">
@@ -2232,18 +2255,22 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>08/27/2013</t>
+          <t>08/05/2013</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Mac-Gray (BofA Merrill Lynch)</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="n"/>
+          <t>Party A</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Deadline set</t>
+          <t>NDA signed</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
@@ -2257,29 +2284,35 @@
       <c r="J28" s="2" t="n"/>
       <c r="K28" s="2" t="n"/>
       <c r="L28" s="2" t="n"/>
-      <c r="M28" s="2" t="n"/>
+      <c r="M28" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N28" s="2" t="n"/>
       <c r="O28" s="2" t="n"/>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>Letter to all four (authorized 08/15): revised written proposals due 09/09/2013 to go on to in-depth evaluation. Proposals to cover valuation, financing, approvals, covenants and diligence.</t>
+          <t>Catch-up access: after talks on non-solicitation terms stalled (07/11–07/23) and resumed 07/27 (filing prints '2103'), Party A signed and got the information package to improve its 06/21 proposal (#8). Already entered at #8.</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>“instructing such bidders to submit revised written proposals no later than September 9, 2013 if such bidders wished to proceed further in the process” (p. 35)</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="n"/>
+          <t>“Party A entered into a confidentiality and standstill agreement with Mac-Gray and was provided with an informational package” (p. 34)</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
       <c r="S28" s="2" t="n"/>
       <c r="T28" s="3" t="n">
-        <v>41513</v>
+        <v>41491</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>41513</v>
+        <v>41491</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>41513</v>
+        <v>41491</v>
       </c>
     </row>
     <row r="29">
@@ -2288,22 +2321,18 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>09/09/2013</t>
+          <t>between 08/06/2013 and 08/27/2013</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>CSC/Pamplona</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Mac-Gray</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n"/>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F29" s="2" t="n">
@@ -2312,52 +2341,38 @@
       <c r="G29" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H29" s="4" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="I29" s="4" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>Heavy</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="H29" s="2" t="n"/>
+      <c r="I29" s="2" t="n"/>
+      <c r="J29" s="2" t="n"/>
+      <c r="K29" s="2" t="n"/>
+      <c r="L29" s="2" t="n"/>
+      <c r="M29" s="2" t="n"/>
       <c r="N29" s="2" t="n"/>
       <c r="O29" s="2" t="n"/>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>Revised IOI, up from $18.50 (#18). Pamplona commits 100% of the capital. Requests 2-week exclusivity. Heavy: customer data still withheld and further in-depth diligence expected.</t>
+          <t>Staged information access: financial bidders Party B and Party C got broad data-room access; strategic bidders Party A and CSC/Pamplona got limited access, customer data incl. locations reserved for later (07/25 staging). Strategics also discussed synergies with management.</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>“CSC/Pamplona submitted a revised indication of interest with an all-cash purchase price of $19.50 per share, indicating that Pamplona was committed to provide 100% of the capital” (p. 35)</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="n"/>
+          <t>“Party B and Party C, in light of the fact that they were financial bidders, were given broad access to an electronic data site” (p. 34)</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
       <c r="S29" s="2" t="n"/>
       <c r="T29" s="3" t="n">
-        <v>41526</v>
+        <v>41492</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>41526</v>
+        <v>41492</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>41526</v>
+        <v>41513</v>
       </c>
     </row>
     <row r="30">
@@ -2366,22 +2381,18 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>09/09/2013</t>
+          <t>08/27/2013</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Party B</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
+          <t>Mac-Gray</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n"/>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Deadline set</t>
         </is>
       </c>
       <c r="F30" s="2" t="n">
@@ -2390,52 +2401,38 @@
       <c r="G30" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H30" s="4" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="I30" s="4" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>Heavy</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="H30" s="2" t="n"/>
+      <c r="I30" s="2" t="n"/>
+      <c r="J30" s="2" t="n"/>
+      <c r="K30" s="2" t="n"/>
+      <c r="L30" s="2" t="n"/>
+      <c r="M30" s="2" t="n"/>
       <c r="N30" s="2" t="n"/>
       <c r="O30" s="2" t="n"/>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>Revised IOI, up from $17.00-$18.00 (#21). Financing from affiliated-fund equity plus third-party debt; no firm financing commitment (Heavy).</t>
+          <t>BofA letters to Party A, Party B, Party C and CSC/Pamplona (authorized 08/15): revised written proposals due 09/09/2013 to go on to in-depth evaluation; address valuation, financing, approvals, covenants, diligence focus.</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>“Party B also submitted a revised indication of interest with an all-cash purchase price of $18.50 per share” (p. 35)</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="n"/>
+          <t>“instructing such bidders to submit revised written proposals no later than September 9, 2013 if such bidders wished to proceed further in the process” (p. 35)</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
       <c r="S30" s="2" t="n"/>
       <c r="T30" s="3" t="n">
-        <v>41526</v>
+        <v>41513</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>41526</v>
+        <v>41513</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>41526</v>
+        <v>41513</v>
       </c>
     </row>
     <row r="31">
@@ -2449,13 +2446,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Mac-Gray</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="n"/>
+          <t>CSC/Pamplona</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Deadline</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F31" s="2" t="n">
@@ -2464,29 +2465,43 @@
       <c r="G31" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H31" s="2" t="n"/>
-      <c r="I31" s="2" t="n"/>
-      <c r="J31" s="2" t="n"/>
-      <c r="K31" s="2" t="n"/>
-      <c r="L31" s="2" t="n"/>
-      <c r="M31" s="2" t="n"/>
+      <c r="H31" s="4" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="I31" s="4" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N31" s="2" t="n"/>
       <c r="O31" s="2" t="n"/>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>Due date for revised written proposals. CSC/Pamplona and Party B bid on time; Party A and Party C bid on 09/10 and were reviewed on 09/11 (late bids accepted).</t>
+          <t>Diligence open per narrative: customer data still reserved; diligence continued 09/11–09/18. Pamplona committed to provide 100% of capital. Requested two-week exclusivity. Revised indication.</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>“instructing such bidders to submit revised written proposals no later than September 9, 2013” (p. 35)</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
+          <t>“CSC/Pamplona submitted a revised indication of interest with an all-cash purchase price of $19.50 per share, indicating that Pamplona was committed to provide 100% of the capital” (p. 35)</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="n"/>
       <c r="S31" s="2" t="n"/>
       <c r="T31" s="3" t="n">
         <v>41526</v>
@@ -2504,17 +2519,17 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>09/10/2013</t>
+          <t>09/09/2013</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Party A</t>
+          <t>Party B</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -2529,10 +2544,10 @@
         <v>2</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
@@ -2556,24 +2571,24 @@
       <c r="O32" s="2" t="n"/>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>Revised IOI, one day late; same range as its 06/21 proposal (#7). To be financed by existing credit facilities or affiliated equity; no firm financing commitment (Heavy).</t>
+          <t>No firm financing commitment: to be financed by affiliated-fund equity plus third-party debt (p. 35). Revised indication.</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>“Party A submitted a revised indication of interest with an all-cash purchase price of $18.00 to $19.00 per share, to be financed by outstanding credit facilities or affiliated equity sources.” (p. 35)</t>
+          <t>“Party B also submitted a revised indication of interest with an all-cash purchase price of $18.50 per share” (p. 35)</t>
         </is>
       </c>
       <c r="R32" s="2" t="n"/>
       <c r="S32" s="2" t="n"/>
       <c r="T32" s="3" t="n">
-        <v>41527</v>
+        <v>41526</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>41527</v>
+        <v>41526</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>41527</v>
+        <v>41526</v>
       </c>
     </row>
     <row r="33">
@@ -2582,22 +2597,18 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>09/10/2013</t>
+          <t>09/09/2013</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Party C</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
+          <t>Mac-Gray</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n"/>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Deadline</t>
         </is>
       </c>
       <c r="F33" s="2" t="n">
@@ -2606,52 +2617,38 @@
       <c r="G33" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H33" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="I33" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>Heavy</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="H33" s="2" t="n"/>
+      <c r="I33" s="2" t="n"/>
+      <c r="J33" s="2" t="n"/>
+      <c r="K33" s="2" t="n"/>
+      <c r="L33" s="2" t="n"/>
+      <c r="M33" s="2" t="n"/>
       <c r="N33" s="2" t="n"/>
       <c r="O33" s="2" t="n"/>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>Revised oral IOI to BofA, one day late; revises #24 ($16.00-$16.50). No firm financing commitment (Heavy).</t>
+          <t>Revised proposals due. CSC/Pamplona and Party B on time (#30, #31); late: Party A and Party C on 09/10 (#33, #34), all reviewed by the committee 09/11.</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>“indicated that it was submitting a revised oral indication of interest with an all-cash purchase price of $16.00 to $17.00 per share” (p. 35)</t>
-        </is>
-      </c>
-      <c r="R33" s="2" t="n"/>
+          <t>“submit revised written proposals no later than September 9, 2013” (p. 35)</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
       <c r="S33" s="2" t="n"/>
       <c r="T33" s="3" t="n">
-        <v>41527</v>
+        <v>41526</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>41527</v>
+        <v>41526</v>
       </c>
       <c r="V33" s="3" t="n">
-        <v>41527</v>
+        <v>41526</v>
       </c>
     </row>
     <row r="34">
@@ -2660,18 +2657,22 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>09/11/2013</t>
+          <t>09/10/2013</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Stewart G. MacDonald, Jr. (CEO)</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="n"/>
+          <t>Party A</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
@@ -2680,34 +2681,56 @@
       <c r="G34" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H34" s="2" t="n"/>
-      <c r="I34" s="2" t="n"/>
-      <c r="J34" s="2" t="n"/>
-      <c r="K34" s="2" t="n"/>
-      <c r="L34" s="2" t="n"/>
-      <c r="M34" s="2" t="n"/>
+      <c r="H34" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N34" s="2" t="n"/>
       <c r="O34" s="2" t="n"/>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>Rollover refused by holder: CEO and major holder says he won't roll over shares. BofA reports bidders unlikely to proceed without his support; committee has him fully briefed (09/12). He backs the process, wants higher value.</t>
+          <t>No firm financing commitment (p. 35); to be funded by existing credit facilities or affiliated equity. Revised indication, one day late; floor raised from $17.00 (#8).</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>“it was unlikely that any of these parties would move forward in the process without the express support of Mr. MacDonald” (p. 35)</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="n"/>
+          <t>“Party A submitted a revised indication of interest with an all-cash purchase price of $18.00 to $19.00 per share, to be financed by outstanding credit facilities or affiliated equity sources” (p. 35)</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
       <c r="S34" s="2" t="n"/>
       <c r="T34" s="3" t="n">
-        <v>41528</v>
+        <v>41527</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>41528</v>
+        <v>41527</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>41528</v>
+        <v>41527</v>
       </c>
     </row>
     <row r="35">
@@ -2716,58 +2739,80 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>09/11/2013</t>
+          <t>09/10/2013</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Mac-Gray (Special Committee)</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="n"/>
+          <t>Party C</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Round opened</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F35" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H35" s="2" t="n"/>
-      <c r="I35" s="2" t="n"/>
-      <c r="J35" s="2" t="n"/>
-      <c r="K35" s="2" t="n"/>
-      <c r="L35" s="2" t="n"/>
-      <c r="M35" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="H35" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="I35" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N35" s="2" t="n"/>
       <c r="O35" s="2" t="n"/>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>BofA calls all four the same day asking for final IOIs by 09/18/2013. Short exclusivity offered to one bidder depending on price and deal certainty.</t>
+          <t>No firm financing commitment (p. 35). Oral revised indication by phone to BofA, one day late; up from $16.00–16.50 (#26).</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>“the Special Committee instructed BofA Merrill Lynch to call each of Party A, Party B, Party C and CSC/Pamplona to request final indications of interest by September 18, 2013” (p. 36)</t>
+          <t>“a representative of Party C indicated that it was submitting a revised oral indication of interest with an all-cash purchase price of $16.00 to $17.00 per share” (p. 35)</t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="S35" s="2" t="n"/>
       <c r="T35" s="3" t="n">
-        <v>41528</v>
+        <v>41527</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>41528</v>
+        <v>41527</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>41528</v>
+        <v>41527</v>
       </c>
     </row>
     <row r="36">
@@ -2776,80 +2821,54 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>09/18/2013</t>
+          <t>09/11/2013</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>CSC/Pamplona</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Stewart G. MacDonald, Jr. (CEO, large holder)</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n"/>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F36" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H36" s="4" t="n">
-        <v>20.75</v>
-      </c>
-      <c r="I36" s="4" t="n">
-        <v>20.75</v>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="H36" s="2" t="n"/>
+      <c r="I36" s="2" t="n"/>
+      <c r="J36" s="2" t="n"/>
+      <c r="K36" s="2" t="n"/>
+      <c r="L36" s="2" t="n"/>
+      <c r="M36" s="2" t="n"/>
       <c r="N36" s="2" t="n"/>
       <c r="O36" s="2" t="n"/>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>Final-round proposal, up from $19.50 (#28); Formal as a response to the final solicitation. Pamplona commits 100% of the capital; only confirmatory diligence followed (Light). Requests 2-week exclusivity.</t>
+          <t>Rollover refused by holder: MacDonald said he would not roll over shares. BofA reported bidders unlikely to proceed without his express support, so the committee had him fully briefed (09/12); he backed continuing but urged a higher value.</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>“CSC/Pamplona submitted a proposal for an all-cash purchase price of $20.75 per share, reiterating that Pamplona was committed to provide 100% of the capital” (p. 36)</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>Q4</t>
-        </is>
-      </c>
+          <t>“Mr. MacDonald indicated that he had decided that he was not interested in rolling over any of his shares in any transaction” (p. 35)</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="n"/>
       <c r="S36" s="2" t="n"/>
       <c r="T36" s="3" t="n">
-        <v>41535</v>
+        <v>41528</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>41535</v>
+        <v>41528</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>41535</v>
+        <v>41528</v>
       </c>
     </row>
     <row r="37">
@@ -2858,22 +2877,18 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>09/18/2013</t>
+          <t>09/11/2013</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Party A</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Mac-Gray</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n"/>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Bid reaffirmed</t>
+          <t>Round opened</t>
         </is>
       </c>
       <c r="F37" s="2" t="n">
@@ -2882,56 +2897,38 @@
       <c r="G37" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H37" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="I37" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>Heavy</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="H37" s="2" t="n"/>
+      <c r="I37" s="2" t="n"/>
+      <c r="J37" s="2" t="n"/>
+      <c r="K37" s="2" t="n"/>
+      <c r="L37" s="2" t="n"/>
+      <c r="M37" s="2" t="n"/>
       <c r="N37" s="2" t="n"/>
       <c r="O37" s="2" t="n"/>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>By phone to BofA: confirms #31 as its best and final offer, answering the final solicitation. The 09/10 bid had no firm financing commitment and none is reported since (Heavy).</t>
+          <t>Committee had BofA call all four (Party A, Party B, Party C, CSC/Pamplona) the same day for final indications due 09/18/2013, saying Mac-Gray might grant one bidder short exclusivity depending on price and deal certainty.</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>“its previous indication of interest with an all-cash purchase price of $18.00 to $19.00 per share was its best and final offer” (p. 36)</t>
+          <t>“request final indications of interest by September 18, 2013” (p. 36)</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="S37" s="2" t="n"/>
       <c r="T37" s="3" t="n">
-        <v>41535</v>
+        <v>41528</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>41535</v>
+        <v>41528</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>41535</v>
+        <v>41528</v>
       </c>
     </row>
     <row r="38">
@@ -2945,12 +2942,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Party B</t>
+          <t>CSC/Pamplona</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -2965,14 +2962,14 @@
         <v>3</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>21.5</v>
+        <v>20.75</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>21.5</v>
+        <v>20.75</v>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -2982,7 +2979,7 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>Heavy</t>
+          <t>Unclear</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
@@ -2992,17 +2989,17 @@
       <c r="O38" s="2" t="n"/>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>Party B values its bid at $21.50: $19.00 cash plus options for 10% of new equity, which it values at $2.50 and which vest on a five-year target. Debt-and-equity financing, no commitment reported (Heavy).</t>
+          <t>Diligence open per narrative: customer data still reserved (#28, #48). Pamplona committed to provide 100% of capital; requested two-week exclusivity. Formal as the answer to the final-indication request, no markup (Q3).</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>“Party B also submitted a revised indication of interest with a purchase price that Party B valued at $21.50 per share, including $19.00 of cash to be paid at closing” (p. 36)</t>
+          <t>“CSC/Pamplona submitted a proposal for an all-cash purchase price of $20.75 per share, reiterating that Pamplona was committed to provide 100% of the capital” (p. 36)</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>Q4; Q5</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="S38" s="2" t="n"/>
@@ -3027,17 +3024,17 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Party C</t>
+          <t>Party A</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Did not submit</t>
+          <t>Bid reaffirmed</t>
         </is>
       </c>
       <c r="F39" s="2" t="n">
@@ -3046,31 +3043,47 @@
       <c r="G39" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H39" s="2" t="n"/>
-      <c r="I39" s="2" t="n"/>
-      <c r="J39" s="2" t="n"/>
-      <c r="K39" s="2" t="n"/>
-      <c r="L39" s="2" t="n"/>
+      <c r="H39" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="I39" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
       <c r="M39" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
+      <c r="N39" s="2" t="n"/>
       <c r="O39" s="2" t="n"/>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>Did not submit or reaffirm its $16.00-$17.00 IOI (#32) and gave no reason. Reported on 09/19; not seen again.</t>
+          <t>Diligence open per narrative: customer data reserved; diligence continued 09/11–09/18. By price confirmation: Party A told BofA by phone its 09/10 range (#33) was its best and final offer. Financing status at this date not reported.</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>“Party C did not submit a revised indication of interest or reiterate its prior indication of interest” (p. 36)</t>
-        </is>
-      </c>
-      <c r="R39" s="2" t="n"/>
+          <t>“its previous indication of interest with an all-cash purchase price of $18.00 to $19.00 per share was its best and final offer” (p. 36)</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
       <c r="S39" s="2" t="n"/>
       <c r="T39" s="3" t="n">
         <v>41535</v>
@@ -3093,13 +3106,17 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Mac-Gray</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="n"/>
+          <t>Party B</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Deadline</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
@@ -3108,27 +3125,45 @@
       <c r="G40" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H40" s="2" t="n"/>
-      <c r="I40" s="2" t="n"/>
-      <c r="J40" s="2" t="n"/>
-      <c r="K40" s="2" t="n"/>
-      <c r="L40" s="2" t="n"/>
-      <c r="M40" s="2" t="n"/>
+      <c r="H40" s="4" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="I40" s="4" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N40" s="2" t="n"/>
       <c r="O40" s="2" t="n"/>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>Due date for final IOIs, reached. On 09/19 the committee acted on the bids in hand (enforced).</t>
+          <t>Diligence open per narrative: diligence continued 09/11–09/18. Bidder values offer at $21.50: $19.00 cash at closing plus options on 10% of new equity, vesting on base-case projections over five years, valued by it at $2.50. Committee expected affiliated equity plus third-party debt (p. 37). Q5.</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>“request final indications of interest by September 18, 2013” (p. 36)</t>
+          <t>“a revised indication of interest with a purchase price that Party B valued at $21.50 per share, including $19.00 of cash to be paid at closing” (p. 36)</t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q3; Q5</t>
         </is>
       </c>
       <c r="S40" s="2" t="n"/>
@@ -3148,18 +3183,22 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>09/19/2013</t>
+          <t>09/18/2013</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Mac-Gray (Special Committee)</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="n"/>
+          <t>Party C</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Did not submit</t>
         </is>
       </c>
       <c r="F41" s="2" t="n">
@@ -3173,29 +3212,35 @@
       <c r="J41" s="2" t="n"/>
       <c r="K41" s="2" t="n"/>
       <c r="L41" s="2" t="n"/>
-      <c r="M41" s="2" t="n"/>
-      <c r="N41" s="2" t="n"/>
+      <c r="M41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
       <c r="O41" s="2" t="n"/>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>Preferred bidder and price requirement: CSC/Pamplona is best on value, certainty and risk (Party B's options and financing riskier). Exclusivity offered at $21.25; MacDonald supports $21.25.</t>
+          <t>Party C neither revised nor reiterated its $16.00–17.00 indication (#34) by the final-indication due date and gave no reason. Its decision.</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t>“the Special Committee would be prepared to move into exclusivity at a price of $21.25 per share” (p. 37)</t>
+          <t>“Party C did not submit a revised indication of interest or reiterate its prior indication of interest” (p. 36)</t>
         </is>
       </c>
       <c r="R41" s="2" t="n"/>
       <c r="S41" s="2" t="n"/>
       <c r="T41" s="3" t="n">
-        <v>41536</v>
+        <v>41535</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>41536</v>
+        <v>41535</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>41536</v>
+        <v>41535</v>
       </c>
     </row>
     <row r="42">
@@ -3204,22 +3249,18 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>09/21/2013</t>
+          <t>09/18/2013</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>CSC/Pamplona</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Mac-Gray</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n"/>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Deadline</t>
         </is>
       </c>
       <c r="F42" s="2" t="n">
@@ -3228,56 +3269,38 @@
       <c r="G42" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H42" s="4" t="n">
-        <v>21.25</v>
-      </c>
-      <c r="I42" s="4" t="n">
-        <v>21.25</v>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="H42" s="2" t="n"/>
+      <c r="I42" s="2" t="n"/>
+      <c r="J42" s="2" t="n"/>
+      <c r="K42" s="2" t="n"/>
+      <c r="L42" s="2" t="n"/>
+      <c r="M42" s="2" t="n"/>
       <c r="N42" s="2" t="n"/>
       <c r="O42" s="2" t="n"/>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>Raised from $20.75 (#35) the same day the committee asked. Conditioned on 2-week exclusivity; asks for voting agreements from MacDonald. Pamplona funds 100%, no financing contingency; confirmatory diligence only (Light).</t>
+          <t>Final indications due. CSC/Pamplona, Party B and Party A (reaffirmation) answered the same day; Party C did not (#40). Committee chose on the bids in hand on 09/19 (#42).</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>“CSC/Pamplona were willing to increase their all-cash purchase price to $21.25 per share as a last and best offer” (p. 37)</t>
+          <t>“request final indications of interest by September 18, 2013” (p. 36)</t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="S42" s="2" t="n"/>
       <c r="T42" s="3" t="n">
-        <v>41538</v>
+        <v>41535</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>41538</v>
+        <v>41535</v>
       </c>
       <c r="V42" s="3" t="n">
-        <v>41538</v>
+        <v>41535</v>
       </c>
     </row>
     <row r="43">
@@ -3286,22 +3309,18 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>09/24/2013</t>
+          <t>09/19/2013</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>CSC/Pamplona</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Mac-Gray</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n"/>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Exclusivity changed</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F43" s="2" t="n">
@@ -3315,31 +3334,29 @@
       <c r="J43" s="2" t="n"/>
       <c r="K43" s="2" t="n"/>
       <c r="L43" s="2" t="n"/>
-      <c r="M43" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M43" s="2" t="n"/>
       <c r="N43" s="2" t="n"/>
       <c r="O43" s="2" t="n"/>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>Executed, authorized 09/23; exclusive until 5 p.m. 10/12/2013. Ends if CSC/Pamplona adversely changes the $21.25 final proposal. CSC/Pamplona then got full data-room access.</t>
+          <t>Preferred bidder and price requirement: committee judged CSC/Pamplona best on value, certainty and no third-party financing, despite Party B's higher face value (option risk); offered exclusivity at $21.25. MacDonald said he would support $21.25.</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t>“CSC, Pamplona and Mac-Gray executed the exclusivity agreement providing for exclusive negotiations until 5 p.m. ET on October 12, 2013” (p. 38)</t>
+          <t>“the Special Committee would be prepared to move into exclusivity at a price of $21.25 per share” (p. 37)</t>
         </is>
       </c>
       <c r="R43" s="2" t="n"/>
       <c r="S43" s="2" t="n"/>
       <c r="T43" s="3" t="n">
-        <v>41541</v>
+        <v>41536</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>41541</v>
+        <v>41536</v>
       </c>
       <c r="V43" s="3" t="n">
-        <v>41541</v>
+        <v>41536</v>
       </c>
     </row>
     <row r="44">
@@ -3348,12 +3365,12 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>by 09/24/2013</t>
+          <t>09/21/2013</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Party A</t>
+          <t>CSC/Pamplona</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -3363,7 +3380,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Dropped by target</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F44" s="2" t="n">
@@ -3372,44 +3389,56 @@
       <c r="G44" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H44" s="2" t="n"/>
-      <c r="I44" s="2" t="n"/>
-      <c r="J44" s="2" t="n"/>
-      <c r="K44" s="2" t="n"/>
-      <c r="L44" s="2" t="n"/>
+      <c r="H44" s="4" t="n">
+        <v>21.25</v>
+      </c>
+      <c r="I44" s="4" t="n">
+        <v>21.25</v>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
       <c r="M44" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>Would not improve earlier offer</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="N44" s="2" t="n"/>
+      <c r="O44" s="2" t="n"/>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>Inferred: displaced when exclusivity with CSC/Pamplona was executed; not reported told. On 09/18 it declined to improve its $18.00-$19.00 range (#36).</t>
+          <t>Diligence open per narrative: customer data not yet released (#48). Pamplona funding 100%, no financing contingency (terms of 09/21–09/23). 'Last and best' answer to #42, conditional on two-week exclusivity; requested MacDonald voting agreements.</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>“CSC, Pamplona and Mac-Gray executed the exclusivity agreement providing for exclusive negotiations until 5 p.m. ET on October 12, 2013” (p. 38)</t>
-        </is>
-      </c>
-      <c r="R44" s="2" t="n"/>
+          <t>“willing to increase their all-cash purchase price to $21.25 per share as a last and best offer, provided that Mac-Gray agree to a two week period of exclusive negotiations” (p. 37)</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
       <c r="S44" s="2" t="n"/>
       <c r="T44" s="3" t="n">
-        <v>41541</v>
+        <v>41538</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>41541</v>
+        <v>41538</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>41541</v>
+        <v>41538</v>
       </c>
     </row>
     <row r="45">
@@ -3418,22 +3447,22 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>by 09/24/2013</t>
+          <t>09/24/2013</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Party B</t>
+          <t>CSC/Pamplona</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Dropped by target</t>
+          <t>Exclusivity changed</t>
         </is>
       </c>
       <c r="F45" s="2" t="n">
@@ -3450,24 +3479,16 @@
       <c r="M45" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N45" s="2" t="inlineStr">
-        <is>
-          <t>Terms or process</t>
-        </is>
-      </c>
-      <c r="O45" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="N45" s="2" t="n"/>
+      <c r="O45" s="2" t="n"/>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>Inferred date: displaced by exclusivity with CSC/Pamplona. Reason from the committee on 09/19: Party B's options were contingent and deferred, and its financing riskier, despite the higher face value.</t>
+          <t>Executed with CSC and Pamplona to 5 p.m. ET 10/12/2013 (authorized 09/23); lapses if they worsen the final proposal: $21.25 cash, $15m reverse termination fee, no financing contingency, Pamplona funding 100%.</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>“the revised indication of interest submitted by CSC/Pamplona had the potential of delivering the most value to stockholders, provided greater certainty and involved less potential risk” (p. 37)</t>
+          <t>“CSC, Pamplona and Mac-Gray executed the exclusivity agreement providing for exclusive negotiations until 5 p.m. ET on October 12, 2013” (p. 38)</t>
         </is>
       </c>
       <c r="R45" s="2" t="n"/>
@@ -3488,18 +3509,22 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>09/25/2013</t>
+          <t>by 09/24/2013</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Kirkland &amp; Ellis LLP</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="n"/>
+          <t>Party A</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Adviser</t>
+          <t>Dropped by target</t>
         </is>
       </c>
       <c r="F46" s="2" t="n">
@@ -3513,29 +3538,39 @@
       <c r="J46" s="2" t="n"/>
       <c r="K46" s="2" t="n"/>
       <c r="L46" s="2" t="n"/>
-      <c r="M46" s="2" t="n"/>
-      <c r="N46" s="2" t="n"/>
-      <c r="O46" s="2" t="n"/>
+      <c r="M46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>Outside legal counsel to CSC/Pamplona; first seen acting when it received the target's first merger agreement draft.</t>
+          <t>Inferred: live rival when exclusivity with CSC/Pamplona was executed (#44); filing does not say it was told. Its best and final $18.00–19.00 (#38) was below CSC/Pamplona's $21.25.</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>“Kirkland &amp; Ellis LLP, outside legal counsel to CSC/Pamplona” (p. 38)</t>
+          <t>“CSC, Pamplona and Mac-Gray executed the exclusivity agreement providing for exclusive negotiations” (p. 38)</t>
         </is>
       </c>
       <c r="R46" s="2" t="n"/>
       <c r="S46" s="2" t="n"/>
       <c r="T46" s="3" t="n">
-        <v>41542</v>
+        <v>41541</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>41542</v>
+        <v>41535</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>41542</v>
+        <v>41541</v>
       </c>
     </row>
     <row r="47">
@@ -3544,18 +3579,22 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>09/25/2013 to 10/07/2013</t>
+          <t>by 09/24/2013</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Moab Partners, L.P.</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="n"/>
+          <t>Party B</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Dropped by target</t>
         </is>
       </c>
       <c r="F47" s="2" t="n">
@@ -3569,29 +3608,39 @@
       <c r="J47" s="2" t="n"/>
       <c r="K47" s="2" t="n"/>
       <c r="L47" s="2" t="n"/>
-      <c r="M47" s="2" t="n"/>
-      <c r="N47" s="2" t="n"/>
-      <c r="O47" s="2" t="n"/>
+      <c r="M47" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>Rollover resolved: talks with Pamplona, allowed from 09/23, end with no Moab rollover (reported 10/07). Moab signed a voting agreement at signing.</t>
+          <t>Inferred: live rival when exclusivity with CSC/Pamplona was executed (#44); not reported as told. Its offer, valued by Party B at $21.50 incl. $19.00 cash (#39), lost on certainty (#42).</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
         <is>
-          <t>“As a result of such discussions, it was determined that Moab would not rollover any Moab shares in the transaction.” (p. 38)</t>
+          <t>“CSC, Pamplona and Mac-Gray executed the exclusivity agreement providing for exclusive negotiations” (p. 38)</t>
         </is>
       </c>
       <c r="R47" s="2" t="n"/>
       <c r="S47" s="2" t="n"/>
       <c r="T47" s="3" t="n">
-        <v>41548</v>
+        <v>41541</v>
       </c>
       <c r="U47" s="3" t="n">
-        <v>41542</v>
+        <v>41535</v>
       </c>
       <c r="V47" s="3" t="n">
-        <v>41554</v>
+        <v>41541</v>
       </c>
     </row>
     <row r="48">
@@ -3600,22 +3649,18 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>10/12/2013</t>
+          <t>09/25/2013</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>CSC/Pamplona</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Kirkland &amp; Ellis LLP</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n"/>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Exclusivity changed</t>
+          <t>Adviser</t>
         </is>
       </c>
       <c r="F48" s="2" t="n">
@@ -3629,31 +3674,29 @@
       <c r="J48" s="2" t="n"/>
       <c r="K48" s="2" t="n"/>
       <c r="L48" s="2" t="n"/>
-      <c r="M48" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M48" s="2" t="n"/>
       <c r="N48" s="2" t="n"/>
       <c r="O48" s="2" t="n"/>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>Extended to 11:59 p.m. 10/15/2013. CSC/Pamplona asked 10/09; the committee required a termination fee of at most $11 million, agreed 10/11.</t>
+          <t>Outside legal counsel to CSC/Pamplona; first seen acting on 09/25, receiving Goodwin Procter's initial merger-agreement draft.</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>“CSC, Pamplona and Mac-Gray executed a letter agreement extending exclusivity until 11:59 p.m. ET on October 15, 2013.” (p. 41)</t>
+          <t>“Kirkland &amp; Ellis LLP, outside legal counsel to CSC/Pamplona” (p. 38)</t>
         </is>
       </c>
       <c r="R48" s="2" t="n"/>
       <c r="S48" s="2" t="n"/>
       <c r="T48" s="3" t="n">
-        <v>41559</v>
+        <v>41542</v>
       </c>
       <c r="U48" s="3" t="n">
-        <v>41559</v>
+        <v>41542</v>
       </c>
       <c r="V48" s="3" t="n">
-        <v>41559</v>
+        <v>41542</v>
       </c>
     </row>
     <row r="49">
@@ -3662,7 +3705,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>10/14/2013</t>
+          <t>between 09/25/2013 and 10/07/2013</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -3677,7 +3720,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Merger agreement signed</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F49" s="2" t="n">
@@ -3698,28 +3741,24 @@
       <c r="O49" s="2" t="n"/>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>$21.25 per share in cash. Pamplona commitment letter ($594m, no financing condition); $11m target fee; $15m reverse fee; MacDonald and Moab voting agreements.</t>
+          <t>Information access after exclusivity: exclusive bidder CSC/Pamplona granted full data-room access (limited earlier, #28) and management access for confirmatory diligence.</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
         <is>
-          <t>“Later in the day, on October 14, 2013, the merger agreement was executed, the Pamplona commitment letter was delivered” (p. 41)</t>
-        </is>
-      </c>
-      <c r="R49" s="2" t="inlineStr">
-        <is>
-          <t>Q6</t>
-        </is>
-      </c>
+          <t>“CSC and Pamplona were granted full access to the electronic data site and access to certain members of management and conducted confirmatory business and legal due diligence” (p. 38)</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="n"/>
       <c r="S49" s="2" t="n"/>
       <c r="T49" s="3" t="n">
-        <v>41561</v>
+        <v>41542</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>41561</v>
+        <v>41542</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>41561</v>
+        <v>41554</v>
       </c>
     </row>
     <row r="50">
@@ -3728,27 +3767,25 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>10/15/2013</t>
+          <t>between 09/25/2013 and 10/07/2013</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Mac-Gray and CSC</t>
+          <t>Moab Partners, L.P. (Moab)</t>
         </is>
       </c>
       <c r="D50" s="2" t="n"/>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Merger announced</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F50" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
+      <c r="G50" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="H50" s="2" t="n"/>
       <c r="I50" s="2" t="n"/>
@@ -3760,28 +3797,210 @@
       <c r="O50" s="2" t="n"/>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>Joint announcement before the market opened. No post-signing competing proposals reported.</t>
+          <t>Rollover resolved, not formed: after Goodwin told Rothenberg on 09/23 that talks could resume, Moab and Pamplona discussed a rollover and determined none (reported 10/07). Moab signed a voting agreement at signing.</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>“Mac-Gray and CSC jointly announced the execution of the merger agreement.” (p. 41)</t>
+          <t>“it was determined that Moab would not rollover any Moab shares in the transaction” (p. 38)</t>
         </is>
       </c>
       <c r="R50" s="2" t="n"/>
       <c r="S50" s="2" t="n"/>
       <c r="T50" s="3" t="n">
+        <v>41548</v>
+      </c>
+      <c r="U50" s="3" t="n">
+        <v>41542</v>
+      </c>
+      <c r="V50" s="3" t="n">
+        <v>41554</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>10/12/2013</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>CSC/Pamplona</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Exclusivity changed</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H51" s="2" t="n"/>
+      <c r="I51" s="2" t="n"/>
+      <c r="J51" s="2" t="n"/>
+      <c r="K51" s="2" t="n"/>
+      <c r="L51" s="2" t="n"/>
+      <c r="M51" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N51" s="2" t="n"/>
+      <c r="O51" s="2" t="n"/>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>Extended to 11:59 p.m. ET 10/15/2013 at CSC/Pamplona's request (made by 10/09); committee required a Mac-Gray termination fee of at most $11m, which CSC/Pamplona accepted on 10/11.</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>“CSC, Pamplona and Mac-Gray executed a letter agreement extending exclusivity until 11:59 p.m. ET on October 15, 2013” (p. 41)</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="n"/>
+      <c r="S51" s="2" t="n"/>
+      <c r="T51" s="3" t="n">
+        <v>41559</v>
+      </c>
+      <c r="U51" s="3" t="n">
+        <v>41559</v>
+      </c>
+      <c r="V51" s="3" t="n">
+        <v>41559</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>10/14/2013</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>CSC/Pamplona</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Merger agreement signed</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H52" s="2" t="n"/>
+      <c r="I52" s="2" t="n"/>
+      <c r="J52" s="2" t="n"/>
+      <c r="K52" s="2" t="n"/>
+      <c r="L52" s="2" t="n"/>
+      <c r="M52" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N52" s="2" t="n"/>
+      <c r="O52" s="2" t="n"/>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>$21.25 per share in cash; buyers Spin Holdco (Parent), CSC ServiceWorks Holdings and CSC. Pamplona commitment letter $594m; Pamplona liability cap $50m; Mac-Gray fee $11m; CSC reverse fee $15m. Moab and MacDonald voting agreements effective. BofA fairness opinion same day.</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>“Later in the day, on October 14, 2013, the merger agreement was executed, the Pamplona commitment letter was delivered” (p. 41)</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="n"/>
+      <c r="S52" s="2" t="n"/>
+      <c r="T52" s="3" t="n">
+        <v>41561</v>
+      </c>
+      <c r="U52" s="3" t="n">
+        <v>41561</v>
+      </c>
+      <c r="V52" s="3" t="n">
+        <v>41561</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>10/15/2013</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Mac-Gray</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n"/>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Merger announced</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="n"/>
+      <c r="I53" s="2" t="n"/>
+      <c r="J53" s="2" t="n"/>
+      <c r="K53" s="2" t="n"/>
+      <c r="L53" s="2" t="n"/>
+      <c r="M53" s="2" t="n"/>
+      <c r="N53" s="2" t="n"/>
+      <c r="O53" s="2" t="n"/>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>Joint announcement by Mac-Gray and CSC before the market opened. Ref: $14.72 close 10/11/2013; about 44% premium (p. 5).</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>“before the U.S. stock markets opened, Mac-Gray and CSC jointly announced the execution of the merger agreement” (p. 41)</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="n"/>
+      <c r="S53" s="2" t="n"/>
+      <c r="T53" s="3" t="n">
         <v>41562</v>
       </c>
-      <c r="U50" s="3" t="n">
+      <c r="U53" s="3" t="n">
         <v>41562</v>
       </c>
-      <c r="V50" s="3" t="n">
+      <c r="V53" s="3" t="n">
         <v>41562</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V50"/>
+  <autoFilter ref="A1:V53"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3803,8 +4022,8 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="45" customWidth="1" min="9" max="9"/>
-    <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="45" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3867,16 +4086,16 @@
         <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>41451</v>
+        <v>41449</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>BofA outreach to 50 parties after the 06/24 decision; NDA signers asked for preliminary IOIs</t>
+          <t>Special Committee's 06/24 decision executed: BofA outreach to 50 parties; confidentiality signers asked for preliminary indications</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>20: 2 strategic (CSC/Pamplona; Party A via its standing 06/21 proposal, NDA only on 08/05) and 18 financial (Party B, Party C, 16 unnamed NDA signers)</t>
+          <t>20 entered: 2 strategic (CSC/Pamplona; Party A via its standing round-0 proposal, no NDA until 08/05) and 18 financial (Party B, Party C, 16 unnamed signers, dates unknown)</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -3896,12 +4115,12 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>3: CSC/Pamplona, Party B, Party C (oral, then written); Party A's round-0 proposal also reviewed</t>
+          <t>3: CSC/Pamplona, Party B, Party C (plus Party A's 06/21 round-0 proposal, reviewed 07/25)</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>four advanced (Party A, Party B, Party C, CSC/Pamplona); 16 financial signers out</t>
+          <t>four advanced (Party A, Party B, Party C, CSC/Pamplona); 16 other financial signers out</t>
         </is>
       </c>
     </row>
@@ -3917,7 +4136,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>committee advanced four, set up management meetings and staged data-room access, then asked for revised IOIs</t>
+          <t>committee advanced four to management meetings and staged diligence, then asked for revised written proposals</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -3942,12 +4161,12 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>4: CSC/Pamplona, Party B, Party A, Party C</t>
+          <t>4: CSC/Pamplona and Party B (09/09), Party A and Party C (09/10)</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>all four asked for final IOIs; none out</t>
+          <t>all four asked for final indications on 09/11</t>
         </is>
       </c>
     </row>
@@ -3963,7 +4182,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>committee asked all four for final IOIs by 09/18, with short exclusivity for one</t>
+          <t>committee asked all four for final indications, holding out short exclusivity</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -3988,12 +4207,12 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3: CSC/Pamplona ($20.75, raised to $21.25 on 09/21), Party B ($21.50 package), Party A (reaffirmed $18.00-$19.00); Party C did not submit</t>
+          <t>3: CSC/Pamplona, Party B, Party A (reaffirmed best and final); Party C did not submit</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>CSC/Pamplona chosen 09/19, exclusivity 09/24, signing 10/14; Party A and Party B dropped, Party C out</t>
+          <t>CSC/Pamplona selected 09/19 and raised to $21.25 on 09/21; exclusivity 09/24 (Party A, Party B out); signing 10/14</t>
         </is>
       </c>
     </row>
@@ -4009,16 +4228,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="45" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4066,27 +4285,27 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Process and round map: one process, three rounds opening at the outreach (06/24-06/28), the 07/25 advancement of four, and the 09/11 final request?</t>
+          <t>Process and round map: one process with three rounds (outreach 06/24; four advanced 07/25; final indications 09/11)?</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Yes, as recorded.</t>
+          <t>Yes. One process; round 0 holds Party A's 06/21 proposal; R1 opens with the outreach launched 06/24; R2 on 07/25; R3 on 09/11 (announced final).</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>07/25: target picked who advanced and opened a staged information stage for revised IOIs (pp. 33-34). 09/11: first request for final IOIs (p. 36).</t>
+          <t>Gaps of two months or more: 04/08/2013 (BofA–Party A call) to 06/21/2013 (Party A proposal), 74 days, both dates certain; no other. C7: (a) fails, since Party A was kept in view (05/09 report; named in 06/24 outreach); (b) fails, gap under three months; (c) met (05/09, 06/24). The 2011–2012 CSC talks had Mac-Gray as buyer (pp. 27–31).</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>8, 9, 23, 25-27, 34</t>
+          <t>#8, #10, #25, #36, #27, #28</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>If round 2 opened with the 08/27 letter, #23, #25 and #26 move to round 1. Bid rounds are unchanged.</t>
+          <t>Most plausible alternative: R2 opens with the 08/27 letter, not the 07/25 decision; #25 would move and #27, #28 would fall in R1. R1 opening date alternatives (06/24 decision vs first calls by 06/28) do not move any bid.</t>
         </is>
       </c>
       <c r="G2" s="2" t="n"/>
@@ -4099,27 +4318,27 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Deadline outcomes: 07/23 Late bids accepted; 09/09 Late bids accepted; 09/18 Enforced?</t>
+          <t>Deadline outcomes: R1 (07/23) and R2 (09/09) Late bids accepted; R3 (09/18) Enforced?</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Yes, as recorded.</t>
+          <t>Yes. R1: Party B and Party C bid 07/24 (Party C again 07/25) after receiving the 07/23 date, and all were reviewed 07/25. R2: Party A and Party C bid 09/10 and were reviewed 09/11. R3: committee selected CSC/Pamplona 09/19 on the bids in hand.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>B and C bid 07/24, reviewed 07/25 (p. 33). A and C bid 09/10, reviewed 09/11 (p. 35). The 09/19 selection used bids in hand (p. 37).</t>
+          <t>Due dates pp. 32, 35, 36; bids pp. 33–36; selection p. 37. The 07/23 instruction went to confidentiality signers, including Party B and Party C, whose agreements predate it (p. 32).</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>19, 21, 22, 30, 31, 32, 39</t>
+          <t>#16, #21, #22, #23, #26, #29, #32, #33, #34, #41</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>If one-day slips count as on time, 07/23 and 09/09 become Enforced. Live counts are unchanged.</t>
+          <t>If the one-day slippages were treated as immaterial, R1 and R2 would read Passed without action or Enforced; neither changes any row, but both would overstate enforcement.</t>
         </is>
       </c>
       <c r="G3" s="2" t="n"/>
@@ -4132,27 +4351,27 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Were all 16 unnamed financial NDA signers eligible at the 07/23 due date?</t>
+          <t>Are the 09/18 answers to the request for 'final indications of interest' and CSC/Pamplona's 09/21 $21.25 'last and best offer' Formal?</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Yes: Did not submit at 07/23 (inferred).</t>
+          <t>Formal (C13 rule 2): the 09/11 request was an announced final solicitation. No markup was delivered; Goodwin sent the first draft only on 09/25. Party A expressly called its range best and final.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>The 20 NDAs were signed 'over the next two months', undated (p. 32). On 07/25 only four bidders were named (p. 34).</t>
+          <t>The request for final indications came with the prospect of exclusivity (p. 36); CSC/Pamplona called $21.25 its 'last and best offer' (p. 37). Evidence is thin because no documents accompanied the bids.</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13, 20</t>
+          <t>#37, #38, #39, #43</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Late signers would instead be Dropped by target on 07/25 or later. The live count after 07/25 stays four.</t>
+          <t>If Informal, the winner reaches signing with no Formal row, and C12 would add a Bid reaffirmed for CSC/Pamplona at 10/07 (Kirkland's revised merger-agreement draft, p. 39), at $21.25 carried from #43, Conditions Unclear.</t>
         </is>
       </c>
       <c r="G4" s="2" t="n"/>
@@ -4165,27 +4384,27 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Are the round-3 bids Formal, though called 'indications of interest' with no markup before exclusivity?</t>
+          <t>The 16 unnamed financial confidentiality signers: are they (and Party B, Party C) within the 35 financial contacts, and did they leave by the 07/25 advancement (Dropped by target) or by the 07/23 due date (Did not submit)?</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Yes, Formal (C13 rule 2): they answer the 09/11 final request as asked.</t>
+          <t>Keep: within the 35; Dropped by target by 07/25, inferred, Count 16.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Final request p. 36. CSC/Pamplona's $21.25 is a 'last and best offer' (p. 37). Kirkland returned a merger agreement draft on 10/07 (p. 39).</t>
+          <t>The filing gives 20 signers (2 strategic, 18 financial) over two months but no dates for the 16, so it cannot show they had signed before 07/23; the four-bidder set advanced on 07/25 is complete (pp. 32–34).</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35, 36, 37, 41</t>
+          <t>#12, #13, #24</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>If Informal: add a CSC/Pamplona Bid reaffirmed at $21.25 on 10/07 (returned draft); Party A and Party B final bids become Informal.</t>
+          <t>Did not submit by 07/23 would change the exit label and round-1 non-submission count, not the live count. If some signed after 07/25, their exit would be by 08/27 (letters to four only).</t>
         </is>
       </c>
       <c r="G5" s="2" t="n"/>
@@ -4198,66 +4417,33 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>How should Party B's 09/18 cash-plus-options package be priced?</t>
+          <t>Party B's 09/18 price: record $21.50 (its own value incl. options) or $19.00 cash?</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>$21.50 (Party B's own valuation), All cash = No; the Note gives $19.00 cash + options valued at $2.50.</t>
+          <t>$21.50 in both price cells, All cash = No, with $19.00 cash and $2.50 option value in the Note.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>'valued at $21.50 per share, including $19.00 of cash'; options vest on five-year targets (p. 36).</t>
+          <t>C15: a stated per-share package value is the total offer value. Party B valued the options at $2.50; the committee questioned that value (pp. 36–37).</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>37, 44</t>
+          <t>#39</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Cash-only $19.00 would rank Party B below CSC/Pamplona's $20.75.</t>
+          <t>Using $19.00 would make Party B's final bid lower than CSC/Pamplona's $20.75, changing the reading of why it lost and the ranking of final bids.</t>
         </is>
       </c>
       <c r="G6" s="2" t="n"/>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Q6</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Is the winner CSC/Pamplona Strategic or Mixed?</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Strategic: sponsor-owned laundry operator; Pamplona provides equity.</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>The filing calls CSC/Pamplona a strategic bidder (pp. 32, 34). Parent is a CSC subsidiary (p. 26). Pamplona commits $594m (p. 59).</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>10, 17, 18, 28, 35, 41, 42, 47, 48</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Mixed if Pamplona is a co-bidder: it signed the NDA and exclusivity and has liability up to $50m. The strategic/financial split would shift.</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="n"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G7"/>
+  <autoFilter ref="A1:G6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4268,11 +4454,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="100" customWidth="1" min="2" max="2"/>
+    <col width="110" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4307,7 +4493,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>CSC ServiceWorks, Inc. (via Spin Holdco Inc. and CSC Fenway, Inc.; with CSC ServiceWorks Holdings, Inc.), a portfolio company of Pamplona Capital; funded by Pamplona Capital Partners III, L.P.</t>
+          <t>CSC ServiceWorks, Inc., through Spin Holdco Inc. (Parent), CSC ServiceWorks Holdings, Inc. and CSC Fenway, Inc.; CSC is owned by Pamplona Capital Partners III, L.P., which committed the equity (the filing calls the bidder "CSC/Pamplona")</t>
         </is>
       </c>
     </row>
@@ -4319,7 +4505,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Strategic (sponsor-owned operating company)</t>
+          <t>Strategic: laundry facilities operator owned by a private equity fund (Pamplona), which funds the deal; the filing calls CSC/Pamplona a strategic bidder (p. 32)</t>
         </is>
       </c>
     </row>
@@ -4331,7 +4517,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>$21.25 per share in cash</t>
+          <t>$21.25 per share in cash; equity funded by a $594m Pamplona commitment letter; no financing condition</t>
         </is>
       </c>
     </row>
@@ -4341,8 +4527,10 @@
           <t>Merger agreement signed</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
-        <v>41561</v>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>10/14/2013</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -4351,8 +4539,10 @@
           <t>Merger announced</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n">
-        <v>41562</v>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>10/15/2013</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -4363,7 +4553,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>DEFM14A, 12/04/2013</t>
+          <t>DEFM14A (definitive proxy statement), 12/04/2013</t>
         </is>
       </c>
     </row>
@@ -4375,7 +4565,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>27-41</t>
+          <t>pp. 27–41</t>
         </is>
       </c>
     </row>
@@ -4387,7 +4577,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>target-led</t>
+          <t>target-led: Board authorized BofA to explore opportunities (04/05/2013) and BofA sounded out Party A (04/08); Party A then made an unsolicited proposal (06/21) before the organized outreach. An activist (Moab) won board seats on 05/30/2013 but is not reported pressing for a sale.</t>
         </is>
       </c>
     </row>
@@ -4397,84 +4587,98 @@
           <t>Number of processes</t>
         </is>
       </c>
-      <c r="B11" s="2" t="n">
-        <v>1</v>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Auction screen</t>
+          <t>Earlier approaches</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Met: 20 confidentiality agreements (2 strategic, 18 financial)</t>
+          <t>Winter 2011 into 2012: talks between Mac-Gray and CSC about Mac-Gray acquiring CSC (Mac-Gray as buyer; BofA engaged 10/23/2012); CSC was instead sold to Pamplona in May 2013. Undated discussions with other industry participants. None was a sale of Mac-Gray.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Whole-company bids</t>
+          <t>Auction screen</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Met (process 1): 20 parties. The filing counts 20 potential bidders (parties) signing confidentiality agreements: 2 strategic, 18 financial; CSC and Pamplona counted as one. No post-signing additions.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Currency and units of bid prices</t>
+          <t>Whole-company bids</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>US dollars per share; Party B's 09/18 bid is $19.00 cash plus options it valued at $2.50</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Target financial advisers</t>
+          <t>Currency and units of bid prices</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>BofA Merrill Lynch (sole)</t>
+          <t>US dollars per share. Party B's 09/18 bid mixed $19.00 cash with options it valued at $2.50 per share (Q5); all others all cash.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Target legal advisers</t>
+          <t>Target financial advisers</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Goodwin Procter LLP</t>
+          <t>BofA Merrill Lynch (Merrill Lynch, Pierce, Fenner &amp; Smith Incorporated), sole financial adviser; engaged 05/31/2013 after its 2011–2012 mandate was ended 05/15/2013</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>Target legal advisers</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Goodwin Procter LLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
           <t>Account</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Mac-Gray, the second-largest US laundry facilities management contractor, had BofA Merrill Lynch sound out strategic rival Party A in April 2013; Party A made an unsolicited $17.00-$19.00 proposal on June 21. On June 24 a new Special Committee decided to consider a sale, and BofA contacted 50 parties (15 strategic, 35 financial), 20 of which signed confidentiality agreements. Preliminary indications from CSC/Pamplona ($18.50), Party B ($17.00-$18.00) and Party C ($15.00-$17.00, then $16.00-$16.50) led the committee to advance four bidders, including Party A, to management meetings and staged data-room access, with less customer data shown to strategic bidders. Revised indications on September 9-10 ranged from $16.00 to $19.50. A request for final indications by September 18 drew $20.75 from CSC/Pamplona, a $21.50 cash-plus-options package from Party B, Party A's unchanged $18.00-$19.00 and nothing from Party C. The committee preferred CSC/Pamplona's fully Pamplona-funded offer for its certainty, asked for $21.25, and signed exclusivity on September 24 once CSC/Pamplona agreed. After one extension of exclusivity, the merger agreement was signed on October 14, 2013 at $21.25 per share in cash and announced on October 15.</t>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>In spring 2013 Mac-Gray's board, with BofA Merrill Lynch, began exploring a sale; Party A made an unsolicited $17–19 all-cash proposal on 06/21/2013. A Special Committee then had BofA approach 50 parties, and 20 (2 strategic, 18 financial) signed confidentiality agreements. Preliminary indications from CSC/Pamplona ($18.50), Party B ($17–18) and Party C ($15–17, then $16–16.50) led the committee to advance four bidders, including Party A, to management meetings and staged diligence. Revised proposals (09/09–09/10) ranged from $16–17 to $19.50, and final indications on 09/18 brought CSC/Pamplona to $20.75 and Party B to a cash-and-options package it valued at $21.50; Party A stood at $18–19 and Party C dropped out. The committee preferred CSC/Pamplona's fully funded offer, obtained $21.25 in exchange for exclusivity (09/24), and signed on 10/14/2013 after negotiating fees and Pamplona's liability.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B17"/>
+  <autoFilter ref="A1:B18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/extraction/mac-gray.xlsx
+++ b/extraction/mac-gray.xlsx
@@ -13,9 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Deal facts" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Deal ledger'!$A$1:$V$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Deal ledger'!$A$1:$V$55</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Rounds'!$A$1:$J$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Questions'!$A$1:$G$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Questions'!$A$1:$G$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Deal facts'!$A$1:$B$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,10 +24,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="MM/DD/YYYY"/>
-    <numFmt numFmtId="166" formatCode="$0.00"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -72,7 +71,7 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -440,14 +439,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V53"/>
+  <dimension ref="A1:V55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="7" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
@@ -456,12 +455,12 @@
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="7" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
     <col width="8" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
-    <col width="55" customWidth="1" min="17" max="17"/>
-    <col width="9" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="60" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
     <col width="12" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
@@ -585,7 +584,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>04/05/2013</t>
+          <t>10/23/2012</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -615,24 +614,24 @@
       <c r="O2" s="2" t="n"/>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Mac-Gray's financial adviser, first seen acting in the sale context: Board authorized management to work with it to explore transactions, incl. with Party A. Engaged 10/23/2012 for the 2011–2012 Discussions (Mac-Gray's possible purchase of CSC).</t>
+          <t>Mac-Gray's financial adviser, first engaged for the 2011-2012 Discussions (Mac-Gray's possible acquisition of CSC). The filing does not say under which engagement BofA made the 04/08/2013 call to Party A.</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>“authorized Mac-Gray management to work with BofA Merrill Lynch to explore transactional opportunities that might be available to Mac-Gray” (p. 27)</t>
+          <t>In connection with Mac-Gray's consideration of a possible acquisition of CSC, which we refer to as the 2011-2012 Discussions, Mac-Gray engaged BofA Merrill Lynch on October 23, 2012. (p. 27)</t>
         </is>
       </c>
       <c r="R2" s="2" t="n"/>
       <c r="S2" s="2" t="n"/>
       <c r="T2" s="3" t="n">
-        <v>41369</v>
+        <v>41205</v>
       </c>
       <c r="U2" s="3" t="n">
-        <v>41369</v>
+        <v>41205</v>
       </c>
       <c r="V2" s="3" t="n">
-        <v>41369</v>
+        <v>41205</v>
       </c>
     </row>
     <row r="3">
@@ -677,15 +676,19 @@
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>BofA, as instructed by the Board, called Party A (a laundry facilities management company) about a possible combination; Party A said it might consider one. First contact with Party A.</t>
+          <t>BofA, instructed by the board (04/05/2013 authorization to explore transactional opportunities, including with Party A), called Party A about a possible business combination; Party A said it might consider one. First contact with Party A.</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>“the representative of Party A indicated that Party A might consider a business combination with Mac-Gray” (p. 27)</t>
-        </is>
-      </c>
-      <c r="R3" s="2" t="n"/>
+          <t>representatives of BofA Merrill Lynch, as instructed by the Board, telephoned a representative of Party A to discuss generally a possible business combination between Party A and Mac-Gray (p. 27)</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
       <c r="S3" s="2" t="n"/>
       <c r="T3" s="3" t="n">
         <v>41372</v>
@@ -733,12 +736,12 @@
       <c r="O4" s="2" t="n"/>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Mac-Gray's outside legal counsel; first seen acting at the 05/09 Board meeting. Later also advised the Special Committee.</t>
+          <t>Mac-Gray's outside legal counsel; earliest reported acting at the 05/09/2013 board meeting, where the board formed the Transaction Committee to pick a financial adviser for a strategic-alternatives review.</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>“Goodwin Procter LLP, outside legal counsel to Mac-Gray” (p. 27)</t>
+          <t>representatives from BofA Merrill Lynch and Goodwin Procter LLP, outside legal counsel to Mac-Gray, were also in attendance for all or portions of the meeting (p. 27)</t>
         </is>
       </c>
       <c r="R4" s="2" t="n"/>
@@ -759,18 +762,18 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>05/09/2013</t>
+          <t>05/15/2013</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Mac-Gray</t>
+          <t>BofA Merrill Lynch</t>
         </is>
       </c>
       <c r="D5" s="2" t="n"/>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Target sale decision</t>
+          <t>Adviser ended</t>
         </is>
       </c>
       <c r="F5" s="2" t="n">
@@ -789,24 +792,24 @@
       <c r="O5" s="2" t="n"/>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>Board discussed a possible sale process and its risks (leaks, disclosure to competitors); formed a Transaction Committee (Bullock, Daoust) to recommend a financial adviser for a strategic-alternatives review incl. a sale. Qualification: sale-process decision deferred.</t>
+          <t>Mac-Gray terminated BofA's 2011-2012 Discussions engagement (decided by the Transaction Committee 05/14/2013) because BofA was being invited to pitch for the new strategic-alternatives mandate and the CSC sale process had ended.</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>“The Board concluded that it would discuss the review of strategic alternatives, including engaging in a potential sale process, at its next meeting” (p. 28)</t>
+          <t>On May 15, 2013, Mac-Gray sent a letter to BofA Merrill Lynch terminating their engagement in connection with the 2011-2012 Discussions. (p. 29)</t>
         </is>
       </c>
       <c r="R5" s="2" t="n"/>
       <c r="S5" s="2" t="n"/>
       <c r="T5" s="3" t="n">
-        <v>41403</v>
+        <v>41409</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>41403</v>
+        <v>41409</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>41403</v>
+        <v>41409</v>
       </c>
     </row>
     <row r="6">
@@ -815,7 +818,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>05/15/2013</t>
+          <t>05/30/2013</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -826,7 +829,7 @@
       <c r="D6" s="2" t="n"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Adviser ended</t>
+          <t>Adviser</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
@@ -845,24 +848,24 @@
       <c r="O6" s="2" t="n"/>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>Mac-Gray terminated BofA's 2011–2012 Discussions engagement letter (Transaction Committee decision 05/14), because BofA was to pitch for the new sale mandate and the CSC sale had ended.</t>
+          <t>Board approved engaging BofA as Mac-Gray's financial adviser for the strategic-alternatives review, including a potential sale, after a three-bank pitch; engagement letter signed 05/31/2013 barred BofA from financing buyers without consent.</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>“Mac-Gray sent a letter to BofA Merrill Lynch terminating their engagement in connection with the 2011-2012 Discussions” (p. 29)</t>
+          <t>Based on the recommendation of the Transaction Committee, the Board unanimously approved the engagement of BofA Merrill Lynch on the terms discussed at this meeting. (p. 29)</t>
         </is>
       </c>
       <c r="R6" s="2" t="n"/>
       <c r="S6" s="2" t="n"/>
       <c r="T6" s="3" t="n">
-        <v>41409</v>
+        <v>41424</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>41409</v>
+        <v>41424</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>41409</v>
+        <v>41424</v>
       </c>
     </row>
     <row r="7">
@@ -876,13 +879,13 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>BofA Merrill Lynch</t>
+          <t>Moab Partners, L.P. (with affiliates)</t>
         </is>
       </c>
       <c r="D7" s="2" t="n"/>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Adviser</t>
+          <t>Activist</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
@@ -901,12 +904,12 @@
       <c r="O7" s="2" t="n"/>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>Re-engaged as Mac-Gray's (sole) financial adviser for the strategic-alternatives review incl. a sale, chosen over two other banks (pitches 05/22, 05/29). Letter signed 05/31 bars it from financing buyers without consent. Fee about $8.1m (p. 51).</t>
+          <t>Moab won a proxy contest: its nominees Rothenberg (Moab's co-founder and General Partner) and Hyman replaced two incumbents at the annual meeting. Moab held about 9% (as of 06/12/2013). The filing does not say Moab pressed for a sale.</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>“the Board unanimously approved the engagement of BofA Merrill Lynch on the terms discussed at this meeting” (p. 29)</t>
+          <t>the Mac-Gray stockholders elected as directors Michael M. Rothenberg and James E. Hyman, candidates nominated by Mac-Gray's stockholder, Moab Partners, L.P. and certain of its affiliates (p. 29)</t>
         </is>
       </c>
       <c r="R7" s="2" t="n"/>
@@ -927,18 +930,22 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>05/30/2013</t>
+          <t>06/21/2013</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Moab Partners, L.P. (Moab)</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n"/>
+          <t>Party A</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Activist</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
@@ -947,34 +954,56 @@
       <c r="G8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="2" t="n"/>
-      <c r="I8" s="2" t="n"/>
-      <c r="J8" s="2" t="n"/>
-      <c r="K8" s="2" t="n"/>
-      <c r="L8" s="2" t="n"/>
-      <c r="M8" s="2" t="n"/>
+      <c r="H8" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="2" t="n"/>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>Moab (about 9% holder, per 06/12) won a proxy contest: its nominees Rothenberg (Moab general partner) and Hyman joined the Board. Moab later sought a possible equity rollover (#18, #49); Rothenberg excluded from sale deliberations.</t>
+          <t>Conditions unclear: the filing reports no financing or diligence terms. Unsolicited written proposal to the board, before any outreach or NDA; the Special Committee expected Party A to raise it after diligence.</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>“the Mac-Gray stockholders elected as directors Michael M. Rothenberg and James E. Hyman, candidates nominated by Mac-Gray's stockholder, Moab Partners, L.P.” (p. 29)</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="n"/>
+          <t>Party A submitted an unsolicited proposal to the Mac-Gray Board of Directors offering to purchase Mac-Gray for an all-cash purchase price of $17.00 to $19.00 per share (p. 30)</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
       <c r="S8" s="2" t="n"/>
       <c r="T8" s="3" t="n">
-        <v>41424</v>
+        <v>41446</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>41424</v>
+        <v>41446</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>41424</v>
+        <v>41446</v>
       </c>
     </row>
     <row r="9">
@@ -983,22 +1012,18 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>06/21/2013</t>
+          <t>06/24/2013</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Party A</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Mac-Gray</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n"/>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Target sale decision</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
@@ -1007,56 +1032,34 @@
       <c r="G9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="I9" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>Unclear</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="H9" s="2" t="n"/>
+      <c r="I9" s="2" t="n"/>
+      <c r="J9" s="2" t="n"/>
+      <c r="K9" s="2" t="n"/>
+      <c r="L9" s="2" t="n"/>
+      <c r="M9" s="2" t="n"/>
       <c r="N9" s="2" t="n"/>
       <c r="O9" s="2" t="n"/>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>Diligence open per narrative: no confidentiality agreement or diligence until 08/05 (#27). Unsolicited written proposal to the Board; Party A enters the process. Financing not stated.</t>
+          <t>Board formed a six-member Special Committee (MacDonald and Rothenberg excluded). The Committee concluded it should consider a potential sale, to be weighed against remaining stand-alone; buybacks and a special dividend were rejected.</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>“Party A submitted an unsolicited proposal to the Mac-Gray Board of Directors offering to purchase Mac-Gray for an all-cash purchase price of $17.00 to $19.00 per share” (p. 30)</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
+          <t>the Special Committee concluded that it would be in the best interests of stockholders to consider a potential sale of Mac-Gray (p. 31)</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="n"/>
       <c r="S9" s="2" t="n"/>
       <c r="T9" s="3" t="n">
-        <v>41446</v>
+        <v>41449</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>41446</v>
+        <v>41449</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>41446</v>
+        <v>41449</v>
       </c>
     </row>
     <row r="10">
@@ -1076,14 +1079,14 @@
       <c r="D10" s="2" t="n"/>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Target sale decision</t>
+          <t>Round opened</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" s="2" t="n"/>
       <c r="I10" s="2" t="n"/>
@@ -1095,15 +1098,19 @@
       <c r="O10" s="2" t="n"/>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>Board excluded CEO MacDonald and Rothenberg (possible rollover partners) and formed a six-member independent Special Committee. Committee decided to consider a sale against the stand-alone plan and to approach 50 parties (15 strategic, 35 financial). Projections presented.</t>
+          <t>Special Committee decided to approach 50 parties (15 strategic, 35 financial, including CSC/Pamplona and Party A); BofA began outreach within days (first NDA 06/28/2013). NDA signers received an informational package and were asked for preliminary indications by 07/23/2013.</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>“the Special Committee concluded that it would be in the best interests of stockholders to consider a potential sale of Mac-Gray” (p. 31)</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="n"/>
+          <t>BofA Merrill Lynch contacted the strategic and financial parties identified at the June 24th Special Committee meeting (p. 32)</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
       <c r="S10" s="2" t="n"/>
       <c r="T10" s="3" t="n">
         <v>41449</v>
@@ -1121,18 +1128,22 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>06/24/2013–06/28/2013 (outreach begins)</t>
+          <t>during the weeks after 06/24/2013</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Mac-Gray</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="n"/>
+          <t>13 other potential strategic buyers</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Round opened</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
@@ -1146,24 +1157,22 @@
       <c r="J11" s="2" t="n"/>
       <c r="K11" s="2" t="n"/>
       <c r="L11" s="2" t="n"/>
-      <c r="M11" s="2" t="n"/>
+      <c r="M11" s="2" t="n">
+        <v>13</v>
+      </c>
       <c r="N11" s="2" t="n"/>
       <c r="O11" s="2" t="n"/>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>BofA began contacting the 50 parties chosen on 06/24 over the following weeks; calls with Party A and Pamplona reported by 06/28. Confidentiality signers received an information package and a request for preliminary indications (#16).</t>
+          <t>Target outreach by BofA. The filing's total of 15 strategic parties approached includes CSC/Pamplona (own row) and Party A (first contacted 04/08/2013, #2; BofA spoke to it again by 06/28/2013). None of these 13 signed an NDA (only two strategic signers).</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>“BofA Merrill Lynch contacted the strategic and financial parties identified at the June 24th Special Committee meeting” (p. 32)</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
+          <t>and Party A, to solicit potential interest in a transaction with Mac-Gray, 15 of which were potential strategic buyers and 35 of which were potential financial buyers (p. 32)</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="n"/>
       <c r="S11" s="2" t="n"/>
       <c r="T11" s="3" t="n">
         <v>41449</v>
@@ -1171,9 +1180,7 @@
       <c r="U11" s="3" t="n">
         <v>41449</v>
       </c>
-      <c r="V11" s="3" t="n">
-        <v>41453</v>
-      </c>
+      <c r="V11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -1181,17 +1188,17 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>during the several weeks after 06/24/2013</t>
+          <t>during the weeks after 06/24/2013</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>13 other strategic parties</t>
+          <t>35 potential financial buyers, including private equity firms</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1211,18 +1218,18 @@
       <c r="K12" s="2" t="n"/>
       <c r="L12" s="2" t="n"/>
       <c r="M12" s="2" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="N12" s="2" t="n"/>
       <c r="O12" s="2" t="n"/>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>Target outreach. Total 50 = 15 strategic + 35 financial, incl. Party A (first contacted 04/08, #2; spoke again 06/28, citing synergies and financing sources) and CSC/Pamplona (#14): 15 − 2 = 13. Responses not reported.</t>
+          <t>Target outreach by BofA. Includes Party B and Party C. 18 of the 35 later signed NDAs; the rest did not.</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>“50 parties, including CSC and Pamplona, who together we refer to as CSC/Pamplona, and Party A, to solicit potential interest in a transaction with Mac-Gray” (p. 32)</t>
+          <t>35 of which were potential financial buyers, including private equity firms (p. 32)</t>
         </is>
       </c>
       <c r="R12" s="2" t="n"/>
@@ -1241,17 +1248,17 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>during the several weeks after 06/24/2013</t>
+          <t>by 06/28/2013</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>35 financial parties (incl. Party B, Party C)</t>
+          <t>CSC/Pamplona</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1271,33 +1278,31 @@
       <c r="K13" s="2" t="n"/>
       <c r="L13" s="2" t="n"/>
       <c r="M13" s="2" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="N13" s="2" t="n"/>
       <c r="O13" s="2" t="n"/>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Target outreach to 35 financial buyers, incl. private equity firms. Party B and Party C assumed to be among them (filing does not say so expressly; Q4). Rows reconcile to 50: 35 + 13 (#11) + CSC/Pamplona + Party A.</t>
+          <t>Target outreach: BofA, as instructed, spoke with Pamplona, which was interested in an acquisition by its portfolio company CSC and said diligence would be minimal. In the same report, Party A cited synergies and was speaking to financing sources.</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>“15 of which were potential strategic buyers and 35 of which were potential financial buyers, including private equity firms” (p. 32)</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>Q4</t>
-        </is>
-      </c>
+          <t>BofA Merrill Lynch also reported that they had spoken with representatives of Pamplona, as instructed by the Special Committee, who expressed interest in a transaction (p. 32)</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="n"/>
       <c r="S13" s="2" t="n"/>
       <c r="T13" s="3" t="n">
-        <v>41449</v>
+        <v>41451</v>
       </c>
       <c r="U13" s="3" t="n">
         <v>41449</v>
       </c>
-      <c r="V13" s="2" t="n"/>
+      <c r="V13" s="3" t="n">
+        <v>41453</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -1305,22 +1310,18 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>06/24/2013–08/24/2013 (over the next two months)</t>
+          <t>by 06/28/2013</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>16 other financial NDA signers</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
+          <t>Mac-Gray</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n"/>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>NDA signed</t>
+          <t>Deadline set</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
@@ -1334,35 +1335,37 @@
       <c r="J14" s="2" t="n"/>
       <c r="K14" s="2" t="n"/>
       <c r="L14" s="2" t="n"/>
-      <c r="M14" s="2" t="n">
-        <v>16</v>
-      </c>
+      <c r="M14" s="2" t="n"/>
       <c r="N14" s="2" t="n"/>
-      <c r="O14" s="2" t="n"/>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>Filing total: 20 signers over two months = 2 strategic (Party A #27, CSC/Pamplona #19) + 18 financial incl. Party B (#15), Party C (#17); residual 18 − 2 = 16. Dates not reported. Standstills had sunset provisions. Each received the information package.</t>
+          <t>NDA signers were told to submit preliminary indications by 07/23/2013 (valuation, financing, conditions, diligence focus). Date inferred: the instruction came with the informational package, and the first package reported went to Party B on 06/28/2013.</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>“a total of 20 potential bidders, including two strategic bidders (Party A and CSC/Pamplona) and 18 financial bidders (including Party B and Party C), entered into confidentiality agreements” (p. 32)</t>
+          <t>furnished an informational package for the purpose of providing potential bidders with data to formulate a preliminary indication of interest, which they were instructed to submit by July 23, 2013 (p. 32)</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="S14" s="2" t="n"/>
       <c r="T14" s="3" t="n">
-        <v>41449</v>
+        <v>41453</v>
       </c>
       <c r="U14" s="3" t="n">
         <v>41449</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>41510</v>
+        <v>41453</v>
       </c>
     </row>
     <row r="15">
@@ -1371,22 +1374,22 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>by 06/28/2013</t>
+          <t>06/28/2013</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>CSC/Pamplona</t>
+          <t>Party B</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>NDA signed</t>
         </is>
       </c>
       <c r="F15" s="2" t="n">
@@ -1407,21 +1410,21 @@
       <c r="O15" s="2" t="n"/>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>BofA, as instructed, called Pamplona, which was interested incl. in an acquisition by its portfolio company CSC; said diligence would be minimal given its familiarity. One bidder unit; filing classes it strategic.</t>
+          <t>Confidentiality and standstill agreement with a sunset clause; Party B received the informational package. Entry.</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>“Pamplona emphasized that business and legal due diligence would be minimal given its familiarity with Mac-Gray and the industry generally” (p. 32)</t>
+          <t>Later on June 28, 2013, Party B, entered into a confidentiality and standstill agreement with Mac-Gray (p. 32)</t>
         </is>
       </c>
       <c r="R15" s="2" t="n"/>
       <c r="S15" s="2" t="n"/>
       <c r="T15" s="3" t="n">
-        <v>41451</v>
+        <v>41453</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>41449</v>
+        <v>41453</v>
       </c>
       <c r="V15" s="3" t="n">
         <v>41453</v>
@@ -1433,12 +1436,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>06/28/2013</t>
+          <t>06/30/2013</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Party B</t>
+          <t>Party C</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1469,24 +1472,24 @@
       <c r="O16" s="2" t="n"/>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Enters: confidentiality and standstill agreement; received the information package for a preliminary indication. Financial bidder (p. 32).</t>
+          <t>Confidentiality and standstill agreement; Party C received the informational package. Entry.</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>“Party B, entered into a confidentiality and standstill agreement with Mac-Gray and was provided with an informational package” (p. 32)</t>
+          <t>On June 30, 2013, Party C entered into a confidentiality and standstill agreement with Mac-Gray (p. 32)</t>
         </is>
       </c>
       <c r="R16" s="2" t="n"/>
       <c r="S16" s="2" t="n"/>
       <c r="T16" s="3" t="n">
-        <v>41453</v>
+        <v>41455</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>41453</v>
+        <v>41455</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>41453</v>
+        <v>41455</v>
       </c>
     </row>
     <row r="17">
@@ -1495,18 +1498,18 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>06/28/2013 (with information packages)</t>
+          <t>07/03/2013</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Mac-Gray</t>
+          <t>Moab Partners (Rothenberg) and CSC/Pamplona</t>
         </is>
       </c>
       <c r="D17" s="2" t="n"/>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Deadline set</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
@@ -1522,35 +1525,27 @@
       <c r="L17" s="2" t="n"/>
       <c r="M17" s="2" t="n"/>
       <c r="N17" s="2" t="n"/>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="O17" s="2" t="n"/>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>Preliminary indications due 07/23/2013, to address valuation, financing, conditions and diligence focus. The instruction came with each signer's information package; dated at the first reported package (Party B, #15).</t>
+          <t>Rollover approach: Rothenberg told Goodwin that he had discussed a possible Moab equity rollover with Pamplona, and that Pamplona would ask for its NDA to let it share its bid with Moab, with Moab dealing only with CSC/Pamplona.</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>“which they were instructed to submit by July 23, 2013” (p. 32)</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
+          <t>Pamplona would be requesting that any confidentiality agreement CSC/Pamplona execute with Mac-Gray permit CSC and Pamplona to discuss their bid and evaluation material with Moab (p. 32)</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="n"/>
       <c r="S17" s="2" t="n"/>
       <c r="T17" s="3" t="n">
-        <v>41453</v>
+        <v>41458</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>41453</v>
+        <v>41458</v>
       </c>
       <c r="V17" s="3" t="n">
-        <v>41453</v>
+        <v>41458</v>
       </c>
     </row>
     <row r="18">
@@ -1559,22 +1554,18 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>06/30/2013</t>
+          <t>07/06/2013</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Party C</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
+          <t>Mac-Gray</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n"/>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>NDA signed</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F18" s="2" t="n">
@@ -1588,31 +1579,29 @@
       <c r="J18" s="2" t="n"/>
       <c r="K18" s="2" t="n"/>
       <c r="L18" s="2" t="n"/>
-      <c r="M18" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M18" s="2" t="n"/>
       <c r="N18" s="2" t="n"/>
       <c r="O18" s="2" t="n"/>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>Enters: confidentiality and standstill agreement; received the information package. Financial bidder (p. 32).</t>
+          <t>Special Committee refused the Moab–CSC/Pamplona exclusive rollover arrangement, keeping Moab's stake available to all bidders; told CSC/Pamplona and Rothenberg that rollover talks with anyone were premature but would be allowed later.</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>“Party C entered into a confidentiality and standstill agreement with Mac-Gray and was provided with an informational package” (p. 32)</t>
+          <t>the Special Committee decided to deny the exclusivity request at this stage of the process so that the potential equity rollover of Moab's shares could be available (p. 33)</t>
         </is>
       </c>
       <c r="R18" s="2" t="n"/>
       <c r="S18" s="2" t="n"/>
       <c r="T18" s="3" t="n">
-        <v>41455</v>
+        <v>41461</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>41455</v>
+        <v>41461</v>
       </c>
       <c r="V18" s="3" t="n">
-        <v>41455</v>
+        <v>41461</v>
       </c>
     </row>
     <row r="19">
@@ -1621,18 +1610,22 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>07/06/2013</t>
+          <t>07/11/2013</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Mac-Gray</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="n"/>
+          <t>CSC/Pamplona</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>NDA signed</t>
         </is>
       </c>
       <c r="F19" s="2" t="n">
@@ -1646,29 +1639,31 @@
       <c r="J19" s="2" t="n"/>
       <c r="K19" s="2" t="n"/>
       <c r="L19" s="2" t="n"/>
-      <c r="M19" s="2" t="n"/>
+      <c r="M19" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N19" s="2" t="n"/>
       <c r="O19" s="2" t="n"/>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>Refused rollover partnership: on 07/03 Rothenberg said Pamplona would seek confidentiality terms letting CSC/Pamplona share its bid and data with Moab, Moab dealing exclusively with them. Special Committee refused; rollover talks premature with anyone, allowed later.</t>
+          <t>Confidentiality and standstill agreement (a letter agreement among Pamplona Capital Management LLC, Parent and Mac-Gray, per merger agreement s.6.17, Annex A); informational package provided. Entry. Party A's NDA talks stalled over non-solicitation terms 07/11–07/23.</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>“the Special Committee decided to deny the exclusivity request at this stage of the process” (p. 33)</t>
+          <t>On July 11, 2013, CSC/Pamplona entered into a confidentiality and standstill agreement with Mac-Gray (p. 33)</t>
         </is>
       </c>
       <c r="R19" s="2" t="n"/>
       <c r="S19" s="2" t="n"/>
       <c r="T19" s="3" t="n">
-        <v>41461</v>
+        <v>41466</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>41461</v>
+        <v>41466</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>41461</v>
+        <v>41466</v>
       </c>
     </row>
     <row r="20">
@@ -1677,17 +1672,17 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>07/11/2013</t>
+          <t>06/24/2013 to about 08/24/2013 ("over the next two months")</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>CSC/Pamplona</t>
+          <t>16 other financial NDA signers</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1707,30 +1702,34 @@
       <c r="K20" s="2" t="n"/>
       <c r="L20" s="2" t="n"/>
       <c r="M20" s="2" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="N20" s="2" t="n"/>
       <c r="O20" s="2" t="n"/>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Enters: confidentiality and standstill agreement signed by CSC/Pamplona; received the information package. CSC is a laundry operator owned by Pamplona (private equity fund).</t>
+          <t>Count: 16 = 20 NDA signers (2 strategic, 18 financial) minus the individually recorded Party A, CSC/Pamplona, Party B and Party C. Signing dates not reported; some may have signed after 07/23/2013. Sort date moved to 07/23/2013 to precede the inferred exit.</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>“CSC/Pamplona entered into a confidentiality and standstill agreement with Mac-Gray and were provided with an informational package” (p. 33)</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="n"/>
+          <t>a total of 20 potential bidders, including two strategic bidders (Party A and CSC/Pamplona) and 18 financial bidders (including Party B and Party C), entered into confidentiality agreements (p. 32)</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
       <c r="S20" s="2" t="n"/>
       <c r="T20" s="3" t="n">
-        <v>41466</v>
+        <v>41478</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>41466</v>
+        <v>41449</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>41466</v>
+        <v>41510</v>
       </c>
     </row>
     <row r="21">
@@ -1791,12 +1790,12 @@
       <c r="O21" s="2" t="n"/>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>Diligence open per narrative: management presentation 08/12; limited data-room access, customer data reserved (#28). Preliminary indication; financing and conditions not stated.</t>
+          <t>Conditions unclear: preliminary indication with no stated conditions, though diligence was still open. On time. Pamplona had earlier said its diligence would be minimal.</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>“CSC/Pamplona submitted a preliminary indication of interest at an all-cash purchase price of $18.50 per share” (p. 33)</t>
+          <t>On July 23, 2013, CSC/Pamplona submitted a preliminary indication of interest at an all-cash purchase price of $18.50 per share. (p. 33)</t>
         </is>
       </c>
       <c r="R21" s="2" t="n"/>
@@ -1847,12 +1846,12 @@
       <c r="O22" s="2" t="n"/>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>Preliminary indications due. CSC/Pamplona on time (#20); late: Party B and Party C on 07/24 (#22, #23), Party C written revision 07/25 (#26); all reviewed 07/25. No bids reported from the other 16 signers.</t>
+          <t>Round 1 due date for preliminary indications. CSC/Pamplona bid on time; Party B and Party C bid on 07/24–07/25 and were still considered (late bids accepted).</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>“which they were instructed to submit by July 23, 2013” (p. 32)</t>
+          <t>which they were instructed to submit by July 23, 2013 (p. 32)</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
@@ -1877,12 +1876,12 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>07/24/2013</t>
+          <t>by 07/23/2013</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Party B</t>
+          <t>16 other financial NDA signers</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1892,7 +1891,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Did not submit</t>
         </is>
       </c>
       <c r="F23" s="2" t="n">
@@ -1901,56 +1900,46 @@
       <c r="G23" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H23" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="I23" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>Unclear</t>
-        </is>
-      </c>
+      <c r="H23" s="2" t="n"/>
+      <c r="I23" s="2" t="n"/>
+      <c r="J23" s="2" t="n"/>
+      <c r="K23" s="2" t="n"/>
+      <c r="L23" s="2" t="n"/>
       <c r="M23" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N23" s="2" t="n"/>
-      <c r="O23" s="2" t="n"/>
+        <v>16</v>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>Diligence open per narrative: management presentation 08/06; data-room diligence 08/06–08/27. Preliminary indication, one day after the 07/23 due date. Financing not stated.</t>
+          <t>Inferred: 20 signers − Party A (no NDA yet) − 3 submitters = 16; only B, C and CSC/Pamplona indications (plus Party A's 06/21 proposal) were reviewed 07/25. Any member signing after 07/23 would instead have been excluded when four advanced.</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>“Party B submitted a preliminary indication of interest at an all-cash purchase price of $17.00 to $18.00 per share” (p. 33)</t>
+          <t>representatives of BofA Merrill Lynch reviewed the preliminary indications of interest received from Party B, Party C and CSC/Pamplona as well as the Party A June 21 proposal (p. 33)</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="S23" s="2" t="n"/>
       <c r="T23" s="3" t="n">
-        <v>41479</v>
-      </c>
-      <c r="U23" s="3" t="n">
-        <v>41479</v>
-      </c>
+        <v>41478</v>
+      </c>
+      <c r="U23" s="2" t="n"/>
       <c r="V23" s="3" t="n">
-        <v>41479</v>
+        <v>41478</v>
       </c>
     </row>
     <row r="24">
@@ -1964,7 +1953,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Party C</t>
+          <t>Party B</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1984,10 +1973,10 @@
         <v>1</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
@@ -2011,12 +2000,12 @@
       <c r="O24" s="2" t="n"/>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>Diligence open per narrative: management presentation 08/08. Oral preliminary indication by phone to BofA, one day after the due date.</t>
+          <t>Conditions unclear: no conditions reported, but diligence was still open. Written preliminary indication one day after the 07/23 due date; reviewed 07/25.</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>“representatives from Party C called BofA Merrill Lynch and presented an oral preliminary indication of interest at an all-cash purchase price of $15.00 to $17.00 per share” (p. 33)</t>
+          <t>On July 24, 2013, Party B submitted a preliminary indication of interest at an all-cash purchase price of $17.00 to $18.00 per share. (p. 33)</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
@@ -2041,12 +2030,12 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>by 07/25/2013</t>
+          <t>07/24/2013</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>16 other financial NDA signers</t>
+          <t>Party C</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -2056,7 +2045,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Dropped by target</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F25" s="2" t="n">
@@ -2065,46 +2054,56 @@
       <c r="G25" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H25" s="2" t="n"/>
-      <c r="I25" s="2" t="n"/>
-      <c r="J25" s="2" t="n"/>
-      <c r="K25" s="2" t="n"/>
-      <c r="L25" s="2" t="n"/>
+      <c r="H25" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
       <c r="M25" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N25" s="2" t="n"/>
+      <c r="O25" s="2" t="n"/>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>Not among the four bidders advanced on 07/25 (#25); no bids from them reported. 20 signers − 4 advanced = 16. Signing dates unknown: any later signer was outside the four-bidder stage (08/27 letters to four only). Q4.</t>
+          <t>Conditions unclear: no conditions reported, diligence still open. Oral preliminary indication made by phone to BofA one day after the due date; reviewed 07/25.</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>“reach out to each of the four interested bidders and arrange management meetings” (p. 34)</t>
+          <t>representatives from Party C called BofA Merrill Lynch and presented an oral preliminary indication of interest at an all-cash purchase price of $15.00 to $17.00 per share (p. 33)</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="S25" s="2" t="n"/>
       <c r="T25" s="3" t="n">
-        <v>41480</v>
-      </c>
-      <c r="U25" s="2" t="n"/>
+        <v>41479</v>
+      </c>
+      <c r="U25" s="3" t="n">
+        <v>41479</v>
+      </c>
       <c r="V25" s="3" t="n">
-        <v>41480</v>
+        <v>41479</v>
       </c>
     </row>
     <row r="26">
@@ -2143,12 +2142,12 @@
       <c r="O26" s="2" t="n"/>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>Committee found indications low; chose staged disclosure and advanced four: Party A (if it signed a confidentiality agreement), Party B, Party C, CSC/Pamplona, for management meetings (held 08/06–08/14 for all four), then revised indications.</t>
+          <t>Finding the indications lower than expected, the Special Committee advanced four bidders (Party A, if it signed an NDA; B; C; CSC/Pamplona) to management meetings, with staged disclosure of sensitive information, and then revised indications. All four had presentations 08/06–08/14.</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>“authorized and instructed BofA Merrill Lynch to proceed with the staged disclosure as discussed at this meeting and to reach out to each of the four interested bidders” (p. 34)</t>
+          <t>authorized and instructed BofA Merrill Lynch to proceed with the staged disclosure as discussed at this meeting and to reach out to each of the four interested bidders (p. 34)</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
@@ -2225,17 +2224,17 @@
       <c r="O27" s="2" t="n"/>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>Diligence open per narrative: management presentation 08/08. Written indication after the committee meeting, replacing the oral range (#23): top cut from $17.00 to $16.50.</t>
+          <t>Conditions unclear: no conditions reported, diligence still open. Written indication revising Party C's oral 07/24 range (#24); made after the 07/25 Special Committee meeting and answering the round 1 request.</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>“Party C submitted a written indication of interest at an all-cash purchase price of $16.00 to $16.50 per share” (p. 34)</t>
+          <t>Later on July 25, 2013, Party C submitted a written indication of interest at an all-cash purchase price of $16.00 to $16.50 per share. (p. 34)</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1; Q2</t>
         </is>
       </c>
       <c r="S27" s="2" t="n"/>
@@ -2291,12 +2290,12 @@
       <c r="O28" s="2" t="n"/>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>Catch-up access: after talks on non-solicitation terms stalled (07/11–07/23) and resumed 07/27 (filing prints '2103'), Party A signed and got the information package to improve its 06/21 proposal (#8). Already entered at #8.</t>
+          <t>Catch-up access for a late entrant: NDA talks resumed 07/27 once non-solicitation terms were agreed. Party A then received the informational package, to improve its 06/21 proposal. Already live since #7.</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>“Party A entered into a confidentiality and standstill agreement with Mac-Gray and was provided with an informational package” (p. 34)</t>
+          <t>On August 5, 2013, Party A entered into a confidentiality and standstill agreement with Mac-Gray and was provided with an informational package (p. 34)</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
@@ -2351,12 +2350,12 @@
       <c r="O29" s="2" t="n"/>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>Staged information access: financial bidders Party B and Party C got broad data-room access; strategic bidders Party A and CSC/Pamplona got limited access, customer data incl. locations reserved for later (07/25 staging). Strategics also discussed synergies with management.</t>
+          <t>Information access differed by type: financial bidders B and C got broad data-room access; strategic bidders A and CSC/Pamplona got limited access, with customer data (including locations) held back, but had synergy talks with management.</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>“Party B and Party C, in light of the fact that they were financial bidders, were given broad access to an electronic data site” (p. 34)</t>
+          <t>Party B and Party C, in light of the fact that they were financial bidders, were given broad access to an electronic data site (p. 34)</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
@@ -2366,7 +2365,7 @@
       </c>
       <c r="S29" s="2" t="n"/>
       <c r="T29" s="3" t="n">
-        <v>41492</v>
+        <v>41502</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>41492</v>
@@ -2411,17 +2410,17 @@
       <c r="O30" s="2" t="n"/>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>BofA letters to Party A, Party B, Party C and CSC/Pamplona (authorized 08/15): revised written proposals due 09/09/2013 to go on to in-depth evaluation; address valuation, financing, approvals, covenants, diligence focus.</t>
+          <t>BofA's letter to all four bidders set 09/09/2013 as the due date for revised written proposals (valuation, financing, approvals, covenants, diligence), needed to go on to in-depth diligence. Authorized 08/15. Follow-up diligence calls: B 08/27, C 08/29, A 09/03.</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>“instructing such bidders to submit revised written proposals no later than September 9, 2013 if such bidders wished to proceed further in the process” (p. 35)</t>
+          <t>instructing such bidders to submit revised written proposals no later than September 9, 2013 if such bidders wished to proceed further in the process (p. 35)</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="S30" s="2" t="n"/>
@@ -2483,7 +2482,7 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>Unclear</t>
+          <t>Heavy</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
@@ -2493,15 +2492,19 @@
       <c r="O31" s="2" t="n"/>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>Diligence open per narrative: customer data still reserved; diligence continued 09/11–09/18. Pamplona committed to provide 100% of capital. Requested two-week exclusivity. Revised indication.</t>
+          <t>Heavy: asked for two weeks of exclusive negotiations. Pamplona committed 100% of the required capital. A revised indication, on time; the next stage was to be in-depth diligence.</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>“CSC/Pamplona submitted a revised indication of interest with an all-cash purchase price of $19.50 per share, indicating that Pamplona was committed to provide 100% of the capital” (p. 35)</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="n"/>
+          <t>CSC/Pamplona submitted a revised indication of interest with an all-cash purchase price of $19.50 per share, indicating that Pamplona was committed to provide 100% of the capital required (p. 35)</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
       <c r="S31" s="2" t="n"/>
       <c r="T31" s="3" t="n">
         <v>41526</v>
@@ -2571,12 +2574,12 @@
       <c r="O32" s="2" t="n"/>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>No firm financing commitment: to be financed by affiliated-fund equity plus third-party debt (p. 35). Revised indication.</t>
+          <t>Heavy: no firm financing commitment; to be financed by equity from affiliated funds plus third-party debt. A revised indication, on time.</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>“Party B also submitted a revised indication of interest with an all-cash purchase price of $18.50 per share” (p. 35)</t>
+          <t>Party B also submitted a revised indication of interest with an all-cash purchase price of $18.50 per share and proposed to finance the transaction with a combination of equity (p. 35)</t>
         </is>
       </c>
       <c r="R32" s="2" t="n"/>
@@ -2627,17 +2630,17 @@
       <c r="O33" s="2" t="n"/>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>Revised proposals due. CSC/Pamplona and Party B on time (#30, #31); late: Party A and Party C on 09/10 (#33, #34), all reviewed by the committee 09/11.</t>
+          <t>Round 2 due date. CSC/Pamplona and Party B bid on time; Party A and Party C bid on 09/10 and all four were reviewed on 09/11 (late bids accepted).</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>“submit revised written proposals no later than September 9, 2013” (p. 35)</t>
+          <t>submit revised written proposals no later than September 9, 2013 (p. 35)</t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="S33" s="2" t="n"/>
@@ -2709,17 +2712,17 @@
       <c r="O34" s="2" t="n"/>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>No firm financing commitment (p. 35); to be funded by existing credit facilities or affiliated equity. Revised indication, one day late; floor raised from $17.00 (#8).</t>
+          <t>Heavy: no firm financing commitment (to use outstanding credit facilities or affiliated equity). A revised indication one day after the due date; its range equals its 06/21 proposal (#7).</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>“Party A submitted a revised indication of interest with an all-cash purchase price of $18.00 to $19.00 per share, to be financed by outstanding credit facilities or affiliated equity sources” (p. 35)</t>
+          <t>Party A submitted a revised indication of interest with an all-cash purchase price of $18.00 to $19.00 per share, to be financed by outstanding credit facilities or affiliated equity sources. (p. 35)</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="S34" s="2" t="n"/>
@@ -2791,17 +2794,17 @@
       <c r="O35" s="2" t="n"/>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>No firm financing commitment (p. 35). Oral revised indication by phone to BofA, one day late; up from $16.00–16.50 (#26).</t>
+          <t>Heavy: no firm financing commitment. A revised oral indication by phone to BofA, one day after the due date; up from its $16.00–$16.50 written range (#26).</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>“a representative of Party C indicated that it was submitting a revised oral indication of interest with an all-cash purchase price of $16.00 to $17.00 per share” (p. 35)</t>
+          <t>a representative of Party C indicated that it was submitting a revised oral indication of interest with an all-cash purchase price of $16.00 to $17.00 per share (p. 35)</t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="S35" s="2" t="n"/>
@@ -2826,7 +2829,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Stewart G. MacDonald, Jr. (CEO, large holder)</t>
+          <t>Stewart G. MacDonald, Jr. (CEO and major shareholder)</t>
         </is>
       </c>
       <c r="D36" s="2" t="n"/>
@@ -2851,12 +2854,12 @@
       <c r="O36" s="2" t="n"/>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>Rollover refused by holder: MacDonald said he would not roll over shares. BofA reported bidders unlikely to proceed without his express support, so the committee had him fully briefed (09/12); he backed continuing but urged a higher value.</t>
+          <t>Rollover declined: after a limited briefing, MacDonald said he would not roll over any shares. BofA reported that no bidder was likely to proceed without his express support. He was fully briefed on 09/12 and urged seeking a higher value.</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>“Mr. MacDonald indicated that he had decided that he was not interested in rolling over any of his shares in any transaction” (p. 35)</t>
+          <t>Mr. MacDonald indicated that he had decided that he was not interested in rolling over any of his shares in any transaction. (p. 35)</t>
         </is>
       </c>
       <c r="R36" s="2" t="n"/>
@@ -2907,17 +2910,17 @@
       <c r="O37" s="2" t="n"/>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>Committee had BofA call all four (Party A, Party B, Party C, CSC/Pamplona) the same day for final indications due 09/18/2013, saying Mac-Gray might grant one bidder short exclusivity depending on price and deal certainty.</t>
+          <t>Special Committee requested final indications from all four bidders by 09/18/2013. BofA told them by phone on 09/11 that Mac-Gray might grant one bidder short exclusivity depending on price and deal certainty. Diligence continued 09/11–09/18.</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>“request final indications of interest by September 18, 2013” (p. 36)</t>
+          <t>the Special Committee instructed BofA Merrill Lynch to call each of Party A, Party B, Party C and CSC/Pamplona to request final indications of interest by September 18, 2013 (p. 36)</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q1; Q6; Q7</t>
         </is>
       </c>
       <c r="S37" s="2" t="n"/>
@@ -2979,7 +2982,7 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>Unclear</t>
+          <t>Heavy</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
@@ -2989,17 +2992,17 @@
       <c r="O38" s="2" t="n"/>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>Diligence open per narrative: customer data still reserved (#28, #48). Pamplona committed to provide 100% of capital; requested two-week exclusivity. Formal as the answer to the final-indication request, no markup (Q3).</t>
+          <t>Heavy: again asked for two weeks of exclusive negotiations. Pamplona still committed 100% of the capital. Final-round response. Up from $19.50 (#30).</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>“CSC/Pamplona submitted a proposal for an all-cash purchase price of $20.75 per share, reiterating that Pamplona was committed to provide 100% of the capital” (p. 36)</t>
+          <t>CSC/Pamplona submitted a proposal for an all-cash purchase price of $20.75 per share, reiterating that Pamplona was committed to provide 100% of the capital required (p. 36)</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q5; Q7</t>
         </is>
       </c>
       <c r="S38" s="2" t="n"/>
@@ -3034,7 +3037,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Bid reaffirmed</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F39" s="2" t="n">
@@ -3061,7 +3064,7 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>Unclear</t>
+          <t>Heavy</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
@@ -3071,17 +3074,17 @@
       <c r="O39" s="2" t="n"/>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>Diligence open per narrative: customer data reserved; diligence continued 09/11–09/18. By price confirmation: Party A told BofA by phone its 09/10 range (#33) was its best and final offer. Financing status at this date not reported.</t>
+          <t>Heavy: repeats its 09/10 indication (#33), which had no firm financing commitment. By phone to BofA, Party A called its $18.00–$19.00 its best and final offer, in response to the final-round request. Price unchanged.</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>“its previous indication of interest with an all-cash purchase price of $18.00 to $19.00 per share was its best and final offer” (p. 36)</t>
+          <t>its previous indication of interest with an all-cash purchase price of $18.00 to $19.00 per share was its best and final offer (p. 36)</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="S39" s="2" t="n"/>
@@ -3153,17 +3156,17 @@
       <c r="O40" s="2" t="n"/>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>Diligence open per narrative: diligence continued 09/11–09/18. Bidder values offer at $21.50: $19.00 cash at closing plus options on 10% of new equity, vesting on base-case projections over five years, valued by it at $2.50. Committee expected affiliated equity plus third-party debt (p. 37). Q5.</t>
+          <t>Unclear: financing was expected from affiliated-fund equity plus third-party debt, but no commitment status was reported. $19.00 cash at closing plus options on 10% of new equity, vesting on base-case projections over five years; Party B valued the options at $2.50/share.</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>“a revised indication of interest with a purchase price that Party B valued at $21.50 per share, including $19.00 of cash to be paid at closing” (p. 36)</t>
+          <t>Party B also submitted a revised indication of interest with a purchase price that Party B valued at $21.50 per share, including $19.00 of cash to be paid at closing (p. 36)</t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>Q3; Q5</t>
+          <t>Q7; Q8</t>
         </is>
       </c>
       <c r="S40" s="2" t="n"/>
@@ -3223,12 +3226,12 @@
       <c r="O41" s="2" t="n"/>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>Party C neither revised nor reiterated its $16.00–17.00 indication (#34) by the final-indication due date and gave no reason. Its decision.</t>
+          <t>Party C neither submitted a final indication nor reaffirmed its $16.00–$17.00 indication (#34), and gave no reason. Reported 09/19.</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t>“Party C did not submit a revised indication of interest or reiterate its prior indication of interest” (p. 36)</t>
+          <t>Party C did not submit a revised indication of interest or reiterate its prior indication of interest of an all-cash purchase price of $16.00 to $17.00 per share (p. 36)</t>
         </is>
       </c>
       <c r="R41" s="2" t="n"/>
@@ -3279,17 +3282,17 @@
       <c r="O42" s="2" t="n"/>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>Final indications due. CSC/Pamplona, Party B and Party A (reaffirmation) answered the same day; Party C did not (#40). Committee chose on the bids in hand on 09/19 (#42).</t>
+          <t>Round 3 due date for final indications. Three bids arrived that day; Party C did not respond. The Special Committee acted on the bids in hand on 09/19.</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>“request final indications of interest by September 18, 2013” (p. 36)</t>
+          <t>request final indications of interest by September 18, 2013 (p. 36)</t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="S42" s="2" t="n"/>
@@ -3339,12 +3342,12 @@
       <c r="O43" s="2" t="n"/>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>Preferred bidder and price requirement: committee judged CSC/Pamplona best on value, certainty and no third-party financing, despite Party B's higher face value (option risk); offered exclusivity at $21.25. MacDonald said he would support $21.25.</t>
+          <t>Preferred bidder and price requirement: Special Committee judged CSC/Pamplona most valuable and certain (Party B's options risky, its financing riskier) and offered exclusivity at $21.25/share. MacDonald said he would support $21.25.</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t>“the Special Committee would be prepared to move into exclusivity at a price of $21.25 per share” (p. 37)</t>
+          <t>authorized the Transaction Committee to inform CSC/Pamplona that the Special Committee would be prepared to move into exclusivity at a price of $21.25 per share (p. 37)</t>
         </is>
       </c>
       <c r="R43" s="2" t="n"/>
@@ -3407,7 +3410,7 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>Unclear</t>
+          <t>Heavy</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
@@ -3417,17 +3420,17 @@
       <c r="O44" s="2" t="n"/>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>Diligence open per narrative: customer data not yet released (#48). Pamplona funding 100%, no financing contingency (terms of 09/21–09/23). 'Last and best' answer to #42, conditional on two-week exclusivity; requested MacDonald voting agreements.</t>
+          <t>Heavy: conditioned on two weeks of exclusive negotiations and voting agreements from MacDonald and family. Raised to $21.25 as its last and best offer, the same day the Transaction Committee proposed that price; Pamplona to fund 100%, no financing contingency.</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>“willing to increase their all-cash purchase price to $21.25 per share as a last and best offer, provided that Mac-Gray agree to a two week period of exclusive negotiations” (p. 37)</t>
+          <t>confirm that CSC/Pamplona were willing to increase their all-cash purchase price to $21.25 per share as a last and best offer, provided that Mac-Gray agree to a two week period (p. 37)</t>
         </is>
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q5; Q7</t>
         </is>
       </c>
       <c r="S44" s="2" t="n"/>
@@ -3447,22 +3450,18 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>09/24/2013</t>
+          <t>09/23/2013</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>CSC/Pamplona</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Mac-Gray and Moab Partners (Rothenberg)</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n"/>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Exclusivity changed</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F45" s="2" t="n">
@@ -3476,31 +3475,29 @@
       <c r="J45" s="2" t="n"/>
       <c r="K45" s="2" t="n"/>
       <c r="L45" s="2" t="n"/>
-      <c r="M45" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M45" s="2" t="n"/>
       <c r="N45" s="2" t="n"/>
       <c r="O45" s="2" t="n"/>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>Executed with CSC and Pamplona to 5 p.m. ET 10/12/2013 (authorized 09/23); lapses if they worsen the final proposal: $21.25 cash, $15m reverse termination fee, no financing contingency, Pamplona funding 100%.</t>
+          <t>Rollover permitted: Goodwin told Rothenberg of the CSC/Pamplona negotiations so that Moab could resume rollover talks with CSC/Pamplona. Rothenberg wanted to, and BofA arranged the talks.</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>“CSC, Pamplona and Mac-Gray executed the exclusivity agreement providing for exclusive negotiations until 5 p.m. ET on October 12, 2013” (p. 38)</t>
+          <t>to provide Moab with the opportunity to resume discussions with CSC/Pamplona regarding a possible equity rollover of Moab's shares in the transaction (p. 38)</t>
         </is>
       </c>
       <c r="R45" s="2" t="n"/>
       <c r="S45" s="2" t="n"/>
       <c r="T45" s="3" t="n">
-        <v>41541</v>
+        <v>41540</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>41541</v>
+        <v>41540</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>41541</v>
+        <v>41540</v>
       </c>
     </row>
     <row r="46">
@@ -3509,12 +3506,12 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>by 09/24/2013</t>
+          <t>09/24/2013</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Party A</t>
+          <t>CSC/Pamplona</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -3524,7 +3521,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Dropped by target</t>
+          <t>Exclusivity changed</t>
         </is>
       </c>
       <c r="F46" s="2" t="n">
@@ -3541,24 +3538,16 @@
       <c r="M46" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="O46" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="N46" s="2" t="n"/>
+      <c r="O46" s="2" t="n"/>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>Inferred: live rival when exclusivity with CSC/Pamplona was executed (#44); filing does not say it was told. Its best and final $18.00–19.00 (#38) was below CSC/Pamplona's $21.25.</t>
+          <t>Executed with CSC/Pamplona until 5 p.m. ET 10/12/2013 (authorized 09/23) on its final proposal: $21.25 cash, $15M reverse termination fee, no financing contingency. Exclusivity lapses automatically if the terms are adversely changed.</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>“CSC, Pamplona and Mac-Gray executed the exclusivity agreement providing for exclusive negotiations” (p. 38)</t>
+          <t>CSC, Pamplona and Mac-Gray executed the exclusivity agreement providing for exclusive negotiations until 5 p.m. ET on October 12, 2013 (p. 38)</t>
         </is>
       </c>
       <c r="R46" s="2" t="n"/>
@@ -3567,7 +3556,7 @@
         <v>41541</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>41535</v>
+        <v>41541</v>
       </c>
       <c r="V46" s="3" t="n">
         <v>41541</v>
@@ -3584,12 +3573,12 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Party B</t>
+          <t>Party A</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -3623,22 +3612,24 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>Inferred: live rival when exclusivity with CSC/Pamplona was executed (#44); not reported as told. Its offer, valued by Party B at $21.50 incl. $19.00 cash (#39), lost on certainty (#42).</t>
+          <t>Inferred: displaced when Mac-Gray signed exclusivity with CSC/Pamplona; the filing never mentions Party A in the process again. Its last offer, $18.00–$19.00, was called best and final (#38).</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
         <is>
-          <t>“CSC, Pamplona and Mac-Gray executed the exclusivity agreement providing for exclusive negotiations” (p. 38)</t>
-        </is>
-      </c>
-      <c r="R47" s="2" t="n"/>
+          <t>CSC, Pamplona and Mac-Gray executed the exclusivity agreement providing for exclusive negotiations until 5 p.m. ET on October 12, 2013 (p. 38)</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>Q9</t>
+        </is>
+      </c>
       <c r="S47" s="2" t="n"/>
       <c r="T47" s="3" t="n">
         <v>41541</v>
       </c>
-      <c r="U47" s="3" t="n">
-        <v>41535</v>
-      </c>
+      <c r="U47" s="2" t="n"/>
       <c r="V47" s="3" t="n">
         <v>41541</v>
       </c>
@@ -3649,18 +3640,22 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>09/25/2013</t>
+          <t>by 09/24/2013</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Kirkland &amp; Ellis LLP</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="n"/>
+          <t>Party B</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Adviser</t>
+          <t>Dropped by target</t>
         </is>
       </c>
       <c r="F48" s="2" t="n">
@@ -3674,29 +3669,41 @@
       <c r="J48" s="2" t="n"/>
       <c r="K48" s="2" t="n"/>
       <c r="L48" s="2" t="n"/>
-      <c r="M48" s="2" t="n"/>
-      <c r="N48" s="2" t="n"/>
-      <c r="O48" s="2" t="n"/>
+      <c r="M48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>Outside legal counsel to CSC/Pamplona; first seen acting on 09/25, receiving Goodwin Procter's initial merger-agreement draft.</t>
+          <t>Inferred: displaced by the exclusivity with CSC/Pamplona. On 09/19 the Special Committee preferred CSC/Pamplona over Party B's nominally higher $21.50 package (#39) because of option and financing risk.</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>“Kirkland &amp; Ellis LLP, outside legal counsel to CSC/Pamplona” (p. 38)</t>
-        </is>
-      </c>
-      <c r="R48" s="2" t="n"/>
+          <t>CSC, Pamplona and Mac-Gray executed the exclusivity agreement providing for exclusive negotiations until 5 p.m. ET on October 12, 2013 (p. 38)</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>Q9</t>
+        </is>
+      </c>
       <c r="S48" s="2" t="n"/>
       <c r="T48" s="3" t="n">
-        <v>41542</v>
-      </c>
-      <c r="U48" s="3" t="n">
-        <v>41542</v>
-      </c>
+        <v>41541</v>
+      </c>
+      <c r="U48" s="2" t="n"/>
       <c r="V48" s="3" t="n">
-        <v>41542</v>
+        <v>41541</v>
       </c>
     </row>
     <row r="49">
@@ -3705,22 +3712,18 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>between 09/25/2013 and 10/07/2013</t>
+          <t>09/25/2013</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>CSC/Pamplona</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Kirkland &amp; Ellis LLP</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n"/>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Adviser</t>
         </is>
       </c>
       <c r="F49" s="2" t="n">
@@ -3734,19 +3737,17 @@
       <c r="J49" s="2" t="n"/>
       <c r="K49" s="2" t="n"/>
       <c r="L49" s="2" t="n"/>
-      <c r="M49" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M49" s="2" t="n"/>
       <c r="N49" s="2" t="n"/>
       <c r="O49" s="2" t="n"/>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>Information access after exclusivity: exclusive bidder CSC/Pamplona granted full data-room access (limited earlier, #28) and management access for confirmatory diligence.</t>
+          <t>Outside legal counsel to CSC/Pamplona; first reported acting when Goodwin sent it the first draft of the merger agreement.</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
         <is>
-          <t>“CSC and Pamplona were granted full access to the electronic data site and access to certain members of management and conducted confirmatory business and legal due diligence” (p. 38)</t>
+          <t>Goodwin Procter delivered to Kirkland &amp; Ellis LLP, outside legal counsel to CSC/Pamplona, whom we refer to as Kirkland, the initial draft of the merger agreement (p. 38)</t>
         </is>
       </c>
       <c r="R49" s="2" t="n"/>
@@ -3758,7 +3759,7 @@
         <v>41542</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>41554</v>
+        <v>41542</v>
       </c>
     </row>
     <row r="50">
@@ -3767,12 +3768,12 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>between 09/25/2013 and 10/07/2013</t>
+          <t>09/27/2013</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Moab Partners, L.P. (Moab)</t>
+          <t>Stewart G. MacDonald, Jr. and family</t>
         </is>
       </c>
       <c r="D50" s="2" t="n"/>
@@ -3797,24 +3798,24 @@
       <c r="O50" s="2" t="n"/>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>Rollover resolved, not formed: after Goodwin told Rothenberg on 09/23 that talks could resume, Moab and Pamplona discussed a rollover and determined none (reported 10/07). Moab signed a voting agreement at signing.</t>
+          <t>Support agreement: MacDonald, his wife and one of his trusts signed voting agreements with CSC/Pamplona (a condition of CSC's 09/21 offer, #43), effective on signing of the merger agreement.</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>“it was determined that Moab would not rollover any Moab shares in the transaction” (p. 38)</t>
+          <t>which were entered into by Mr. MacDonald, his wife and one of his trusts on September 27, 2013, and which became effective upon entry into the merger agreement (p. 39)</t>
         </is>
       </c>
       <c r="R50" s="2" t="n"/>
       <c r="S50" s="2" t="n"/>
       <c r="T50" s="3" t="n">
-        <v>41548</v>
+        <v>41544</v>
       </c>
       <c r="U50" s="3" t="n">
-        <v>41542</v>
+        <v>41544</v>
       </c>
       <c r="V50" s="3" t="n">
-        <v>41554</v>
+        <v>41544</v>
       </c>
     </row>
     <row r="51">
@@ -3823,7 +3824,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>10/12/2013</t>
+          <t>between 09/25/2013 and 10/07/2013</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -3838,7 +3839,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Exclusivity changed</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F51" s="2" t="n">
@@ -3859,24 +3860,24 @@
       <c r="O51" s="2" t="n"/>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>Extended to 11:59 p.m. ET 10/15/2013 at CSC/Pamplona's request (made by 10/09); committee required a Mac-Gray termination fee of at most $11m, which CSC/Pamplona accepted on 10/11.</t>
+          <t>Information access: in exclusivity, CSC/Pamplona got full data-room access (customer data had been withheld from strategic bidders, #28) and management access, and did confirmatory diligence, including a 10/01 meeting.</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
         <is>
-          <t>“CSC, Pamplona and Mac-Gray executed a letter agreement extending exclusivity until 11:59 p.m. ET on October 15, 2013” (p. 41)</t>
+          <t>CSC and Pamplona were granted full access to the electronic data site and access to certain members of management and conducted confirmatory business and legal due diligence (p. 38)</t>
         </is>
       </c>
       <c r="R51" s="2" t="n"/>
       <c r="S51" s="2" t="n"/>
       <c r="T51" s="3" t="n">
-        <v>41559</v>
+        <v>41548</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>41559</v>
+        <v>41542</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>41559</v>
+        <v>41554</v>
       </c>
     </row>
     <row r="52">
@@ -3885,22 +3886,18 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>10/14/2013</t>
+          <t>between 09/25/2013 and 10/07/2013</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>CSC/Pamplona</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Moab Partners (Rothenberg)</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n"/>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Merger agreement signed</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F52" s="2" t="n">
@@ -3914,31 +3911,29 @@
       <c r="J52" s="2" t="n"/>
       <c r="K52" s="2" t="n"/>
       <c r="L52" s="2" t="n"/>
-      <c r="M52" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M52" s="2" t="n"/>
       <c r="N52" s="2" t="n"/>
       <c r="O52" s="2" t="n"/>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>$21.25 per share in cash; buyers Spin Holdco (Parent), CSC ServiceWorks Holdings and CSC. Pamplona commitment letter $594m; Pamplona liability cap $50m; Mac-Gray fee $11m; CSC reverse fee $15m. Moab and MacDonald voting agreements effective. BofA fairness opinion same day.</t>
+          <t>Rollover abandoned: after talks between Rothenberg and Pamplona, it was decided that Moab would not roll over any shares (reported to the Special Committee 10/07). Moab signed a voting agreement at signing.</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
         <is>
-          <t>“Later in the day, on October 14, 2013, the merger agreement was executed, the Pamplona commitment letter was delivered” (p. 41)</t>
+          <t>As a result of such discussions, it was determined that Moab would not rollover any Moab shares in the transaction. (p. 38)</t>
         </is>
       </c>
       <c r="R52" s="2" t="n"/>
       <c r="S52" s="2" t="n"/>
       <c r="T52" s="3" t="n">
-        <v>41561</v>
+        <v>41548</v>
       </c>
       <c r="U52" s="3" t="n">
-        <v>41561</v>
+        <v>41542</v>
       </c>
       <c r="V52" s="3" t="n">
-        <v>41561</v>
+        <v>41554</v>
       </c>
     </row>
     <row r="53">
@@ -3947,60 +3942,184 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>10/15/2013</t>
+          <t>10/12/2013</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Mac-Gray</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="n"/>
+          <t>CSC/Pamplona</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Merger announced</t>
+          <t>Exclusivity changed</t>
         </is>
       </c>
       <c r="F53" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
+      <c r="G53" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="H53" s="2" t="n"/>
       <c r="I53" s="2" t="n"/>
       <c r="J53" s="2" t="n"/>
       <c r="K53" s="2" t="n"/>
       <c r="L53" s="2" t="n"/>
-      <c r="M53" s="2" t="n"/>
+      <c r="M53" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N53" s="2" t="n"/>
       <c r="O53" s="2" t="n"/>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>Joint announcement by Mac-Gray and CSC before the market opened. Ref: $14.72 close 10/11/2013; about 44% premium (p. 5).</t>
+          <t>Extended from 5 p.m. ET 10/12 to 11:59 p.m. ET 10/15/2013 at CSC/Pamplona's request (made 10/09). The Special Committee extended only after CSC/Pamplona accepted an $11M Mac-Gray termination fee on 10/11, down from its proposed $15M.</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
         <is>
-          <t>“before the U.S. stock markets opened, Mac-Gray and CSC jointly announced the execution of the merger agreement” (p. 41)</t>
+          <t>On October 12, 2013, CSC, Pamplona and Mac-Gray executed a letter agreement extending exclusivity until 11:59 p.m. ET on October 15, 2013. (p. 41)</t>
         </is>
       </c>
       <c r="R53" s="2" t="n"/>
       <c r="S53" s="2" t="n"/>
       <c r="T53" s="3" t="n">
+        <v>41559</v>
+      </c>
+      <c r="U53" s="3" t="n">
+        <v>41559</v>
+      </c>
+      <c r="V53" s="3" t="n">
+        <v>41559</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>10/14/2013</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>CSC/Pamplona</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Merger agreement signed</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H54" s="2" t="n"/>
+      <c r="I54" s="2" t="n"/>
+      <c r="J54" s="2" t="n"/>
+      <c r="K54" s="2" t="n"/>
+      <c r="L54" s="2" t="n"/>
+      <c r="M54" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N54" s="2" t="n"/>
+      <c r="O54" s="2" t="n"/>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>$21.25/share cash; Pamplona commitment letter for $594M, no financing condition; $11M target fee; $15M reverse fee; Pamplona damages cap $50M. Moab and MacDonald voting agreements effective. BofA fairness opinion same day.</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>Later in the day, on October 14, 2013, the merger agreement was executed, the Pamplona commitment letter was delivered, Moab and Parent executed the Moab voting agreement (p. 41)</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="n"/>
+      <c r="S54" s="2" t="n"/>
+      <c r="T54" s="3" t="n">
+        <v>41561</v>
+      </c>
+      <c r="U54" s="3" t="n">
+        <v>41561</v>
+      </c>
+      <c r="V54" s="3" t="n">
+        <v>41561</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>10/15/2013</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Mac-Gray and CSC</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n"/>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Merger announced</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="n"/>
+      <c r="I55" s="2" t="n"/>
+      <c r="J55" s="2" t="n"/>
+      <c r="K55" s="2" t="n"/>
+      <c r="L55" s="2" t="n"/>
+      <c r="M55" s="2" t="n"/>
+      <c r="N55" s="2" t="n"/>
+      <c r="O55" s="2" t="n"/>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>Joint announcement before market open. No go-shop, and no competing proposal was reported before the filing (12/04/2013).</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>On October 15, 2013, before the U.S. stock markets opened, Mac-Gray and CSC jointly announced the execution of the merger agreement. (p. 41)</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="n"/>
+      <c r="S55" s="2" t="n"/>
+      <c r="T55" s="3" t="n">
         <v>41562</v>
       </c>
-      <c r="U53" s="3" t="n">
+      <c r="U55" s="3" t="n">
         <v>41562</v>
       </c>
-      <c r="V53" s="3" t="n">
+      <c r="V55" s="3" t="n">
         <v>41562</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V53"/>
+  <autoFilter ref="A1:V55"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4018,11 +4137,11 @@
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="45" customWidth="1" min="9" max="9"/>
     <col width="45" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -4090,12 +4209,12 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Special Committee's 06/24 decision executed: BofA outreach to 50 parties; confidentiality signers asked for preliminary indications</t>
+          <t>Special Committee decision to approach 50 parties; BofA outreach, NDAs and informational package</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>20 entered: 2 strategic (CSC/Pamplona; Party A via its standing round-0 proposal, no NDA until 08/05) and 18 financial (Party B, Party C, 16 unnamed signers, dates unknown)</t>
+          <t>19 NDA signers furnished the package: 1 strategic (CSC/Pamplona); 18 financial (Party B, Party C, 16 unnamed, some possibly signing after 07/23). Party A (strategic) — 06/21 proposal still being received, not admitted (NDA unsigned until 08/05)</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -4115,12 +4234,12 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>3: CSC/Pamplona, Party B, Party C (plus Party A's 06/21 round-0 proposal, reviewed 07/25)</t>
+          <t>3 bidders: CSC/Pamplona (07/23), Party B (07/24), Party C (07/24 oral, 07/25 written); Party A's 06/21 proposal also reviewed</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>four advanced (Party A, Party B, Party C, CSC/Pamplona); 16 other financial signers out</t>
+          <t>four advanced (Party A, Party B, Party C, CSC/Pamplona); 16 financial signers out (inferred Did not submit)</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4255,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>committee advanced four to management meetings and staged diligence, then asked for revised written proposals</t>
+          <t>Special Committee selected four bidders for management meetings and staged diligence, then revised proposals</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -4161,12 +4280,12 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>4: CSC/Pamplona and Party B (09/09), Party A and Party C (09/10)</t>
+          <t>4 bidders: CSC/Pamplona, Party B (09/09); Party A, Party C (09/10)</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>all four asked for final indications on 09/11</t>
+          <t>all four asked for final indications; none out</t>
         </is>
       </c>
     </row>
@@ -4182,7 +4301,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>committee asked all four for final indications, holding out short exclusivity</t>
+          <t>BofA called all four bidders requesting final indications of interest</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -4207,12 +4326,12 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3: CSC/Pamplona, Party B, Party A (reaffirmed best and final); Party C did not submit</t>
+          <t>3 bidders: CSC/Pamplona, Party A (reiterated best and final), Party B; Party C did not submit</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>CSC/Pamplona selected 09/19 and raised to $21.25 on 09/21; exclusivity 09/24 (Party A, Party B out); signing 10/14</t>
+          <t>CSC/Pamplona preferred 09/19, raised to $21.25 09/21, exclusivity 09/24 (Party A, Party B dropped), signing 10/14/2013</t>
         </is>
       </c>
     </row>
@@ -4228,16 +4347,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4285,27 +4404,27 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Process and round map: one process with three rounds (outreach 06/24; four advanced 07/25; final indications 09/11)?</t>
+          <t>Process and round map: one process with rounds 0–3?</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Yes. One process; round 0 holds Party A's 06/21 proposal; R1 opens with the outreach launched 06/24; R2 on 07/25; R3 on 09/11 (announced final).</t>
+          <t>One process. Round 0: the 04/08 approach to Party A and its 06/21 unsolicited proposal. R1 opens 06/24 (outreach began within four days). R2 opens 07/25 (four selected, management meetings, revised proposals). R3 opens 09/11 (first request for final indications). It ends in exclusivity 09/24 and signing 10/14.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Gaps of two months or more: 04/08/2013 (BofA–Party A call) to 06/21/2013 (Party A proposal), 74 days, both dates certain; no other. C7: (a) fails, since Party A was kept in view (05/09 report; named in 06/24 outreach); (b) fails, gap under three months; (c) met (05/09, 06/24). The 2011–2012 CSC talks had Mac-Gray as buyer (pp. 27–31).</t>
+          <t>Pp. 27–41. Gap of about two months or more with no reported contact with any prospective acquirer: 04/08/2013 to 06/21/2013. E5: (a) fails, since Party A was kept in view; (b) fails, since no end was reported and the gap is under three months; (c) the 06/24 decision is a fresh start. So there is no second process.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>#8, #10, #25, #36, #27, #28</t>
+          <t>#2, #7, #9, #25, #26, #27, #28, #36</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Most plausible alternative: R2 opens with the 08/27 letter, not the 07/25 decision; #25 would move and #27, #28 would fall in R1. R1 opening date alternatives (06/24 decision vs first calls by 06/28) do not move any bid.</t>
+          <t>Plausible alternative: open R2 at the 08/27 due-date letter. Party A's NDA (#27) and the access row (#28) would then move to R1. Party C's 07/25 written bid (#26) stays in R1 either way. Opening R1 on 06/28 (first dated outreach evidence) moves no rows.</t>
         </is>
       </c>
       <c r="G2" s="2" t="n"/>
@@ -4318,27 +4437,27 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Deadline outcomes: R1 (07/23) and R2 (09/09) Late bids accepted; R3 (09/18) Enforced?</t>
+          <t>Round 1 deadline outcome (due 07/23/2013)?</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Yes. R1: Party B and Party C bid 07/24 (Party C again 07/25) after receiving the 07/23 date, and all were reviewed 07/25. R2: Party A and Party C bid 09/10 and were reviewed 09/11. R3: committee selected CSC/Pamplona 09/19 on the bids in hand.</t>
+          <t>Late bids accepted. CSC/Pamplona bid on 07/23. Party B (written) and Party C (oral) bid on 07/24, and both were reviewed on 07/25; Party C's written 07/25 bid followed. The Deadline set date (06/28, first informational package) is inferred.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Due dates pp. 32, 35, 36; bids pp. 33–36; selection p. 37. The 07/23 instruction went to confidentiality signers, including Party B and Party C, whose agreements predate it (p. 32).</t>
+          <t>P. 32: NDA signers were 'instructed to submit by July 23, 2013'. P. 33: the 07/24 bids, and on 07/25 BofA reviewed the indications from Party B, Party C and CSC/Pamplona.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>#16, #21, #22, #23, #26, #29, #32, #33, #34, #41</t>
+          <t>#13, #21, #23, #24, #26</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>If the one-day slippages were treated as immaterial, R1 and R2 would read Passed without action or Enforced; neither changes any row, but both would overstate enforcement.</t>
+          <t>If 07/23 were treated as a soft target, not a deadline, the outcome becomes Passed without action. Rows and live counts are unchanged.</t>
         </is>
       </c>
       <c r="G3" s="2" t="n"/>
@@ -4351,27 +4470,27 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Are the 09/18 answers to the request for 'final indications of interest' and CSC/Pamplona's 09/21 $21.25 'last and best offer' Formal?</t>
+          <t>Exits and timing of the 16 unnamed financial NDA signers?</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Formal (C13 rule 2): the 09/11 request was an announced final solicitation. No markup was delivered; Goodwin sent the first draft only on 09/25. Party A expressly called its range best and final.</t>
+          <t>Keep one cohort: Count 16 on entry (#19) and an inferred Did not submit by 07/23 (#22). No other indications were reported, and only four 'interested bidders' advanced on 07/25.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>The request for final indications came with the prospect of exclusivity (p. 36); CSC/Pamplona called $21.25 its 'last and best offer' (p. 37). Evidence is thin because no documents accompanied the bids.</t>
+          <t>P. 32: 20 signers '(2 strategic, 18 financial)' signed 'over the next two months'. P. 33: only three indications plus Party A's 06/21 proposal were reviewed. P. 34: 'the four interested bidders'.</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>#37, #38, #39, #43</t>
+          <t>#19, #22</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>If Informal, the winner reaches signing with no Formal row, and C12 would add a Bid reaffirmed for CSC/Pamplona at 10/07 (Kirkland's revised merger-agreement draft, p. 39), at $21.25 carried from #43, Conditions Unclear.</t>
+          <t>Some of the 16 may have signed after 07/23, some even after 07/25. Those would exit as Dropped by target (07/25 advancement) or Not selected at signing. The Round 1 admitted count would then fall below 19. Total entries are unaffected.</t>
         </is>
       </c>
       <c r="G4" s="2" t="n"/>
@@ -4384,27 +4503,27 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>The 16 unnamed financial confidentiality signers: are they (and Party B, Party C) within the 35 financial contacts, and did they leave by the 07/25 advancement (Dropped by target) or by the 07/23 due date (Did not submit)?</t>
+          <t>Round 2 deadline outcome (due 09/09/2013)?</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Keep: within the 35; Dropped by target by 07/25, inferred, Count 16.</t>
+          <t>Late bids accepted. CSC/Pamplona and Party B bid on 09/09. Party A and Party C bid on 09/10 and were still reviewed with the others by the Special Committee on 09/11.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>The filing gives 20 signers (2 strategic, 18 financial) over two months but no dates for the 16, so it cannot show they had signed before 07/23; the four-bidder set advanced on 07/25 is complete (pp. 32–34).</t>
+          <t>P. 35: the letter required revised proposals 'no later than September 9, 2013'. On 09/10 Party A submitted and Party C gave an oral revised indication. On 09/11 the Committee reviewed the indications of all four.</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>#12, #13, #24</t>
+          <t>#29, #32, #33, #34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Did not submit by 07/23 would change the exit label and round-1 non-submission count, not the live count. If some signed after 07/25, their exit would be by 08/27 (letters to four only).</t>
+          <t>None supported; the two late bids clearly were considered.</t>
         </is>
       </c>
       <c r="G5" s="2" t="n"/>
@@ -4417,33 +4536,165 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Party B's 09/18 price: record $21.50 (its own value incl. options) or $19.00 cash?</t>
+          <t>Conditions on CSC/Pamplona's 09/09, 09/18 and 09/21 bids: Heavy or Light?</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>$21.50 in both price cells, All cash = No, with $19.00 cash and $2.50 option value in the Note.</t>
+          <t>Heavy. Each bid asked for, or was conditioned on, a two-week exclusive negotiation period, and E12 counts a stated exclusive period as a further diligence period. The 09/21 bid also required MacDonald voting agreements.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>C15: a stated per-share package value is the total offer value. Party B valued the options at $2.50; the committee questioned that value (pp. 36–37).</t>
+          <t>Pp. 35–37: two weeks of exclusivity was requested on 09/09 and 09/18, and was a proviso of the 09/21 last-and-best offer. Pamplona committed 100% of the capital and had said its diligence would be minimal (p. 32).</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>#30, #37, #43</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Light: financing was committed and diligence in exclusivity was only 'confirmatory' (p. 38). Rows #30, #37 and #43 would become Light, making the winner's bids far less conditional than its rivals'.</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Round 3 deadline outcome (due 09/18/2013)?</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Enforced. CSC/Pamplona, Party A and Party B responded on 09/18; Party C did not. On 09/19 the Special Committee chose CSC/Pamplona from the bids in hand.</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>P. 36: 'request final indications of interest by September 18, 2013'; the 09/18 submissions; and at the 09/19 meeting, 'Party C did not submit'.</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>#36, #41</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>None supported.</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Q7</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Is Round 3 a genuine final solicitation, making its bids Formal?</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Yes. Round 3 is Announced as final: BofA asked all four bidders for 'final indications of interest'. The 09/18 responses (#37, #38, #39) and CSC/Pamplona's 09/21 last-and-best offer (#43) are therefore Formal under E11(2). Party A's 09/18 reiteration is a Round 3 Bid, not Bid reaffirmed, because the target was not finalizing with Party A.</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>P. 36: 'request final indications of interest by September 18, 2013'. Party A called its range 'best and final'. No markup of the merger agreement was reported before exclusivity; the first draft was sent 09/25 (p. 38).</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>#36, #37, #38, #39, #43</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>If 'final indications' are read as still non-binding, rows #37–#39 and #43 become Informal and the ledger has no Formal bid before signing. Dropping Party A's reiteration row would make it look like a non-response.</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Q8</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>How to price Party B's 09/18 cash-plus-options bid?</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Price cells hold $21.50, Party B's own stated package value: $19.00 cash at closing plus options valued at $2.50. All cash is No. Bid prices are otherwise per-share cash in US dollars.</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>P. 36: the purchase price 'that Party B valued at $21.50 per share, including $19.00 of cash'. The options vest on base-case projections over five years. P. 37: the Committee judged them contingent and risky.</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
           <t>#39</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Using $19.00 would make Party B's final bid lower than CSC/Pamplona's $20.75, changing the reading of why it lost and the ranking of final bids.</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="n"/>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Recording $19.00 (cash only) would rank Party B below CSC/Pamplona's $20.75 rather than above it. That changes the interpretation of the winner's selection.</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Q9</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Exit label and reason for Party A and Party B at exclusivity?</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Dropped by target by 09/24 (inferred), when exclusivity with CSC/Pamplona was signed; Exit reason Not stated. The filing never reports either bidder being told it was out, or leaving.</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>P. 38: exclusivity executed 09/24. P. 37: on 09/19 the Special Committee preferred CSC/Pamplona on value and certainty. P. 36: Party A called $18–$19 its 'best and final offer'.</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>#46, #47</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Party A could take 'Would not improve earlier offer', since it declined to raise its price when asked for final bids. Party B could take 'Lower offer than rivals' on a risk-adjusted view, though it was nominally higher. Either reading changes the valuation information in the exit.</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G6"/>
+  <autoFilter ref="A1:G10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4457,7 +4708,7 @@
   <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
     <col width="110" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -4481,7 +4732,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Mac-Gray Corporation</t>
+          <t>Mac-Gray Corporation (NYSE), laundry facilities management contractor, Waltham, Massachusetts</t>
         </is>
       </c>
     </row>
@@ -4493,7 +4744,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>CSC ServiceWorks, Inc., through Spin Holdco Inc. (Parent), CSC ServiceWorks Holdings, Inc. and CSC Fenway, Inc.; CSC is owned by Pamplona Capital Partners III, L.P., which committed the equity (the filing calls the bidder "CSC/Pamplona")</t>
+          <t>CSC ServiceWorks, Inc., through Spin Holdco Inc. (Parent) and CSC Fenway, Inc. (Merger Subsidiary), with CSC ServiceWorks Holdings, Inc.; CSC is a portfolio company of Pamplona Capital Partners III, L.P., which committed the equity (bidder unit: CSC/Pamplona)</t>
         </is>
       </c>
     </row>
@@ -4505,7 +4756,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Strategic: laundry facilities operator owned by a private equity fund (Pamplona), which funds the deal; the filing calls CSC/Pamplona a strategic bidder (p. 32)</t>
+          <t>Strategic (sponsor-owned operating company; the filing calls CSC/Pamplona a strategic bidder, p. 34)</t>
         </is>
       </c>
     </row>
@@ -4517,7 +4768,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>$21.25 per share in cash; equity funded by a $594m Pamplona commitment letter; no financing condition</t>
+          <t>$21.25 per share in cash; funded by $594 million Pamplona equity commitment, no financing condition (pp. 5–6, 58)</t>
         </is>
       </c>
     </row>
@@ -4565,7 +4816,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>pp. 27–41</t>
+          <t>27–41</t>
         </is>
       </c>
     </row>
@@ -4577,7 +4828,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>target-led: Board authorized BofA to explore opportunities (04/05/2013) and BofA sounded out Party A (04/08); Party A then made an unsolicited proposal (06/21) before the organized outreach. An activist (Moab) won board seats on 05/30/2013 but is not reported pressing for a sale.</t>
+          <t>target-led (board had BofA approach Party A on 04/08/2013 before any bid; Party A's 06/21/2013 proposal was unsolicited; activist Moab won two board seats 05/30/2013 but is not reported pressing for a sale)</t>
         </is>
       </c>
     </row>
@@ -4601,7 +4852,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Winter 2011 into 2012: talks between Mac-Gray and CSC about Mac-Gray acquiring CSC (Mac-Gray as buyer; BofA engaged 10/23/2012); CSC was instead sold to Pamplona in May 2013. Undated discussions with other industry participants. None was a sale of Mac-Gray.</t>
+          <t>Unspecified strategic discussions from time to time with CSC and other industry participants, including 2011–2012 talks about Mac-Gray acquiring CSC (BofA engaged 10/23/2012); CSC was instead sold to Pamplona in May 2013. None was a sale of Mac-Gray (p. 27).</t>
         </is>
       </c>
     </row>
@@ -4613,7 +4864,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Met (process 1): 20 parties. The filing counts 20 potential bidders (parties) signing confidentiality agreements: 2 strategic, 18 financial; CSC and Pamplona counted as one. No post-signing additions.</t>
+          <t>Met (process 1): 20 parties (2 strategic, 18 financial)</t>
         </is>
       </c>
     </row>
@@ -4637,7 +4888,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>US dollars per share. Party B's 09/18 bid mixed $19.00 cash with options it valued at $2.50 per share (Q5); all others all cash.</t>
+          <t>US dollars per share, cash; exception: Party B's 09/18/2013 bid of $19.00 cash plus options it valued at $2.50 (Q8)</t>
         </is>
       </c>
     </row>
@@ -4649,7 +4900,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>BofA Merrill Lynch (Merrill Lynch, Pierce, Fenner &amp; Smith Incorporated), sole financial adviser; engaged 05/31/2013 after its 2011–2012 mandate was ended 05/15/2013</t>
+          <t>BofA Merrill Lynch (Merrill Lynch, Pierce, Fenner &amp; Smith Incorporated)</t>
         </is>
       </c>
     </row>
@@ -4673,7 +4924,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>In spring 2013 Mac-Gray's board, with BofA Merrill Lynch, began exploring a sale; Party A made an unsolicited $17–19 all-cash proposal on 06/21/2013. A Special Committee then had BofA approach 50 parties, and 20 (2 strategic, 18 financial) signed confidentiality agreements. Preliminary indications from CSC/Pamplona ($18.50), Party B ($17–18) and Party C ($15–17, then $16–16.50) led the committee to advance four bidders, including Party A, to management meetings and staged diligence. Revised proposals (09/09–09/10) ranged from $16–17 to $19.50, and final indications on 09/18 brought CSC/Pamplona to $20.75 and Party B to a cash-and-options package it valued at $21.50; Party A stood at $18–19 and Party C dropped out. The committee preferred CSC/Pamplona's fully funded offer, obtained $21.25 in exchange for exclusivity (09/24), and signed on 10/14/2013 after negotiating fees and Pamplona's liability.</t>
+          <t>After Party A signalled interest in April 2013 and made an unsolicited $17–$19 proposal in June, a Special Committee had BofA Merrill Lynch approach 50 parties; 20 signed confidentiality agreements. Three preliminary indications arrived in July, and four bidders (Party A, CSC/Pamplona, and financial bidders Party B and Party C) advanced to management meetings, with customer data withheld from the strategic bidders. Revised indications in September ranged from $16–$17 to $19.50, and a request for final indications drew $20.75 from CSC/Pamplona, a best-and-final $18–$19 from Party A, and a $21.50 cash-and-options package from Party B, while Party C dropped out. The Special Committee preferred CSC/Pamplona's fully equity-backed offer and asked for $21.25, which CSC/Pamplona accepted as its last and best offer in return for two weeks' exclusivity. After exclusivity from 09/24, extended to 10/15, the merger agreement was signed at $21.25 in cash on 10/14/2013 and announced 10/15/2013.</t>
         </is>
       </c>
     </row>

--- a/extraction/mac-gray.xlsx
+++ b/extraction/mac-gray.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Deal facts" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Deal ledger'!$A$1:$V$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Deal ledger'!$A$1:$V$54</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Rounds'!$A$1:$J$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Questions'!$A$1:$G$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Deal facts'!$A$1:$B$18</definedName>
@@ -25,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="MM/DD/YYYY"/>
   </numFmts>
   <fonts count="2">
@@ -439,13 +439,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V55"/>
+  <dimension ref="A1:V54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="7" customWidth="1" min="7" max="7"/>
@@ -453,14 +453,14 @@
     <col width="9" customWidth="1" min="9" max="9"/>
     <col width="9" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
     <col width="7" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="8" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
-    <col width="20" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
     <col width="12" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
@@ -614,7 +614,7 @@
       <c r="O2" s="2" t="n"/>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Mac-Gray's financial adviser, first engaged for the 2011-2012 Discussions (Mac-Gray's possible acquisition of CSC). The filing does not say under which engagement BofA made the 04/08/2013 call to Party A.</t>
+          <t>Target financial adviser, first engagement: hired for the 2011-2012 Discussions (Mac-Gray's possible acquisition of CSC), a buy-side mandate. Under it, BofA called Party A on 04/08/2013 at the Board's instruction. Ended 05/15/2013 (#4).</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -676,12 +676,12 @@
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>BofA, instructed by the board (04/05/2013 authorization to explore transactional opportunities, including with Party A), called Party A about a possible business combination; Party A said it might consider one. First contact with Party A.</t>
+          <t>First contact with Party A, initiated by the target. On 04/05 the Board authorized management to work with BofA to explore transactional opportunities, including with Party A. BofA phoned Party A about a business combination, and Party A said it might consider one. No price.</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>representatives of BofA Merrill Lynch, as instructed by the Board, telephoned a representative of Party A to discuss generally a possible business combination between Party A and Mac-Gray (p. 27)</t>
+          <t>representatives of BofA Merrill Lynch, as instructed by the Board, telephoned a representative of Party A to discuss generally a possible business combination between Party A and Mac-Gray. (p. 27)</t>
         </is>
       </c>
       <c r="R3" s="2" t="inlineStr">
@@ -736,12 +736,12 @@
       <c r="O4" s="2" t="n"/>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Mac-Gray's outside legal counsel; earliest reported acting at the 05/09/2013 board meeting, where the board formed the Transaction Committee to pick a financial adviser for a strategic-alternatives review.</t>
+          <t>Target outside legal counsel; first shown acting at the 05/09 Board meeting. At the same meeting the Board formed a Transaction Committee (Bullock, Daoust) to recommend a financial adviser for strategic alternatives, including a sale. The Board deferred any decision on a sale process.</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>representatives from BofA Merrill Lynch and Goodwin Procter LLP, outside legal counsel to Mac-Gray, were also in attendance for all or portions of the meeting (p. 27)</t>
+          <t>representatives from BofA Merrill Lynch and Goodwin Procter LLP, outside legal counsel to Mac-Gray, were also in attendance for all or portions of the meeting. (p. 27)</t>
         </is>
       </c>
       <c r="R4" s="2" t="n"/>
@@ -792,12 +792,12 @@
       <c r="O5" s="2" t="n"/>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>Mac-Gray terminated BofA's 2011-2012 Discussions engagement (decided by the Transaction Committee 05/14/2013) because BofA was being invited to pitch for the new strategic-alternatives mandate and the CSC sale process had ended.</t>
+          <t>Ends the 2011-2012 buy-side engagement (#1). The Transaction Committee decided on 05/14 to terminate it because BofA was one of three banks invited to pitch for the sale-side mandate.</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>On May 15, 2013, Mac-Gray sent a letter to BofA Merrill Lynch terminating their engagement in connection with the 2011-2012 Discussions. (p. 29)</t>
+          <t>Mac-Gray sent a letter to BofA Merrill Lynch terminating their engagement in connection with the 2011-2012 Discussions. (p. 29)</t>
         </is>
       </c>
       <c r="R5" s="2" t="n"/>
@@ -848,7 +848,7 @@
       <c r="O6" s="2" t="n"/>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>Board approved engaging BofA as Mac-Gray's financial adviser for the strategic-alternatives review, including a potential sale, after a three-bank pitch; engagement letter signed 05/31/2013 barred BofA from financing buyers without consent.</t>
+          <t>Target financial adviser for the review of strategic alternatives, including a potential sale. The Board approved the engagement on the Transaction Committee's recommendation, choosing BofA over two other candidates. The engagement letter, signed 05/31, bars BofA from financing any buyer without consent. BofA later gave the fairness opinion.</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Moab Partners, L.P. (with affiliates)</t>
+          <t>Moab Partners, L.P. (Moab)</t>
         </is>
       </c>
       <c r="D7" s="2" t="n"/>
@@ -904,12 +904,12 @@
       <c r="O7" s="2" t="n"/>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>Moab won a proxy contest: its nominees Rothenberg (Moab's co-founder and General Partner) and Hyman replaced two incumbents at the annual meeting. Moab held about 9% (as of 06/12/2013). The filing does not say Moab pressed for a sale.</t>
+          <t>Moab's nominees Rothenberg (Moab's general partner) and Hyman were elected directors at the annual meeting after a proxy contest, replacing incumbent nominees. Moab held about 9% as of 06/12. The filing does not say Moab pressed for a sale. Its rollover interest is at #15, #16, #44 and #49.</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>the Mac-Gray stockholders elected as directors Michael M. Rothenberg and James E. Hyman, candidates nominated by Mac-Gray's stockholder, Moab Partners, L.P. and certain of its affiliates (p. 29)</t>
+          <t>Mac-Gray and Moab engaged in a proxy contest leading up to the annual meeting and Mr. Rothenberg and Mr. Hyman were elected in place of Mac-Gray's incumbent nominees (p. 29)</t>
         </is>
       </c>
       <c r="R7" s="2" t="n"/>
@@ -982,7 +982,7 @@
       <c r="O8" s="2" t="n"/>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>Conditions unclear: the filing reports no financing or diligence terms. Unsolicited written proposal to the board, before any outreach or NDA; the Special Committee expected Party A to raise it after diligence.</t>
+          <t>Unclear: no conditions reported, but Party A had no NDA or diligence yet. On 06/24 the Committee expected Party A to raise its price after diligence. Unsolicited written proposal to the Board. Party A enters the process here.</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1030,7 +1030,7 @@
         <v>1</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" s="2" t="n"/>
       <c r="I9" s="2" t="n"/>
@@ -1042,7 +1042,7 @@
       <c r="O9" s="2" t="n"/>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>Board formed a six-member Special Committee (MacDonald and Rothenberg excluded). The Committee concluded it should consider a potential sale, to be weighed against remaining stand-alone; buybacks and a special dividend were rejected.</t>
+          <t>The Board formed a six-member Special Committee, excluding the CEO (MacDonald) and Rothenberg because of possible rollover conflicts. The Committee concluded it was in stockholders' best interests to consider a sale, compared against remaining stand-alone. It rejected a large buyback and an extraordinary dividend.</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1098,12 +1098,12 @@
       <c r="O10" s="2" t="n"/>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>Special Committee decided to approach 50 parties (15 strategic, 35 financial, including CSC/Pamplona and Party A); BofA began outreach within days (first NDA 06/28/2013). NDA signers received an informational package and were asked for preliminary indications by 07/23/2013.</t>
+          <t>The Special Committee decided to approach 50 parties (15 strategic, 35 financial), including CSC/Pamplona and Party A. BofA began within days: Pamplona and Party A were reached by 06/28, and Party B signed an NDA 06/28. NDA signers got an information package and a due date of 07/23 for preliminary indications covering valuation, financing, conditions and diligence.</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>BofA Merrill Lynch contacted the strategic and financial parties identified at the June 24th Special Committee meeting (p. 32)</t>
+          <t>50 parties, including CSC and Pamplona, who together we refer to as CSC/Pamplona, and Party A, to solicit potential interest in a transaction with Mac-Gray (p. 32)</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>during the weeks after 06/24/2013</t>
+          <t>during the several weeks after 06/24/2013</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1164,15 +1164,19 @@
       <c r="O11" s="2" t="n"/>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>Target outreach by BofA. The filing's total of 15 strategic parties approached includes CSC/Pamplona (own row) and Party A (first contacted 04/08/2013, #2; BofA spoke to it again by 06/28/2013). None of these 13 signed an NDA (only two strategic signers).</t>
+          <t>Outreach initiated by BofA for the target. 15 strategic parties approached, minus Party A and CSC/Pamplona (both named members of the 50) = 13. None signed an NDA: the only strategic NDA signers were Party A and CSC/Pamplona. Party A's first contact is #2.</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>and Party A, to solicit potential interest in a transaction with Mac-Gray, 15 of which were potential strategic buyers and 35 of which were potential financial buyers (p. 32)</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="n"/>
+          <t>in accordance with the directives of the Special Committee, BofA Merrill Lynch contacted the strategic and financial parties identified at the June 24th Special Committee meeting. (p. 32)</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
       <c r="S11" s="2" t="n"/>
       <c r="T11" s="3" t="n">
         <v>41449</v>
@@ -1188,12 +1192,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>during the weeks after 06/24/2013</t>
+          <t>during the several weeks after 06/24/2013</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>35 potential financial buyers, including private equity firms</t>
+          <t>35 potential financial buyers (including Party B and Party C)</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1224,15 +1228,19 @@
       <c r="O12" s="2" t="n"/>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>Target outreach by BofA. Includes Party B and Party C. 18 of the 35 later signed NDAs; the rest did not.</t>
+          <t>Outreach initiated by BofA for the target: the 35 financial buyers among the 50 approached. 18 later signed NDAs: Party B (#13), Party C (#14) and 16 unnamed (#18). The other 17 are not reported to have signed.</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>35 of which were potential financial buyers, including private equity firms (p. 32)</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="n"/>
+          <t>15 of which were potential strategic buyers and 35 of which were potential financial buyers, including private equity firms. (p. 32)</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
       <c r="S12" s="2" t="n"/>
       <c r="T12" s="3" t="n">
         <v>41449</v>
@@ -1248,7 +1256,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>by 06/28/2013</t>
+          <t>06/24/2013-06/28/2013</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1284,7 +1292,7 @@
       <c r="O13" s="2" t="n"/>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Target outreach: BofA, as instructed, spoke with Pamplona, which was interested in an acquisition by its portfolio company CSC and said diligence would be minimal. In the same report, Party A cited synergies and was speaking to financing sources.</t>
+          <t>First contact, initiated by the target. BofA spoke with Pamplona as the Committee instructed, and BofA reported the call on 06/28. Pamplona was interested in an acquisition by its portfolio company CSC and said diligence would be minimal. Party A told BofA it saw large synergies and was talking to financing sources.</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1310,18 +1318,22 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>by 06/28/2013</t>
+          <t>06/28/2013</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Mac-Gray</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="n"/>
+          <t>Party B</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Deadline set</t>
+          <t>NDA signed</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
@@ -1335,34 +1347,28 @@
       <c r="J14" s="2" t="n"/>
       <c r="K14" s="2" t="n"/>
       <c r="L14" s="2" t="n"/>
-      <c r="M14" s="2" t="n"/>
+      <c r="M14" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N14" s="2" t="n"/>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="O14" s="2" t="n"/>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>NDA signers were told to submit preliminary indications by 07/23/2013 (valuation, financing, conditions, diligence focus). Date inferred: the instruction came with the informational package, and the first package reported went to Party B on 06/28/2013.</t>
+          <t>Party B enters. It signed a confidentiality and standstill agreement (with a sunset on a third-party deal announcement) and received the information package for a preliminary indication.</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>furnished an informational package for the purpose of providing potential bidders with data to formulate a preliminary indication of interest, which they were instructed to submit by July 23, 2013 (p. 32)</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
+          <t>Later on June 28, 2013, Party B, entered into a confidentiality and standstill agreement with Mac-Gray (p. 32)</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="n"/>
       <c r="S14" s="2" t="n"/>
       <c r="T14" s="3" t="n">
         <v>41453</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>41449</v>
+        <v>41453</v>
       </c>
       <c r="V14" s="3" t="n">
         <v>41453</v>
@@ -1374,12 +1380,12 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>06/28/2013</t>
+          <t>06/30/2013</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Party B</t>
+          <t>Party C</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1410,24 +1416,24 @@
       <c r="O15" s="2" t="n"/>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>Confidentiality and standstill agreement with a sunset clause; Party B received the informational package. Entry.</t>
+          <t>Party C enters. It signed a confidentiality and standstill agreement and received the information package for a preliminary indication.</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>Later on June 28, 2013, Party B, entered into a confidentiality and standstill agreement with Mac-Gray (p. 32)</t>
+          <t>June 30, 2013, Party C entered into a confidentiality and standstill agreement with Mac-Gray (p. 32)</t>
         </is>
       </c>
       <c r="R15" s="2" t="n"/>
       <c r="S15" s="2" t="n"/>
       <c r="T15" s="3" t="n">
-        <v>41453</v>
+        <v>41455</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>41453</v>
+        <v>41455</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>41453</v>
+        <v>41455</v>
       </c>
     </row>
     <row r="16">
@@ -1436,22 +1442,18 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>06/30/2013</t>
+          <t>07/03/2013</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Party C</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
+          <t>Moab / CSC/Pamplona</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n"/>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>NDA signed</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
@@ -1465,31 +1467,29 @@
       <c r="J16" s="2" t="n"/>
       <c r="K16" s="2" t="n"/>
       <c r="L16" s="2" t="n"/>
-      <c r="M16" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M16" s="2" t="n"/>
       <c r="N16" s="2" t="n"/>
       <c r="O16" s="2" t="n"/>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Confidentiality and standstill agreement; Party C received the informational package. Entry.</t>
+          <t>Request for an exclusive rollover tie-up. Rothenberg told Goodwin that Moab had discussed a possible equity rollover with Pamplona. Pamplona would ask that its NDA let it share bid material with Moab, with Moab dealing only with CSC/Pamplona.</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>On June 30, 2013, Party C entered into a confidentiality and standstill agreement with Mac-Gray (p. 32)</t>
+          <t>Pamplona would be requesting that any confidentiality agreement CSC/Pamplona execute with Mac-Gray permit CSC and Pamplona to discuss their bid and evaluation material with Moab (p. 32)</t>
         </is>
       </c>
       <c r="R16" s="2" t="n"/>
       <c r="S16" s="2" t="n"/>
       <c r="T16" s="3" t="n">
-        <v>41455</v>
+        <v>41458</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>41455</v>
+        <v>41458</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>41455</v>
+        <v>41458</v>
       </c>
     </row>
     <row r="17">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>07/03/2013</t>
+          <t>07/06/2013</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Moab Partners (Rothenberg) and CSC/Pamplona</t>
+          <t>Mac-Gray</t>
         </is>
       </c>
       <c r="D17" s="2" t="n"/>
@@ -1528,24 +1528,24 @@
       <c r="O17" s="2" t="n"/>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>Rollover approach: Rothenberg told Goodwin that he had discussed a possible Moab equity rollover with Pamplona, and that Pamplona would ask for its NDA to let it share its bid with Moab, with Moab dealing only with CSC/Pamplona.</t>
+          <t>The Special Committee denied the request in #15, keeping Moab's rollover open as a source of capital for all bidders. BofA and Goodwin told CSC/Pamplona and Rothenberg that rollover talks with any party were premature but would be allowed later.</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>Pamplona would be requesting that any confidentiality agreement CSC/Pamplona execute with Mac-Gray permit CSC and Pamplona to discuss their bid and evaluation material with Moab (p. 32)</t>
+          <t>the Special Committee decided to deny the exclusivity request at this stage of the process so that the potential equity rollover of Moab's shares could be available (p. 33)</t>
         </is>
       </c>
       <c r="R17" s="2" t="n"/>
       <c r="S17" s="2" t="n"/>
       <c r="T17" s="3" t="n">
-        <v>41458</v>
+        <v>41461</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>41458</v>
+        <v>41461</v>
       </c>
       <c r="V17" s="3" t="n">
-        <v>41458</v>
+        <v>41461</v>
       </c>
     </row>
     <row r="18">
@@ -1554,18 +1554,22 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>07/06/2013</t>
+          <t>07/11/2013</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Mac-Gray</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="n"/>
+          <t>CSC/Pamplona</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>NDA signed</t>
         </is>
       </c>
       <c r="F18" s="2" t="n">
@@ -1579,29 +1583,31 @@
       <c r="J18" s="2" t="n"/>
       <c r="K18" s="2" t="n"/>
       <c r="L18" s="2" t="n"/>
-      <c r="M18" s="2" t="n"/>
+      <c r="M18" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N18" s="2" t="n"/>
       <c r="O18" s="2" t="n"/>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>Special Committee refused the Moab–CSC/Pamplona exclusive rollover arrangement, keeping Moab's stake available to all bidders; told CSC/Pamplona and Rothenberg that rollover talks with anyone were premature but would be allowed later.</t>
+          <t>CSC/Pamplona enters. CSC, an operating company owned by Pamplona, bids jointly with Pamplona as one unit. They received the information package. Meanwhile (07/11-07/23), Party A's NDA talks stalled over the non-solicitation terms.</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>the Special Committee decided to deny the exclusivity request at this stage of the process so that the potential equity rollover of Moab's shares could be available (p. 33)</t>
+          <t>July 11, 2013, CSC/Pamplona entered into a confidentiality and standstill agreement with Mac-Gray (p. 33)</t>
         </is>
       </c>
       <c r="R18" s="2" t="n"/>
       <c r="S18" s="2" t="n"/>
       <c r="T18" s="3" t="n">
-        <v>41461</v>
+        <v>41466</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>41461</v>
+        <v>41466</v>
       </c>
       <c r="V18" s="3" t="n">
-        <v>41461</v>
+        <v>41466</v>
       </c>
     </row>
     <row r="19">
@@ -1610,17 +1616,17 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>07/11/2013</t>
+          <t>over the two months after 06/24/2013</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>CSC/Pamplona</t>
+          <t>16 other financial NDA signers (unnamed)</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1640,30 +1646,34 @@
       <c r="K19" s="2" t="n"/>
       <c r="L19" s="2" t="n"/>
       <c r="M19" s="2" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="N19" s="2" t="n"/>
       <c r="O19" s="2" t="n"/>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>Confidentiality and standstill agreement (a letter agreement among Pamplona Capital Management LLC, Parent and Mac-Gray, per merger agreement s.6.17, Annex A); informational package provided. Entry. Party A's NDA talks stalled over non-solicitation terms 07/11–07/23.</t>
+          <t>20 NDA signers in total: 18 financial (including Party B and Party C) and 2 strategic (Party A and CSC/Pamplona). Their individual rows are #13, #14, #17 and #26, so 18 - 2 = 16 here. Signing dates are not given, only "over the next two months". Sort date moved from the window midpoint (07/24) to 07/23 so it precedes #21.</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>On July 11, 2013, CSC/Pamplona entered into a confidentiality and standstill agreement with Mac-Gray (p. 33)</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="n"/>
+          <t>Over the next two months a total of 20 potential bidders, including two strategic bidders (Party A and CSC/Pamplona) and 18 financial bidders (including Party B and Party C) (p. 32)</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
       <c r="S19" s="2" t="n"/>
       <c r="T19" s="3" t="n">
-        <v>41466</v>
+        <v>41478</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>41466</v>
+        <v>41449</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>41466</v>
+        <v>41510</v>
       </c>
     </row>
     <row r="20">
@@ -1672,22 +1682,18 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>06/24/2013 to about 08/24/2013 ("over the next two months")</t>
+          <t>07/23/2013</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>16 other financial NDA signers</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
+          <t>Mac-Gray</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n"/>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>NDA signed</t>
+          <t>Deadline</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
@@ -1701,24 +1707,22 @@
       <c r="J20" s="2" t="n"/>
       <c r="K20" s="2" t="n"/>
       <c r="L20" s="2" t="n"/>
-      <c r="M20" s="2" t="n">
-        <v>16</v>
-      </c>
+      <c r="M20" s="2" t="n"/>
       <c r="N20" s="2" t="n"/>
       <c r="O20" s="2" t="n"/>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Count: 16 = 20 NDA signers (2 strategic, 18 financial) minus the individually recorded Party A, CSC/Pamplona, Party B and Party C. Signing dates not reported; some may have signed after 07/23/2013. Sort date moved to 07/23/2013 to precede the inferred exit.</t>
+          <t>Due date for preliminary indications of interest. CSC/Pamplona bid on time. Party B and Party C bid on 07/24 and were considered on 07/25 (#22, #23).</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>a total of 20 potential bidders, including two strategic bidders (Party A and CSC/Pamplona) and 18 financial bidders (including Party B and Party C), entered into confidentiality agreements (p. 32)</t>
+          <t>an informational package for the purpose of providing potential bidders with data to formulate a preliminary indication of interest, which they were instructed to submit by July 23, 2013. (p. 32)</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="S20" s="2" t="n"/>
@@ -1726,10 +1730,10 @@
         <v>41478</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>41449</v>
+        <v>41478</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>41510</v>
+        <v>41478</v>
       </c>
     </row>
     <row r="21">
@@ -1790,12 +1794,12 @@
       <c r="O21" s="2" t="n"/>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>Conditions unclear: preliminary indication with no stated conditions, though diligence was still open. On time. Pamplona had earlier said its diligence would be minimal.</t>
+          <t>Unclear: no conditions or financing terms reported, and diligence was still ahead in the staged second stage. Pamplona had said on 06/28 that diligence would be minimal. Preliminary indication of interest.</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>On July 23, 2013, CSC/Pamplona submitted a preliminary indication of interest at an all-cash purchase price of $18.50 per share. (p. 33)</t>
+          <t>CSC/Pamplona submitted a preliminary indication of interest at an all-cash purchase price of $18.50 per share. (p. 33)</t>
         </is>
       </c>
       <c r="R21" s="2" t="n"/>
@@ -1816,18 +1820,22 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>07/23/2013</t>
+          <t>by 07/23/2013</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Mac-Gray</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="n"/>
+          <t>16 other financial NDA signers (unnamed)</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Deadline</t>
+          <t>Did not submit</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
@@ -1841,31 +1849,39 @@
       <c r="J22" s="2" t="n"/>
       <c r="K22" s="2" t="n"/>
       <c r="L22" s="2" t="n"/>
-      <c r="M22" s="2" t="n"/>
-      <c r="N22" s="2" t="n"/>
-      <c r="O22" s="2" t="n"/>
+      <c r="M22" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>Round 1 due date for preliminary indications. CSC/Pamplona bid on time; Party B and Party C bid on 07/24–07/25 and were still considered (late bids accepted).</t>
+          <t>Inferred. 20 signers - Party A (not asked for a 07/23 indication; NDA 08/05) - 3 submitters (CSC/Pamplona, Party B, Party C) = 16. The 07/25 review lists no other indication, and only four bidders advanced. Any who signed after 07/23 would instead have been dropped on 07/25.</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>which they were instructed to submit by July 23, 2013 (p. 32)</t>
+          <t>representatives of BofA Merrill Lynch reviewed the preliminary indications of interest received from Party B, Party C and CSC/Pamplona as well as the Party A June 21 proposal (p. 33)</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="S22" s="2" t="n"/>
       <c r="T22" s="3" t="n">
         <v>41478</v>
       </c>
-      <c r="U22" s="3" t="n">
-        <v>41478</v>
-      </c>
+      <c r="U22" s="2" t="n"/>
       <c r="V22" s="3" t="n">
         <v>41478</v>
       </c>
@@ -1876,12 +1892,12 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>by 07/23/2013</t>
+          <t>07/24/2013</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>16 other financial NDA signers</t>
+          <t>Party B</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1891,7 +1907,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Did not submit</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F23" s="2" t="n">
@@ -1900,46 +1916,56 @@
       <c r="G23" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H23" s="2" t="n"/>
-      <c r="I23" s="2" t="n"/>
-      <c r="J23" s="2" t="n"/>
-      <c r="K23" s="2" t="n"/>
-      <c r="L23" s="2" t="n"/>
+      <c r="H23" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
       <c r="M23" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N23" s="2" t="n"/>
+      <c r="O23" s="2" t="n"/>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>Inferred: 20 signers − Party A (no NDA yet) − 3 submitters = 16; only B, C and CSC/Pamplona indications (plus Party A's 06/21 proposal) were reviewed 07/25. Any member signing after 07/23 would instead have been excluded when four advanced.</t>
+          <t>Unclear: no conditions or financing terms reported, and diligence was still ahead. Preliminary indication of interest, one day after the 07/23 due date. It was considered on 07/25.</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>representatives of BofA Merrill Lynch reviewed the preliminary indications of interest received from Party B, Party C and CSC/Pamplona as well as the Party A June 21 proposal (p. 33)</t>
+          <t>July 24, 2013, Party B submitted a preliminary indication of interest at an all-cash purchase price of $17.00 to $18.00 per share. (p. 33)</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="S23" s="2" t="n"/>
       <c r="T23" s="3" t="n">
-        <v>41478</v>
-      </c>
-      <c r="U23" s="2" t="n"/>
+        <v>41479</v>
+      </c>
+      <c r="U23" s="3" t="n">
+        <v>41479</v>
+      </c>
       <c r="V23" s="3" t="n">
-        <v>41478</v>
+        <v>41479</v>
       </c>
     </row>
     <row r="24">
@@ -1953,7 +1979,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Party B</t>
+          <t>Party C</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1973,10 +1999,10 @@
         <v>1</v>
       </c>
       <c r="H24" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="I24" s="4" t="n">
         <v>17</v>
-      </c>
-      <c r="I24" s="4" t="n">
-        <v>18</v>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
@@ -2000,17 +2026,17 @@
       <c r="O24" s="2" t="n"/>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>Conditions unclear: no conditions reported, but diligence was still open. Written preliminary indication one day after the 07/23 due date; reviewed 07/25.</t>
+          <t>Unclear: no conditions or financing terms reported, and diligence was still ahead. Oral preliminary indication phoned to BofA, one day after the 07/23 due date. Replaced by a written range on 07/25 (#25).</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>On July 24, 2013, Party B submitted a preliminary indication of interest at an all-cash purchase price of $17.00 to $18.00 per share. (p. 33)</t>
+          <t>representatives from Party C called BofA Merrill Lynch and presented an oral preliminary indication of interest at an all-cash purchase price of $15.00 to $17.00 per share. (p. 33)</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="S24" s="2" t="n"/>
@@ -2030,80 +2056,58 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>07/24/2013</t>
+          <t>07/25/2013</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Party C</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
+          <t>Mac-Gray</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n"/>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Round opened</t>
         </is>
       </c>
       <c r="F25" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="I25" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>Unclear</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="H25" s="2" t="n"/>
+      <c r="I25" s="2" t="n"/>
+      <c r="J25" s="2" t="n"/>
+      <c r="K25" s="2" t="n"/>
+      <c r="L25" s="2" t="n"/>
+      <c r="M25" s="2" t="n"/>
       <c r="N25" s="2" t="n"/>
       <c r="O25" s="2" t="n"/>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>Conditions unclear: no conditions reported, diligence still open. Oral preliminary indication made by phone to BofA one day after the due date; reviewed 07/25.</t>
+          <t>The Committee found the indications lower than expected and chose to stage disclosure of sensitive information, especially to strategic bidders. It admitted four bidders to management meetings and diligence before revised indications: Party A (if it signed an NDA), Party B, Party C and CSC/Pamplona. Only Party A and CSC/Pamplona would get synergy information. Rothenberg was recused.</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>representatives from Party C called BofA Merrill Lynch and presented an oral preliminary indication of interest at an all-cash purchase price of $15.00 to $17.00 per share (p. 33)</t>
+          <t>authorized and instructed BofA Merrill Lynch to proceed with the staged disclosure as discussed at this meeting and to reach out to each of the four interested bidders (p. 34)</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="S25" s="2" t="n"/>
       <c r="T25" s="3" t="n">
-        <v>41479</v>
+        <v>41480</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>41479</v>
+        <v>41480</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>41479</v>
+        <v>41480</v>
       </c>
     </row>
     <row r="26">
@@ -2117,42 +2121,64 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Mac-Gray</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="n"/>
+          <t>Party C</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Round opened</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H26" s="2" t="n"/>
-      <c r="I26" s="2" t="n"/>
-      <c r="J26" s="2" t="n"/>
-      <c r="K26" s="2" t="n"/>
-      <c r="L26" s="2" t="n"/>
-      <c r="M26" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N26" s="2" t="n"/>
       <c r="O26" s="2" t="n"/>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>Finding the indications lower than expected, the Special Committee advanced four bidders (Party A, if it signed an NDA; B; C; CSC/Pamplona) to management meetings, with staged disclosure of sensitive information, and then revised indications. All four had presentations 08/06–08/14.</t>
+          <t>Unclear: no conditions or financing terms reported. Written indication following up the oral one (#23): the low end rose from $15.00 and the high end fell from $17.00. Submitted after the 07/25 meeting, answering the round-1 request.</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>authorized and instructed BofA Merrill Lynch to proceed with the staged disclosure as discussed at this meeting and to reach out to each of the four interested bidders (p. 34)</t>
+          <t>Later on July 25, 2013, Party C submitted a written indication of interest at an all-cash purchase price of $16.00 to $16.50 per share. (p. 34)</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="S26" s="2" t="n"/>
@@ -2172,51 +2198,35 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>07/25/2013</t>
+          <t>08/05/2013</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Party C</t>
+          <t>Party A</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>NDA signed</t>
         </is>
       </c>
       <c r="F27" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="I27" s="4" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>Unclear</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="H27" s="2" t="n"/>
+      <c r="I27" s="2" t="n"/>
+      <c r="J27" s="2" t="n"/>
+      <c r="K27" s="2" t="n"/>
+      <c r="L27" s="2" t="n"/>
       <c r="M27" s="2" t="n">
         <v>1</v>
       </c>
@@ -2224,28 +2234,28 @@
       <c r="O27" s="2" t="n"/>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>Conditions unclear: no conditions reported, diligence still open. Written indication revising Party C's oral 07/24 range (#24); made after the 07/25 Special Committee meeting and answering the round 1 request.</t>
+          <t>Not a new entry: Party A entered with its 06/21 bid (#7). NDA talks had stalled over non-solicitation terms and resumed 07/27 (the filing prints 2103). With the NDA and information package, Party A joins the round-2 stage so it can improve its 06/21 proposal.</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>Later on July 25, 2013, Party C submitted a written indication of interest at an all-cash purchase price of $16.00 to $16.50 per share. (p. 34)</t>
+          <t>August 5, 2013, Party A entered into a confidentiality and standstill agreement with Mac-Gray and was provided with an informational package (p. 34)</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>Q1; Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="S27" s="2" t="n"/>
       <c r="T27" s="3" t="n">
-        <v>41480</v>
+        <v>41491</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>41480</v>
+        <v>41491</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>41480</v>
+        <v>41491</v>
       </c>
     </row>
     <row r="28">
@@ -2254,22 +2264,22 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>08/05/2013</t>
+          <t>08/06/2013-08/27/2013</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Party A</t>
+          <t>Party B, Party C</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>NDA signed</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
@@ -2284,18 +2294,18 @@
       <c r="K28" s="2" t="n"/>
       <c r="L28" s="2" t="n"/>
       <c r="M28" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N28" s="2" t="n"/>
       <c r="O28" s="2" t="n"/>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>Catch-up access for a late entrant: NDA talks resumed 07/27 once non-solicitation terms were agreed. Party A then received the informational package, to improve its 06/21 proposal. Already live since #7.</t>
+          <t>Unequal information access, financial side: B and C got broad data-room access, unlike the strategic bidders (#28). Management presentations: B 08/06, C 08/08. Follow-up diligence sessions: B 08/27, C 08/29.</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>On August 5, 2013, Party A entered into a confidentiality and standstill agreement with Mac-Gray and was provided with an informational package (p. 34)</t>
+          <t>Party B and Party C, in light of the fact that they were financial bidders, were given broad access to an electronic data site (p. 34)</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
@@ -2305,13 +2315,13 @@
       </c>
       <c r="S28" s="2" t="n"/>
       <c r="T28" s="3" t="n">
-        <v>41491</v>
+        <v>41502</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>41491</v>
+        <v>41492</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>41491</v>
+        <v>41513</v>
       </c>
     </row>
     <row r="29">
@@ -2320,15 +2330,19 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>between 08/06/2013 and 08/27/2013</t>
+          <t>08/06/2013-08/27/2013</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Mac-Gray</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="n"/>
+          <t>Party A, CSC/Pamplona</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Other material event</t>
@@ -2345,17 +2359,19 @@
       <c r="J29" s="2" t="n"/>
       <c r="K29" s="2" t="n"/>
       <c r="L29" s="2" t="n"/>
-      <c r="M29" s="2" t="n"/>
+      <c r="M29" s="2" t="n">
+        <v>2</v>
+      </c>
       <c r="N29" s="2" t="n"/>
       <c r="O29" s="2" t="n"/>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>Information access differed by type: financial bidders B and C got broad data-room access; strategic bidders A and CSC/Pamplona got limited access, with customer data (including locations) held back, but had synergy talks with management.</t>
+          <t>Unequal information access, strategic side: A and CSC/Pamplona got limited data-room access, with customer data (including locations) held back under the staging decided 07/25. Unlike B and C, they had synergy discussions with management. Management presentations: CSC/Pamplona 08/12, A 08/14.</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>Party B and Party C, in light of the fact that they were financial bidders, were given broad access to an electronic data site (p. 34)</t>
+          <t>Party A and CSC/Pamplona, in light of the fact that they were strategic bidders, were given somewhat limited access to this electronic data site (p. 34)</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
@@ -2410,7 +2426,7 @@
       <c r="O30" s="2" t="n"/>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>BofA's letter to all four bidders set 09/09/2013 as the due date for revised written proposals (valuation, financing, approvals, covenants, diligence), needed to go on to in-depth diligence. Authorized 08/15. Follow-up diligence calls: B 08/27, C 08/29, A 09/03.</t>
+          <t>Letter from BofA, authorized by the Committee on 08/15, to Party A, Party B, Party C and CSC/Pamplona. Bidders wishing to proceed to an in-depth evaluation must send revised written proposals by 09/09, covering valuation, financing, regulatory approvals, covenants and diligence. Follow-up diligence calls followed: B 08/27, C 08/29, A 09/03.</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -2420,7 +2436,7 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="S30" s="2" t="n"/>
@@ -2445,17 +2461,13 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>CSC/Pamplona</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Mac-Gray</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n"/>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Deadline</t>
         </is>
       </c>
       <c r="F31" s="2" t="n">
@@ -2464,40 +2476,22 @@
       <c r="G31" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H31" s="4" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="I31" s="4" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>Heavy</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="H31" s="2" t="n"/>
+      <c r="I31" s="2" t="n"/>
+      <c r="J31" s="2" t="n"/>
+      <c r="K31" s="2" t="n"/>
+      <c r="L31" s="2" t="n"/>
+      <c r="M31" s="2" t="n"/>
       <c r="N31" s="2" t="n"/>
       <c r="O31" s="2" t="n"/>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>Heavy: asked for two weeks of exclusive negotiations. Pamplona committed 100% of the required capital. A revised indication, on time; the next stage was to be in-depth diligence.</t>
+          <t>Due date for revised proposals. CSC/Pamplona and Party B bid on time. Party A and Party C bid on 09/10, and all four were reviewed on 09/11.</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>CSC/Pamplona submitted a revised indication of interest with an all-cash purchase price of $19.50 per share, indicating that Pamplona was committed to provide 100% of the capital required (p. 35)</t>
+          <t>submit revised written proposals no later than September 9, 2013 (p. 35)</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
@@ -2527,12 +2521,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Party B</t>
+          <t>CSC/Pamplona</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -2547,10 +2541,10 @@
         <v>2</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
@@ -2574,15 +2568,19 @@
       <c r="O32" s="2" t="n"/>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>Heavy: no firm financing commitment; to be financed by equity from affiliated funds plus third-party debt. A revised indication, on time.</t>
+          <t>Heavy: asks for two weeks of exclusive negotiations (E12). Pamplona committed to provide 100% of the capital needed. Revised indication, up from $18.50 (#20).</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>Party B also submitted a revised indication of interest with an all-cash purchase price of $18.50 per share and proposed to finance the transaction with a combination of equity (p. 35)</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="n"/>
+          <t>CSC/Pamplona submitted a revised indication of interest with an all-cash purchase price of $19.50 per share, indicating that Pamplona was committed to provide 100% of the capital required (p. 35)</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
       <c r="S32" s="2" t="n"/>
       <c r="T32" s="3" t="n">
         <v>41526</v>
@@ -2605,13 +2603,17 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Mac-Gray</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="n"/>
+          <t>Party B</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Deadline</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F33" s="2" t="n">
@@ -2620,29 +2622,43 @@
       <c r="G33" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H33" s="2" t="n"/>
-      <c r="I33" s="2" t="n"/>
-      <c r="J33" s="2" t="n"/>
-      <c r="K33" s="2" t="n"/>
-      <c r="L33" s="2" t="n"/>
-      <c r="M33" s="2" t="n"/>
+      <c r="H33" s="4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="I33" s="4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N33" s="2" t="n"/>
       <c r="O33" s="2" t="n"/>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>Round 2 due date. CSC/Pamplona and Party B bid on time; Party A and Party C bid on 09/10 and all four were reviewed on 09/11 (late bids accepted).</t>
+          <t>Heavy: no firm financing commitment. To be financed with equity from affiliated funds plus third-party debt. Revised indication, up from $17.00-$18.00 (#22).</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>submit revised written proposals no later than September 9, 2013 (p. 35)</t>
-        </is>
-      </c>
-      <c r="R33" s="2" t="inlineStr">
-        <is>
-          <t>Q4</t>
-        </is>
-      </c>
+          <t>Party B also submitted a revised indication of interest with an all-cash purchase price of $18.50 per share (p. 35)</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="n"/>
       <c r="S33" s="2" t="n"/>
       <c r="T33" s="3" t="n">
         <v>41526</v>
@@ -2712,17 +2728,17 @@
       <c r="O34" s="2" t="n"/>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>Heavy: no firm financing commitment (to use outstanding credit facilities or affiliated equity). A revised indication one day after the due date; its range equals its 06/21 proposal (#7).</t>
+          <t>Heavy: no firm financing commitment. To be financed from existing credit facilities or affiliated equity. Revised indication one day after the 09/09 due date; its low end rose from $17.00 (#7).</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>Party A submitted a revised indication of interest with an all-cash purchase price of $18.00 to $19.00 per share, to be financed by outstanding credit facilities or affiliated equity sources. (p. 35)</t>
+          <t>Party A submitted a revised indication of interest with an all-cash purchase price of $18.00 to $19.00 per share (p. 35)</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="S34" s="2" t="n"/>
@@ -2794,17 +2810,17 @@
       <c r="O35" s="2" t="n"/>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>Heavy: no firm financing commitment. A revised oral indication by phone to BofA, one day after the due date; up from its $16.00–$16.50 written range (#26).</t>
+          <t>Heavy: no firm financing commitment. Oral revised indication phoned to BofA, one day after the 09/09 due date. The high end rose from $16.50 (#25).</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>a representative of Party C indicated that it was submitting a revised oral indication of interest with an all-cash purchase price of $16.00 to $17.00 per share (p. 35)</t>
+          <t>a representative of Party C indicated that it was submitting a revised oral indication of interest with an all-cash purchase price of $16.00 to $17.00 per share. (p. 35)</t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="S35" s="2" t="n"/>
@@ -2829,7 +2845,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Stewart G. MacDonald, Jr. (CEO and major shareholder)</t>
+          <t>Stewart G. MacDonald, Jr. (CEO, major holder)</t>
         </is>
       </c>
       <c r="D36" s="2" t="n"/>
@@ -2854,12 +2870,12 @@
       <c r="O36" s="2" t="n"/>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>Rollover declined: after a limited briefing, MacDonald said he would not roll over any shares. BofA reported that no bidder was likely to proceed without his express support. He was fully briefed on 09/12 and urged seeking a higher value.</t>
+          <t>The CEO declined any rollover. BofA said the bidders were unlikely to proceed without his express support, so the Committee decided to brief him fully. He was briefed on 09/12: he backed continuing the process but urged a higher value, and on 09/19 said he would support $21.25.</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>Mr. MacDonald indicated that he had decided that he was not interested in rolling over any of his shares in any transaction. (p. 35)</t>
+          <t>During this call, Mr. MacDonald indicated that he had decided that he was not interested in rolling over any of his shares in any transaction. (p. 35)</t>
         </is>
       </c>
       <c r="R36" s="2" t="n"/>
@@ -2910,17 +2926,17 @@
       <c r="O37" s="2" t="n"/>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>Special Committee requested final indications from all four bidders by 09/18/2013. BofA told them by phone on 09/11 that Mac-Gray might grant one bidder short exclusivity depending on price and deal certainty. Diligence continued 09/11–09/18.</t>
+          <t>The Special Committee had BofA call Party A, Party B, Party C and CSC/Pamplona on 09/11 to request final indications by 09/18. Mac-Gray said it might grant one bidder a short exclusivity, based on price and deal certainty. The bidders continued diligence from 09/11 to 09/18.</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>the Special Committee instructed BofA Merrill Lynch to call each of Party A, Party B, Party C and CSC/Pamplona to request final indications of interest by September 18, 2013 (p. 36)</t>
+          <t>request final indications of interest by September 18, 2013 and to indicate that Mac-Gray would consider engaging in a short period of exclusive negotiations with one of the bidders (p. 36)</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>Q1; Q6; Q7</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="S37" s="2" t="n"/>
@@ -2945,17 +2961,13 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>CSC/Pamplona</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Mac-Gray</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n"/>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Deadline</t>
         </is>
       </c>
       <c r="F38" s="2" t="n">
@@ -2964,45 +2976,27 @@
       <c r="G38" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H38" s="4" t="n">
-        <v>20.75</v>
-      </c>
-      <c r="I38" s="4" t="n">
-        <v>20.75</v>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>Heavy</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="H38" s="2" t="n"/>
+      <c r="I38" s="2" t="n"/>
+      <c r="J38" s="2" t="n"/>
+      <c r="K38" s="2" t="n"/>
+      <c r="L38" s="2" t="n"/>
+      <c r="M38" s="2" t="n"/>
       <c r="N38" s="2" t="n"/>
       <c r="O38" s="2" t="n"/>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>Heavy: again asked for two weeks of exclusive negotiations. Pamplona still committed 100% of the capital. Final-round response. Up from $19.50 (#30).</t>
+          <t>Due date for final indications. CSC/Pamplona, Party A and Party B responded; Party C did not. The Committee met the next day (09/19) to act on the bids in hand.</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>CSC/Pamplona submitted a proposal for an all-cash purchase price of $20.75 per share, reiterating that Pamplona was committed to provide 100% of the capital required (p. 36)</t>
+          <t>request final indications of interest by September 18, 2013 (p. 36)</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>Q5; Q7</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="S38" s="2" t="n"/>
@@ -3027,7 +3021,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Party A</t>
+          <t>CSC/Pamplona</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -3047,10 +3041,10 @@
         <v>3</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>18</v>
+        <v>20.75</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>19</v>
+        <v>20.75</v>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
@@ -3074,17 +3068,17 @@
       <c r="O39" s="2" t="n"/>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>Heavy: repeats its 09/10 indication (#33), which had no firm financing commitment. By phone to BofA, Party A called its $18.00–$19.00 its best and final offer, in response to the final-round request. Price unchanged.</t>
+          <t>Heavy: again asks for two weeks of exclusive negotiations (E12). Pamplona committed 100% of the capital. Formal because it answers the request for final indications (E11.2). Up from $19.50 (#31).</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>its previous indication of interest with an all-cash purchase price of $18.00 to $19.00 per share was its best and final offer (p. 36)</t>
+          <t>CSC/Pamplona submitted a proposal for an all-cash purchase price of $20.75 per share, reiterating that Pamplona was committed to provide 100% of the capital required (p. 36)</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>Q7</t>
+          <t>Q6; Q8</t>
         </is>
       </c>
       <c r="S39" s="2" t="n"/>
@@ -3109,12 +3103,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Party B</t>
+          <t>Party A</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -3129,14 +3123,14 @@
         <v>3</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>21.5</v>
+        <v>18</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>21.5</v>
+        <v>19</v>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3146,7 +3140,7 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>Unclear</t>
+          <t>Heavy</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
@@ -3156,17 +3150,17 @@
       <c r="O40" s="2" t="n"/>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>Unclear: financing was expected from affiliated-fund equity plus third-party debt, but no commitment status was reported. $19.00 cash at closing plus options on 10% of new equity, vesting on base-case projections over five years; Party B valued the options at $2.50/share.</t>
+          <t>Heavy: it reiterates #33, which had no firm financing commitment. By phone to BofA, Party A called its $18.00-$19.00 indication its best and final offer. The price is unchanged; the row records Party A's answer to the final request (E11.2).</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>Party B also submitted a revised indication of interest with a purchase price that Party B valued at $21.50 per share, including $19.00 of cash to be paid at closing (p. 36)</t>
+          <t>its previous indication of interest with an all-cash purchase price of $18.00 to $19.00 per share was its best and final offer (p. 36)</t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>Q7; Q8</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="S40" s="2" t="n"/>
@@ -3191,7 +3185,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Party C</t>
+          <t>Party B</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -3201,7 +3195,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Did not submit</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F41" s="2" t="n">
@@ -3210,31 +3204,47 @@
       <c r="G41" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H41" s="2" t="n"/>
-      <c r="I41" s="2" t="n"/>
-      <c r="J41" s="2" t="n"/>
-      <c r="K41" s="2" t="n"/>
-      <c r="L41" s="2" t="n"/>
+      <c r="H41" s="4" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="I41" s="4" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
       <c r="M41" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
+      <c r="N41" s="2" t="n"/>
       <c r="O41" s="2" t="n"/>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>Party C neither submitted a final indication nor reaffirmed its $16.00–$17.00 indication (#34), and gave no reason. Reported 09/19.</t>
+          <t>Unclear: financing not reported as committed or uncommitted for this bid. The Committee noted likely equity-plus-debt financing and contingent options. $21.50 is Party B's valuation: $19.00 cash at closing plus options (10% of new equity, vesting on base-case projections over five years) that it valued at $2.50.</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t>Party C did not submit a revised indication of interest or reiterate its prior indication of interest of an all-cash purchase price of $16.00 to $17.00 per share (p. 36)</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="n"/>
+          <t>Party B also submitted a revised indication of interest with a purchase price that Party B valued at $21.50 per share, including $19.00 of cash to be paid at closing (p. 36)</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>Q8; Q9</t>
+        </is>
+      </c>
       <c r="S41" s="2" t="n"/>
       <c r="T41" s="3" t="n">
         <v>41535</v>
@@ -3257,13 +3267,17 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Mac-Gray</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="n"/>
+          <t>Party C</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Deadline</t>
+          <t>Did not submit</t>
         </is>
       </c>
       <c r="F42" s="2" t="n">
@@ -3277,22 +3291,28 @@
       <c r="J42" s="2" t="n"/>
       <c r="K42" s="2" t="n"/>
       <c r="L42" s="2" t="n"/>
-      <c r="M42" s="2" t="n"/>
-      <c r="N42" s="2" t="n"/>
+      <c r="M42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
       <c r="O42" s="2" t="n"/>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>Round 3 due date for final indications. Three bids arrived that day; Party C did not respond. The Special Committee acted on the bids in hand on 09/19.</t>
+          <t>Reported. Party C neither submitted a final indication nor reiterated its $16.00-$17.00 indication (#34), and gave no reason. It is not mentioned again.</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>request final indications of interest by September 18, 2013 (p. 36)</t>
+          <t>Party C did not submit a revised indication of interest or reiterate its prior indication of interest of an all-cash purchase price of $16.00 to $17.00 per share (p. 36)</t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>Q6</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="S42" s="2" t="n"/>
@@ -3312,7 +3332,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>09/19/2013</t>
+          <t>09/21/2013</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3342,24 +3362,28 @@
       <c r="O43" s="2" t="n"/>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>Preferred bidder and price requirement: Special Committee judged CSC/Pamplona most valuable and certain (Party B's options risky, its financing riskier) and offered exclusivity at $21.25/share. MacDonald said he would support $21.25.</t>
+          <t>Mac-Gray names CSC/Pamplona preferred bidder and sets a price condition. On 09/19 the Committee judged CSC/Pamplona best on value and certainty, over Party B's higher headline price with contingent options and debt financing. It authorized exclusivity at $21.25, and the Transaction Committee made the counter-proposal on 09/21.</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t>authorized the Transaction Committee to inform CSC/Pamplona that the Special Committee would be prepared to move into exclusivity at a price of $21.25 per share (p. 37)</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="n"/>
+          <t>propose that Mac-Gray was prepared to move forward with CSC/Pamplona on an exclusive basis for two weeks subject to CSC/Pamplona increasing their all-cash purchase price to $21.25 per share. (p. 37)</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>Q7</t>
+        </is>
+      </c>
       <c r="S43" s="2" t="n"/>
       <c r="T43" s="3" t="n">
-        <v>41536</v>
+        <v>41538</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>41536</v>
+        <v>41538</v>
       </c>
       <c r="V43" s="3" t="n">
-        <v>41536</v>
+        <v>41538</v>
       </c>
     </row>
     <row r="44">
@@ -3420,7 +3444,7 @@
       <c r="O44" s="2" t="n"/>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>Heavy: conditioned on two weeks of exclusive negotiations and voting agreements from MacDonald and family. Raised to $21.25 as its last and best offer, the same day the Transaction Committee proposed that price; Pamplona to fund 100%, no financing contingency.</t>
+          <t>Heavy: conditional on two weeks of exclusive negotiations, and CSC/Pamplona also asked for voting agreements from MacDonald and his family. Pamplona is to fund 100%. Its "last and best offer", up from $20.75 (#38), accepting the target's counter (#42).</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -3430,7 +3454,7 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>Q5; Q7</t>
+          <t>Q6; Q8</t>
         </is>
       </c>
       <c r="S44" s="2" t="n"/>
@@ -3455,7 +3479,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Mac-Gray and Moab Partners (Rothenberg)</t>
+          <t>Moab</t>
         </is>
       </c>
       <c r="D45" s="2" t="n"/>
@@ -3480,7 +3504,7 @@
       <c r="O45" s="2" t="n"/>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>Rollover permitted: Goodwin told Rothenberg of the CSC/Pamplona negotiations so that Moab could resume rollover talks with CSC/Pamplona. Rothenberg wanted to, and BofA arranged the talks.</t>
+          <t>Mac-Gray lets Moab resume rollover talks with CSC/Pamplona, with BofA to arrange them. Goodwin briefed Rothenberg on a limited basis. Rothenberg wanted to discuss a rollover.</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -3542,7 +3566,7 @@
       <c r="O46" s="2" t="n"/>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>Executed with CSC/Pamplona until 5 p.m. ET 10/12/2013 (authorized 09/23) on its final proposal: $21.25 cash, $15M reverse termination fee, no financing contingency. Exclusivity lapses automatically if the terms are adversely changed.</t>
+          <t>Executed exclusivity with CSC/Pamplona until 5 p.m. ET on 10/12 (authorized 09/23), on the final-proposal terms: $21.25 cash, a $15 million reverse termination fee if regulatory clearance fails, no financing contingency and 100% Pamplona funding. It ends automatically if CSC/Pamplona worsen those terms.</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -3612,7 +3636,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>Inferred: displaced when Mac-Gray signed exclusivity with CSC/Pamplona; the filing never mentions Party A in the process again. Its last offer, $18.00–$19.00, was called best and final (#38).</t>
+          <t>Inferred: Party A was a live rival when Mac-Gray signed exclusivity with CSC/Pamplona and is not mentioned again. Its last position was a best and final $18.00-$19.00 (#39), below CSC/Pamplona's $21.25.</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -3620,11 +3644,7 @@
           <t>CSC, Pamplona and Mac-Gray executed the exclusivity agreement providing for exclusive negotiations until 5 p.m. ET on October 12, 2013 (p. 38)</t>
         </is>
       </c>
-      <c r="R47" s="2" t="inlineStr">
-        <is>
-          <t>Q9</t>
-        </is>
-      </c>
+      <c r="R47" s="2" t="n"/>
       <c r="S47" s="2" t="n"/>
       <c r="T47" s="3" t="n">
         <v>41541</v>
@@ -3684,7 +3704,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>Inferred: displaced by the exclusivity with CSC/Pamplona. On 09/19 the Special Committee preferred CSC/Pamplona over Party B's nominally higher $21.50 package (#39) because of option and financing risk.</t>
+          <t>Inferred: Party B was a live rival when Mac-Gray signed exclusivity with CSC/Pamplona and is not mentioned again. Its last bid was $21.50 by its own valuation ($19.00 cash plus options, #40). The Committee preferred CSC/Pamplona on certainty.</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -3692,11 +3712,7 @@
           <t>CSC, Pamplona and Mac-Gray executed the exclusivity agreement providing for exclusive negotiations until 5 p.m. ET on October 12, 2013 (p. 38)</t>
         </is>
       </c>
-      <c r="R48" s="2" t="inlineStr">
-        <is>
-          <t>Q9</t>
-        </is>
-      </c>
+      <c r="R48" s="2" t="n"/>
       <c r="S48" s="2" t="n"/>
       <c r="T48" s="3" t="n">
         <v>41541</v>
@@ -3742,12 +3758,12 @@
       <c r="O49" s="2" t="n"/>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>Outside legal counsel to CSC/Pamplona; first reported acting when Goodwin sent it the first draft of the merger agreement.</t>
+          <t>CSC/Pamplona's outside legal counsel, first shown acting when Goodwin sent the first merger agreement draft. During exclusivity CSC/Pamplona got full data-room access and did confirmatory diligence; Party A and Party B were already out.</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
         <is>
-          <t>Goodwin Procter delivered to Kirkland &amp; Ellis LLP, outside legal counsel to CSC/Pamplona, whom we refer to as Kirkland, the initial draft of the merger agreement (p. 38)</t>
+          <t>Goodwin Procter delivered to Kirkland &amp; Ellis LLP, outside legal counsel to CSC/Pamplona, whom we refer to as Kirkland, the initial draft of the merger agreement. (p. 38)</t>
         </is>
       </c>
       <c r="R49" s="2" t="n"/>
@@ -3768,12 +3784,12 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>09/27/2013</t>
+          <t>09/25/2013-10/07/2013</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Stewart G. MacDonald, Jr. and family</t>
+          <t>Moab</t>
         </is>
       </c>
       <c r="D50" s="2" t="n"/>
@@ -3798,24 +3814,24 @@
       <c r="O50" s="2" t="n"/>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>Support agreement: MacDonald, his wife and one of his trusts signed voting agreements with CSC/Pamplona (a condition of CSC's 09/21 offer, #43), effective on signing of the merger agreement.</t>
+          <t>Moab decides against rolling over, after Rothenberg's talks with Pamplona. Reported to the Committee 10/07. Rothenberg was then briefed fully. Moab signed a voting agreement at signing (#52).</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>which were entered into by Mr. MacDonald, his wife and one of his trusts on September 27, 2013, and which became effective upon entry into the merger agreement (p. 39)</t>
+          <t>As a result of such discussions, it was determined that Moab would not rollover any Moab shares in the transaction. (p. 38)</t>
         </is>
       </c>
       <c r="R50" s="2" t="n"/>
       <c r="S50" s="2" t="n"/>
       <c r="T50" s="3" t="n">
-        <v>41544</v>
+        <v>41548</v>
       </c>
       <c r="U50" s="3" t="n">
-        <v>41544</v>
+        <v>41542</v>
       </c>
       <c r="V50" s="3" t="n">
-        <v>41544</v>
+        <v>41554</v>
       </c>
     </row>
     <row r="51">
@@ -3824,7 +3840,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>between 09/25/2013 and 10/07/2013</t>
+          <t>by 10/09/2013</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -3839,7 +3855,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Exclusivity changed</t>
         </is>
       </c>
       <c r="F51" s="2" t="n">
@@ -3860,24 +3876,22 @@
       <c r="O51" s="2" t="n"/>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>Information access: in exclusivity, CSC/Pamplona got full data-room access (customer data had been withheld from strategic bidders, #28) and management access, and did confirmatory diligence, including a 10/01 meeting.</t>
+          <t>CSC/Pamplona, through Kirkland, asked to extend exclusivity past 10/12 so open issues could be negotiated. The Committee authorized an extension to 10/15 (10/09). On 10/11 it made the extension conditional on a Mac-Gray termination fee of at most $11 million, and CSC/Pamplona agreed to $11 million.</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
         <is>
-          <t>CSC and Pamplona were granted full access to the electronic data site and access to certain members of management and conducted confirmatory business and legal due diligence (p. 38)</t>
+          <t>Goodwin Procter then reported that Kirkland had requested on behalf of CSC/Pamplona that the exclusivity agreement, due to expire at 5 p.m. ET on October 12, 2013, be extended (p. 40)</t>
         </is>
       </c>
       <c r="R51" s="2" t="n"/>
       <c r="S51" s="2" t="n"/>
       <c r="T51" s="3" t="n">
-        <v>41548</v>
-      </c>
-      <c r="U51" s="3" t="n">
-        <v>41542</v>
-      </c>
+        <v>41556</v>
+      </c>
+      <c r="U51" s="2" t="n"/>
       <c r="V51" s="3" t="n">
-        <v>41554</v>
+        <v>41556</v>
       </c>
     </row>
     <row r="52">
@@ -3886,18 +3900,22 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>between 09/25/2013 and 10/07/2013</t>
+          <t>10/12/2013</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Moab Partners (Rothenberg)</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="n"/>
+          <t>CSC/Pamplona</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Exclusivity changed</t>
         </is>
       </c>
       <c r="F52" s="2" t="n">
@@ -3911,29 +3929,31 @@
       <c r="J52" s="2" t="n"/>
       <c r="K52" s="2" t="n"/>
       <c r="L52" s="2" t="n"/>
-      <c r="M52" s="2" t="n"/>
+      <c r="M52" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N52" s="2" t="n"/>
       <c r="O52" s="2" t="n"/>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>Rollover abandoned: after talks between Rothenberg and Pamplona, it was decided that Moab would not roll over any shares (reported to the Special Committee 10/07). Moab signed a voting agreement at signing.</t>
+          <t>Exclusivity with CSC/Pamplona extended by letter agreement from 5 p.m. ET 10/12 to 11:59 p.m. ET 10/15. Given in return for CSC/Pamplona accepting the $11 million Mac-Gray termination fee (#50).</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
         <is>
-          <t>As a result of such discussions, it was determined that Moab would not rollover any Moab shares in the transaction. (p. 38)</t>
+          <t>CSC, Pamplona and Mac-Gray executed a letter agreement extending exclusivity until 11:59 p.m. ET on October 15, 2013. (p. 41)</t>
         </is>
       </c>
       <c r="R52" s="2" t="n"/>
       <c r="S52" s="2" t="n"/>
       <c r="T52" s="3" t="n">
-        <v>41548</v>
+        <v>41559</v>
       </c>
       <c r="U52" s="3" t="n">
-        <v>41542</v>
+        <v>41559</v>
       </c>
       <c r="V52" s="3" t="n">
-        <v>41554</v>
+        <v>41559</v>
       </c>
     </row>
     <row r="53">
@@ -3942,12 +3962,12 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>10/12/2013</t>
+          <t>10/14/2013</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>CSC/Pamplona</t>
+          <t>CSC/Pamplona (CSC ServiceWorks, Inc. via Spin Holdco Inc.)</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -3957,7 +3977,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Exclusivity changed</t>
+          <t>Merger agreement signed</t>
         </is>
       </c>
       <c r="F53" s="2" t="n">
@@ -3978,24 +3998,24 @@
       <c r="O53" s="2" t="n"/>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>Extended from 5 p.m. ET 10/12 to 11:59 p.m. ET 10/15/2013 at CSC/Pamplona's request (made 10/09). The Special Committee extended only after CSC/Pamplona accepted an $11M Mac-Gray termination fee on 10/11, down from its proposed $15M.</t>
+          <t>$21.25 per share in cash. $11 million Mac-Gray termination fee; $15 million reverse fee. Pamplona commits $594 million (p. 58), with liability capped at $50 million; no financing condition. No-shop with a fiduciary out; no go-shop. MacDonald and Moab voting agreements cover about 15%. BofA gave a fairness opinion.</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
         <is>
-          <t>On October 12, 2013, CSC, Pamplona and Mac-Gray executed a letter agreement extending exclusivity until 11:59 p.m. ET on October 15, 2013. (p. 41)</t>
+          <t>Later in the day, on October 14, 2013, the merger agreement was executed, the Pamplona commitment letter was delivered, Moab and Parent executed the Moab voting agreement (p. 41)</t>
         </is>
       </c>
       <c r="R53" s="2" t="n"/>
       <c r="S53" s="2" t="n"/>
       <c r="T53" s="3" t="n">
-        <v>41559</v>
+        <v>41561</v>
       </c>
       <c r="U53" s="3" t="n">
-        <v>41559</v>
+        <v>41561</v>
       </c>
       <c r="V53" s="3" t="n">
-        <v>41559</v>
+        <v>41561</v>
       </c>
     </row>
     <row r="54">
@@ -4004,122 +4024,60 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>10/14/2013</t>
+          <t>10/15/2013</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>CSC/Pamplona</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Mac-Gray and CSC</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n"/>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Merger agreement signed</t>
+          <t>Merger announced</t>
         </is>
       </c>
       <c r="F54" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G54" s="2" t="n">
-        <v>3</v>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
       </c>
       <c r="H54" s="2" t="n"/>
       <c r="I54" s="2" t="n"/>
       <c r="J54" s="2" t="n"/>
       <c r="K54" s="2" t="n"/>
       <c r="L54" s="2" t="n"/>
-      <c r="M54" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M54" s="2" t="n"/>
       <c r="N54" s="2" t="n"/>
       <c r="O54" s="2" t="n"/>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>$21.25/share cash; Pamplona commitment letter for $594M, no financing condition; $11M target fee; $15M reverse fee; Pamplona damages cap $50M. Moab and MacDonald voting agreements effective. BofA fairness opinion same day.</t>
+          <t>Joint public announcement of the merger agreement before the U.S. market opened. No competing proposal or termination is reported before the 12/04/2013 filing.</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
         <is>
-          <t>Later in the day, on October 14, 2013, the merger agreement was executed, the Pamplona commitment letter was delivered, Moab and Parent executed the Moab voting agreement (p. 41)</t>
+          <t>On October 15, 2013, before the U.S. stock markets opened, Mac-Gray and CSC jointly announced the execution of the merger agreement. (p. 41)</t>
         </is>
       </c>
       <c r="R54" s="2" t="n"/>
       <c r="S54" s="2" t="n"/>
       <c r="T54" s="3" t="n">
-        <v>41561</v>
+        <v>41562</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>41561</v>
+        <v>41562</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>41561</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>10/15/2013</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>Mac-Gray and CSC</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="n"/>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>Merger announced</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="n"/>
-      <c r="I55" s="2" t="n"/>
-      <c r="J55" s="2" t="n"/>
-      <c r="K55" s="2" t="n"/>
-      <c r="L55" s="2" t="n"/>
-      <c r="M55" s="2" t="n"/>
-      <c r="N55" s="2" t="n"/>
-      <c r="O55" s="2" t="n"/>
-      <c r="P55" s="2" t="inlineStr">
-        <is>
-          <t>Joint announcement before market open. No go-shop, and no competing proposal was reported before the filing (12/04/2013).</t>
-        </is>
-      </c>
-      <c r="Q55" s="2" t="inlineStr">
-        <is>
-          <t>On October 15, 2013, before the U.S. stock markets opened, Mac-Gray and CSC jointly announced the execution of the merger agreement. (p. 41)</t>
-        </is>
-      </c>
-      <c r="R55" s="2" t="n"/>
-      <c r="S55" s="2" t="n"/>
-      <c r="T55" s="3" t="n">
         <v>41562</v>
       </c>
-      <c r="U55" s="3" t="n">
-        <v>41562</v>
-      </c>
-      <c r="V55" s="3" t="n">
-        <v>41562</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V55"/>
+  <autoFilter ref="A1:V54"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4138,10 +4096,10 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="55" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="45" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
     <col width="45" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -4209,12 +4167,12 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Special Committee decision to approach 50 parties; BofA outreach, NDAs and informational package</t>
+          <t>Special Committee decision to approach 50 parties via BofA; NDA signers sent information package</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>19 NDA signers furnished the package: 1 strategic (CSC/Pamplona); 18 financial (Party B, Party C, 16 unnamed, some possibly signing after 07/23). Party A (strategic) — 06/21 proposal still being received, not admitted (NDA unsigned until 08/05)</t>
+          <t>19 admitted by NDA: 1 strategic (CSC/Pamplona); 18 financial (Party B, Party C, 16 unnamed, some possibly signing after 07/23 - Q3). Party A (strategic; 06/21 proposal, no NDA until 08/05) - still being received, not admitted</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -4234,12 +4192,12 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>3 bidders: CSC/Pamplona (07/23), Party B (07/24), Party C (07/24 oral, 07/25 written); Party A's 06/21 proposal also reviewed</t>
+          <t>3: CSC/Pamplona, Party B, Party C (Party A's round-0 proposal also reviewed 07/25)</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>four advanced (Party A, Party B, Party C, CSC/Pamplona); 16 financial signers out (inferred Did not submit)</t>
+          <t>four advanced (Party A, Party B, Party C, CSC/Pamplona); sixteen out (Did not submit, inferred)</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4213,12 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Special Committee selected four bidders for management meetings and staged diligence, then revised proposals</t>
+          <t>Committee selects four bidders for staged management meetings and diligence, then revised indications</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>4: 2 strategic (Party A, CSC/Pamplona), 2 financial (Party B, Party C)</t>
+          <t>4: 2 strategic (Party A from its 08/05 NDA, CSC/Pamplona); 2 financial (Party B, Party C)</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -4280,12 +4238,12 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>4 bidders: CSC/Pamplona, Party B (09/09); Party A, Party C (09/10)</t>
+          <t>4: CSC/Pamplona, Party B, Party A, Party C</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>all four asked for final indications; none out</t>
+          <t>four advanced to final-indication request; none out</t>
         </is>
       </c>
     </row>
@@ -4301,12 +4259,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>BofA called all four bidders requesting final indications of interest</t>
+          <t>BofA calls requesting final indications, with possible short exclusivity for one bidder</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4: 2 strategic (Party A, CSC/Pamplona), 2 financial (Party B, Party C)</t>
+          <t>4: 2 strategic (Party A, CSC/Pamplona); 2 financial (Party B, Party C)</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -4326,12 +4284,12 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3 bidders: CSC/Pamplona, Party A (reiterated best and final), Party B; Party C did not submit</t>
+          <t>3: CSC/Pamplona, Party A (reiteration), Party B</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>CSC/Pamplona preferred 09/19, raised to $21.25 09/21, exclusivity 09/24 (Party A, Party B dropped), signing 10/14/2013</t>
+          <t>Party C did not submit; exclusivity with CSC/Pamplona at $21.25 on 09/24 (Party A, Party B dropped); signing 10/14/2013</t>
         </is>
       </c>
     </row>
@@ -4350,13 +4308,13 @@
   <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="55" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4404,27 +4362,27 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Process and round map: one process with rounds 0–3?</t>
+          <t>Process and round map: is this one process with three rounds (round 1 opening 06/24/2013, round 2 07/25, round 3 09/11), with the 04/08 Party A call and the 06/21 Party A proposal in round 0?</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>One process. Round 0: the 04/08 approach to Party A and its 06/21 unsolicited proposal. R1 opens 06/24 (outreach began within four days). R2 opens 07/25 (four selected, management meetings, revised proposals). R3 opens 09/11 (first request for final indications). It ends in exclusivity 09/24 and signing 10/14.</t>
+          <t>Yes. One process, rounds opening 06/24, 07/25 and 09/11. Most plausible alternative: round 2 opens at the 08/27 letter rather than 07/25, which would remove #24, move #26, #27, #28 into round 1 and make #29 the round-2 opening.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Pp. 27–41. Gap of about two months or more with no reported contact with any prospective acquirer: 04/08/2013 to 06/21/2013. E5: (a) fails, since Party A was kept in view; (b) fails, since no end was reported and the gap is under three months; (c) the 06/24 decision is a fresh start. So there is no second process.</t>
+          <t>Round 1 opens with the 06/24 decision; outreach followed within days (p. 32). Round 2: four bidders selected into a staged information stage tied to revised offers (p. 33-34). Round 3: the first request for final indications (p. 36). Gaps of two months or more with no acquirer contact: 10/23/2012-04/08/2013 (before any sale step; #1 is a buy-side engagement) and 04/08-06/21/2013. E5: (a) fails, Party A kept in view (pp. 28, 31); (b) fails, gap under three months and no reported end; (c) met, 06/24. So no second process. The 2011-2012 Discussions were a target buy-side effort.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>#2, #7, #9, #25, #26, #27, #28, #36</t>
+          <t>#2, #7, #9, #24, #26, #27, #28, #29, #36</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Plausible alternative: open R2 at the 08/27 due-date letter. Party A's NDA (#27) and the access row (#28) would then move to R1. Party C's 07/25 written bid (#26) stays in R1 either way. Opening R1 on 06/28 (first dated outreach evidence) moves no rows.</t>
+          <t>If round 2 opened 08/27, round 1 would absorb the information stage, and Party A's NDA and the access differences would move to round 1. Treating 04/08 as the start of bilateral round-1 negotiation would move #2 and #7 into round 1 and make Party A's bid solicited.</t>
         </is>
       </c>
       <c r="G2" s="2" t="n"/>
@@ -4437,27 +4395,27 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Round 1 deadline outcome (due 07/23/2013)?</t>
+          <t>Outreach counts: are the contact cohorts right at 13 strategic and 35 financial, treating CSC/Pamplona as one of the 50 parties approached?</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Late bids accepted. CSC/Pamplona bid on 07/23. Party B (written) and Party C (oral) bid on 07/24, and both were reviewed on 07/25; Party C's written 07/25 bid followed. The Deadline set date (06/28, first informational package) is inferred.</t>
+          <t>Keep 13 and 35. The filing names CSC and Pamplona "together" as CSC/Pamplona inside the 50, and counts them as one strategic bidder among the 20 NDA signers.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>P. 32: NDA signers were 'instructed to submit by July 23, 2013'. P. 33: the 07/24 bids, and on 07/25 BofA reviewed the indications from Party B, Party C and CSC/Pamplona.</t>
+          <t>P. 32: 50 parties "including CSC and Pamplona, who together we refer to as CSC/Pamplona, and Party A", split 15 strategic and 35 financial. The NDA sentence counts "two strategic bidders (Party A and CSC/Pamplona)".</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>#13, #21, #23, #24, #26</t>
+          <t>#10, #11</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>If 07/23 were treated as a soft target, not a deadline, the outcome becomes Passed without action. Rows and live counts are unchanged.</t>
+          <t>If CSC and Pamplona were counted as two of the 50 (CSC strategic, Pamplona financial), the financial contact cohort would be 34. Nothing downstream changes.</t>
         </is>
       </c>
       <c r="G3" s="2" t="n"/>
@@ -4470,27 +4428,27 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Exits and timing of the 16 unnamed financial NDA signers?</t>
+          <t>Should the 16 unnamed financial NDA signers exit as Did not submit by 07/23/2013 (round 1) rather than Dropped by target on 07/25?</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Keep one cohort: Count 16 on entry (#19) and an inferred Did not submit by 07/23 (#22). No other indications were reported, and only four 'interested bidders' advanced on 07/25.</t>
+          <t>Did not submit by 07/23. Signers were asked for preliminary indications by 07/23, and only three signers submitted.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>P. 32: 20 signers '(2 strategic, 18 financial)' signed 'over the next two months'. P. 33: only three indications plus Party A's 06/21 proposal were reviewed. P. 34: 'the four interested bidders'.</t>
+          <t>P. 32: NDAs were signed "over the next two months", and signers were "instructed to submit by July 23". P. 33: the 07/25 review lists only Party B, Party C and CSC/Pamplona (plus Party A's 06/21 proposal). Some of the 16 may have signed after 07/23, since Party A signed 08/05.</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>#19, #22</t>
+          <t>#18, #21</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Some of the 16 may have signed after 07/23, some even after 07/25. Those would exit as Dropped by target (07/25 advancement) or Not selected at signing. The Round 1 admitted count would then fall below 19. Total entries are unaffected.</t>
+          <t>Any signer after 07/23 was never solicited and would instead be Dropped by target on 07/25, when the four advancing bidders were named. That changes the exit label for part of the 16 and the count of bidders who declined to bid.</t>
         </is>
       </c>
       <c r="G4" s="2" t="n"/>
@@ -4503,27 +4461,27 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Round 2 deadline outcome (due 09/09/2013)?</t>
+          <t>Round 1 deadline outcome: is 07/23/2013 "Late bids accepted"?</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Late bids accepted. CSC/Pamplona and Party B bid on 09/09. Party A and Party C bid on 09/10 and were still reviewed with the others by the Special Committee on 09/11.</t>
+          <t>Late bids accepted.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>P. 35: the letter required revised proposals 'no later than September 9, 2013'. On 09/10 Party A submitted and Party C gave an oral revised indication. On 09/11 the Committee reviewed the indications of all four.</t>
+          <t>Party B's written indication and Party C's oral indication came on 07/24 and were reviewed on 07/25 with CSC/Pamplona's on-time bid (p. 33). Party C's written range followed later on 07/25. No extension was given.</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>#29, #32, #33, #34</t>
+          <t>#19, #22, #23, #25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>None supported; the two late bids clearly were considered.</t>
+          <t>If one-day lateness is treated as immaterial, the outcome would be Enforced, since the Committee acted on the bids in hand on 07/25. Participation is unchanged either way.</t>
         </is>
       </c>
       <c r="G5" s="2" t="n"/>
@@ -4536,27 +4494,27 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Conditions on CSC/Pamplona's 09/09, 09/18 and 09/21 bids: Heavy or Light?</t>
+          <t>Round 2 deadline outcome: is 09/09/2013 "Late bids accepted"?</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Heavy. Each bid asked for, or was conditioned on, a two-week exclusive negotiation period, and E12 counts a stated exclusive period as a further diligence period. The 09/21 bid also required MacDonald voting agreements.</t>
+          <t>Late bids accepted.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Pp. 35–37: two weeks of exclusivity was requested on 09/09 and 09/18, and was a proviso of the 09/21 last-and-best offer. Pamplona committed 100% of the capital and had said its diligence would be minimal (p. 32).</t>
+          <t>The 08/27 letter set 09/09 (p. 35). Party A and Party C bid on 09/10 and were reviewed on 09/11 with the on-time bids of CSC/Pamplona and Party B (p. 35), and all four were invited to round 3.</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>#30, #37, #43</t>
+          <t>#30, #33, #34</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Light: financing was committed and diligence in exclusivity was only 'confirmatory' (p. 38). Rows #30, #37 and #43 would become Light, making the winner's bids far less conditional than its rivals'.</t>
+          <t>The alternative is Enforced, if the one-day delays are ignored. No bidder's participation changes.</t>
         </is>
       </c>
       <c r="G6" s="2" t="n"/>
@@ -4569,27 +4527,27 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Round 3 deadline outcome (due 09/18/2013)?</t>
+          <t>Conditions for CSC/Pamplona: Heavy (exclusive period requested) or Light (committed financing)?</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Enforced. CSC/Pamplona, Party A and Party B responded on 09/18; Party C did not. On 09/19 the Special Committee chose CSC/Pamplona from the bids in hand.</t>
+          <t>Heavy, as E12 counts a stated multi-week or exclusive period. Confirmatory diligence, including customer data held back until then, ran during exclusivity.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>P. 36: 'request final indications of interest by September 18, 2013'; the 09/18 submissions; and at the 09/19 meeting, 'Party C did not submit'.</t>
+          <t>P. 35 and 36: each bid asked for two weeks of exclusive negotiations, and Pamplona committed 100% of the capital. P. 38: CSC/Pamplona got full data-room access and did confirmatory diligence during exclusivity.</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>#36, #41</t>
+          <t>#31, #38, #43</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>None supported.</t>
+          <t>Light would make the winner's bids look nearly unconditional and more formal than the rivals'. Those rivals (Party A, Party B, Party C) are Heavy for lack of committed financing, or Unclear.</t>
         </is>
       </c>
       <c r="G7" s="2" t="n"/>
@@ -4602,27 +4560,27 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Is Round 3 a genuine final solicitation, making its bids Formal?</t>
+          <t>Round 3 deadline outcome: is 09/18/2013 "Enforced"?</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Yes. Round 3 is Announced as final: BofA asked all four bidders for 'final indications of interest'. The 09/18 responses (#37, #38, #39) and CSC/Pamplona's 09/21 last-and-best offer (#43) are therefore Formal under E11(2). Party A's 09/18 reiteration is a Round 3 Bid, not Bid reaffirmed, because the target was not finalizing with Party A.</t>
+          <t>Enforced.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>P. 36: 'request final indications of interest by September 18, 2013'. Party A called its range 'best and final'. No markup of the merger agreement was reported before exclusivity; the first draft was sent 09/25 (p. 38).</t>
+          <t>CSC/Pamplona, Party A and Party B responded by 09/18. Party C did not (p. 36). The Committee met on 09/19, weighed the three bids in hand and chose CSC/Pamplona with a $21.25 counter (p. 37). No extension or late bid is reported.</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>#36, #37, #38, #39, #43</t>
+          <t>#37, #41, #42</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>If 'final indications' are read as still non-binding, rows #37–#39 and #43 become Informal and the ledger has no Formal bid before signing. Dropping Party A's reiteration row would make it look like a non-response.</t>
+          <t>Passed without action would fit only if the 09/21 counter were read as continued bidding rather than the target acting on the bids. Participation is unchanged either way.</t>
         </is>
       </c>
       <c r="G8" s="2" t="n"/>
@@ -4635,27 +4593,27 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>How to price Party B's 09/18 cash-plus-options bid?</t>
+          <t>Round 3: are the responses to the request for "final indications of interest" Formal (E11.2), and should Party A's unchanged best-and-final reiteration be its own Bid row?</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Price cells hold $21.50, Party B's own stated package value: $19.00 cash at closing plus options valued at $2.50. All cash is No. Bid prices are otherwise per-share cash in US dollars.</t>
+          <t>Formal, and keep the Party A row. The request was the first call for final offers, it came with an exclusivity carrot, and it led straight to selection. Party A's reply changed its commitment to "best and final".</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>P. 36: the purchase price 'that Party B valued at $21.50 per share, including $19.00 of cash'. The options vest on base-case projections over five years. P. 37: the Committee judged them contingent and risky.</t>
+          <t>P. 36: BofA told the bidders to submit final indications by 09/18 and that exclusivity might follow. CSC/Pamplona called its 09/21 price a "last and best offer" (p. 37). No markup by a bidder before signing is reported apart from Kirkland's 10/07 draft.</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>#39</t>
+          <t>#38, #39, #40, #43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Recording $19.00 (cash only) would rank Party B below CSC/Pamplona's $20.75 rather than above it. That changes the interpretation of the winner's selection.</t>
+          <t>If "indications of interest" means the round was not genuinely final, #38, #39, #40 and #43 become Informal. The round would be Inferred final, and a Formal Bid reaffirmed for CSC/Pamplona at $21.25 would need adding at Kirkland's 10/07 merger-agreement draft (p. 39).</t>
         </is>
       </c>
       <c r="G9" s="2" t="n"/>
@@ -4668,27 +4626,27 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Exit label and reason for Party A and Party B at exclusivity?</t>
+          <t>Party B's 09/18 bid: should the price cells hold its own $21.50 package valuation, or the $19.00 cash component?</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Dropped by target by 09/24 (inferred), when exclusivity with CSC/Pamplona was signed; Exit reason Not stated. The filing never reports either bidder being told it was out, or leaving.</t>
+          <t>Keep $21.50, attributed in the Note to Party B's own valuation, with All cash = No. E13 puts a stated per-share package value in the price cells.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>P. 38: exclusivity executed 09/24. P. 37: on 09/19 the Special Committee preferred CSC/Pamplona on value and certainty. P. 36: Party A called $18–$19 its 'best and final offer'.</t>
+          <t>P. 36: $19.00 cash at closing plus options on 10% of the new equity, vesting on base-case projections over five years, which Party B valued at $2.50. On 09/19 the Committee discounted the options as contingent and deferred (p. 37).</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>#46, #47</t>
+          <t>#40</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Party A could take 'Would not improve earlier offer', since it declined to raise its price when asked for final bids. Party B could take 'Lower offer than rivals' on a risk-adjusted view, though it was nominally higher. Either reading changes the valuation information in the exit.</t>
+          <t>At $19.00, Party B would rank below CSC/Pamplona's $20.75 rather than above it. That changes how the model reads the target's choice of CSC/Pamplona.</t>
         </is>
       </c>
       <c r="G10" s="2" t="n"/>
@@ -4708,7 +4666,7 @@
   <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="110" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -4732,7 +4690,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Mac-Gray Corporation (NYSE), laundry facilities management contractor, Waltham, Massachusetts</t>
+          <t>Mac-Gray Corporation</t>
         </is>
       </c>
     </row>
@@ -4744,7 +4702,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>CSC ServiceWorks, Inc., through Spin Holdco Inc. (Parent) and CSC Fenway, Inc. (Merger Subsidiary), with CSC ServiceWorks Holdings, Inc.; CSC is a portfolio company of Pamplona Capital Partners III, L.P., which committed the equity (bidder unit: CSC/Pamplona)</t>
+          <t>CSC ServiceWorks, Inc. (with CSC ServiceWorks Holdings, Inc.; buyer entity Spin Holdco Inc., merger sub CSC Fenway, Inc.), a portfolio company of Pamplona; equity funded by Pamplona Capital Partners III, L.P. (bidder referred to as CSC/Pamplona)</t>
         </is>
       </c>
     </row>
@@ -4756,7 +4714,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Strategic (sponsor-owned operating company; the filing calls CSC/Pamplona a strategic bidder, p. 34)</t>
+          <t>Strategic (sponsor-owned operating company: CSC, laundry facilities operator owned by Pamplona)</t>
         </is>
       </c>
     </row>
@@ -4768,7 +4726,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>$21.25 per share in cash; funded by $594 million Pamplona equity commitment, no financing condition (pp. 5–6, 58)</t>
+          <t>$21.25 per share in cash; funded by a $594 million Pamplona commitment letter; no financing condition</t>
         </is>
       </c>
     </row>
@@ -4792,7 +4750,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>10/15/2013</t>
+          <t>10/15/2013 (before market open, joint announcement)</t>
         </is>
       </c>
     </row>
@@ -4804,7 +4762,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>DEFM14A (definitive proxy statement), 12/04/2013</t>
+          <t>DEFM14A, 12/04/2013</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4774,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>27–41</t>
+          <t>27-41</t>
         </is>
       </c>
     </row>
@@ -4828,7 +4786,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>target-led (board had BofA approach Party A on 04/08/2013 before any bid; Party A's 06/21/2013 proposal was unsolicited; activist Moab won two board seats 05/30/2013 but is not reported pressing for a sale)</t>
+          <t>target-led (Board-instructed BofA call to Party A 04/08/2013; Special Committee outreach from 06/24/2013); Moab, a proxy-contest activist, was involved via rollover interest but is not reported to have pressed for a sale</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4810,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Unspecified strategic discussions from time to time with CSC and other industry participants, including 2011–2012 talks about Mac-Gray acquiring CSC (BofA engaged 10/23/2012); CSC was instead sold to Pamplona in May 2013. None was a sale of Mac-Gray (p. 27).</t>
+          <t>None reported for a sale of Mac-Gray. The 2011-2012 Discussions concerned Mac-Gray possibly acquiring CSC (Mac-Gray as buyer), not a sale of the target.</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4822,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Met (process 1): 20 parties (2 strategic, 18 financial)</t>
+          <t>Met (process 1): 20 parties</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4846,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>US dollars per share, cash; exception: Party B's 09/18/2013 bid of $19.00 cash plus options it valued at $2.50 (Q8)</t>
+          <t>US dollars per share; all bids all-cash except Party B's 09/18 bid ($19.00 cash plus options it valued at $2.50; recorded at $21.50, Q9)</t>
         </is>
       </c>
     </row>
@@ -4900,7 +4858,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>BofA Merrill Lynch (Merrill Lynch, Pierce, Fenner &amp; Smith Incorporated)</t>
+          <t>BofA Merrill Lynch (buy-side engagement 10/23/2012-05/15/2013; sale-side engagement approved 05/30/2013, letter 05/31/2013; fairness opinion 10/14/2013)</t>
         </is>
       </c>
     </row>
@@ -4924,7 +4882,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>After Party A signalled interest in April 2013 and made an unsolicited $17–$19 proposal in June, a Special Committee had BofA Merrill Lynch approach 50 parties; 20 signed confidentiality agreements. Three preliminary indications arrived in July, and four bidders (Party A, CSC/Pamplona, and financial bidders Party B and Party C) advanced to management meetings, with customer data withheld from the strategic bidders. Revised indications in September ranged from $16–$17 to $19.50, and a request for final indications drew $20.75 from CSC/Pamplona, a best-and-final $18–$19 from Party A, and a $21.50 cash-and-options package from Party B, while Party C dropped out. The Special Committee preferred CSC/Pamplona's fully equity-backed offer and asked for $21.25, which CSC/Pamplona accepted as its last and best offer in return for two weeks' exclusivity. After exclusivity from 09/24, extended to 10/15, the merger agreement was signed at $21.25 in cash on 10/14/2013 and announced 10/15/2013.</t>
+          <t>After BofA Merrill Lynch sounded out Party A in April 2013, Party A made an unsolicited $17-$19 proposal on 06/21/2013, and a new Special Committee launched an outreach to 50 parties on 06/24. Twenty parties signed NDAs, and CSC/Pamplona, Party B and Party C sent preliminary indications around 07/23. Those three and Party A went into a staged second round, with strategic bidders kept from customer data, and all four submitted revised indications on 09/09-09/10. On the request for final indications by 09/18, Party C dropped out, Party A stood at $18-$19, Party B offered $19.00 cash plus options it valued at $21.50, and CSC/Pamplona offered $20.75 with fully committed Pamplona funding. The Committee countered at $21.25, CSC/Pamplona accepted as its last and best offer, and exclusivity was signed on 09/24 and extended on 10/12. The merger agreement at $21.25 cash was signed on 10/14/2013 and announced on 10/15/2013.</t>
         </is>
       </c>
     </row>
